--- a/tests/traces/mi300/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
+++ b/tests/traces/mi300/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2059,6 +2063,6745 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AJ6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_input_elems</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_output_elems</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>param: dtype_in_out</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>param: reduce_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GFLOPS_first</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Data Moved (MB)_first</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FLOPS/Byte_first</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_mean</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_median</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_std</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_min</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_max</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_mean</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_median</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_std</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_min</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_max</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Compute Spec</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details__summarize_kernel_stats</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_kernel_details</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Input Dims_first</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Input type_first</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Input Strides_first</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs_first</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>name_count</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>UID_first</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::linalg_norm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>norm</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>7.68e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0029296875</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.000653363847306895</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0006649950204568901</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0001044819361624662</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0005178579306938843</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0007983068138561096</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0001633409618267238</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0001662487551142225</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.612048404061655e-05</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0001294644826734711</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0001995767034640274</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>thread 14646 (python3)</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 10, 'total_duration_us': np.float64(48.14), 'mean_duration_us': np.float64(4.814), 'median_duration_us': np.float64(4.63), 'std_dev_duration_us': np.float64(0.7427319839619135), 'min_duration_us': np.float64(3.848), 'max_duration_us': np.float64(5.932)}]</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(4.81)}]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>[[1, 768], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'Scalar', 'ScalarList', 'Scalar', '']</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>[[768, 1], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>['', '2', '[-1]', 'True', '']</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.814013671875</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.630126953125</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.7829011025606529</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3.84814453125</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>5.93212890625</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>48.14013671875</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>4582</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::linalg_norm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3981312</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>norm</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.003981312</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.593751907348633</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4999998744132903</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.241544667684163</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.241432555420219</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.07091261215372953</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.15483733786559</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.351409467804757</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6207721779205716</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.6207161218026797</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.03545629717118316</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.5774185239005736</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.6757045641833098</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>thread 14646 (python3)</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(32.149), 'mean_duration_us': np.float64(6.4298), 'median_duration_us': np.float64(6.414), 'std_dev_duration_us': np.float64(0.32155770866206873), 'min_duration_us': np.float64(5.892), 'max_duration_us': np.float64(6.895)}]</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(6.43)}]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>[[1, 5184, 768], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', '', 'ScalarList', 'Scalar', '']</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>[[3981312, 768, 1], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>['', '', '[-1]', 'True', '']</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.4298828125</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>6.4140625</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.3594968174672817</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>5.89208984375</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>6.89501953125</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>32.1494140625</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>4654</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aten::linalg_norm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>norm</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>7.68e-07</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001466751098632812</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4993498049414825</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0003613396923387094</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0003620487356321839</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.779948916443615e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0003396036657681941</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0003876229387152351</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0001804349048869498</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0001807889655172414</v>
+      </c>
+      <c r="P4" t="n">
+        <v>8.888171442319212e-06</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.0001695810242587601</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.0001935594388382968</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>thread 14646 (python3)</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(21.323), 'mean_duration_us': np.float64(4.2646), 'median_duration_us': np.float64(4.248), 'std_dev_duration_us': np.float64(0.1855506399881175), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(4.529)}]</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(4.26)}]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>[[1, 1, 768], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', '', 'ScalarList', 'Scalar', '']</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>[[768, 768, 1], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>['', '', '[-1]', 'True', '']</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.26455078125</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4.248046875</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.2074897726824681</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3.9677734375</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>4.52880859375</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>21.32275390625</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>4658</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aten::max</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>5.184e-06</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.03955078125</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>thread 14646 (python3)</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>vector_fp32</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>[[1, 5184, 1], [], []]</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>['float', 'Scalar', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>[[5184, 1, 1], [], []]</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>['', '-1', 'False']</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>24159</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>aten::max</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>('int', None)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1e-09</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>thread 14646 (python3)</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>[[1], [1]]</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>['int', 'int']</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>[[2], [2]]</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>['', '']</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>24217</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parent op category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Parent cpu_op</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel stream</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_sum</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_count</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_mean</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_min</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_max</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Percent of kernels time (%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Percent of total time (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::cunn_SoftMaxForwardReg&lt;c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue, long, 6&gt;(c10::BFloat16*, c10::BFloat16 const*, long)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>153698.475</v>
+      </c>
+      <c r="F2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1280.820625</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1151.523</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1475.988</v>
+      </c>
+      <c r="J2" t="n">
+        <v>46.94231752031421</v>
+      </c>
+      <c r="K2" t="n">
+        <v>16.92084321134274</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x288x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA32_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_9_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>55056.329</v>
+      </c>
+      <c r="F3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G3" t="n">
+        <v>458.8027416666666</v>
+      </c>
+      <c r="H3" t="n">
+        <v>399.316</v>
+      </c>
+      <c r="I3" t="n">
+        <v>559.804</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16.81520703065455</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.0612150563049</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB256_LBSPPM0_LPA4_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>40460.247</v>
+      </c>
+      <c r="F4" t="n">
+        <v>120</v>
+      </c>
+      <c r="G4" t="n">
+        <v>337.1687250000001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>322.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>377.545</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12.35729737477448</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.454315475668841</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_5_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>15828.359</v>
+      </c>
+      <c r="F5" t="n">
+        <v>500</v>
+      </c>
+      <c r="G5" t="n">
+        <v>31.656718</v>
+      </c>
+      <c r="H5" t="n">
+        <v>28.705</v>
+      </c>
+      <c r="I5" t="n">
+        <v>38.488</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.834269526770016</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.742562383470921</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT160x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT5_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12190.583</v>
+      </c>
+      <c r="F6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G6" t="n">
+        <v>101.5881916666667</v>
+      </c>
+      <c r="H6" t="n">
+        <v>96.98099999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>110.813</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.723226388184688</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.342075408346506</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x288x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_9_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>11587.363</v>
+      </c>
+      <c r="F7" t="n">
+        <v>120</v>
+      </c>
+      <c r="G7" t="n">
+        <v>96.56135833333333</v>
+      </c>
+      <c r="H7" t="n">
+        <v>93.81399999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>105.121</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.538991998255939</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.275666219563428</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9666.441000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>720</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13.4256125</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I8" t="n">
+        <v>23.693</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.952307384399121</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.064189690709001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NORM_fwd</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5852.737</v>
+      </c>
+      <c r="F9" t="n">
+        <v>385</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15.20191428571429</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.409</v>
+      </c>
+      <c r="I9" t="n">
+        <v>28.384</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.787532625921573</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.6443345982074608</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4818.482</v>
+      </c>
+      <c r="F10" t="n">
+        <v>190</v>
+      </c>
+      <c r="G10" t="n">
+        <v>25.36043157894737</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.848</v>
+      </c>
+      <c r="I10" t="n">
+        <v>50.435</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.471652285488966</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5304722668112171</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4459.415</v>
+      </c>
+      <c r="F11" t="n">
+        <v>360</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12.38726388888889</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.209</v>
+      </c>
+      <c r="I11" t="n">
+        <v>33.957</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.361986674785498</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.4909421647111982</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>aten::sigmoid</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3837.21</v>
+      </c>
+      <c r="F12" t="n">
+        <v>185</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20.74167567567568</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="I12" t="n">
+        <v>33.035</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.171953919595656</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.4224428952791917</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3045.33</v>
+      </c>
+      <c r="F13" t="n">
+        <v>375</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8.12088</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.048</v>
+      </c>
+      <c r="I13" t="n">
+        <v>13.429</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9300993247599787</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.3352639084857438</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2164.27</v>
+      </c>
+      <c r="F14" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7.214233333333333</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.812</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6610075313999727</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.2382669921546895</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>555.234</v>
+      </c>
+      <c r="F15" t="n">
+        <v>120</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.62695</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.008</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.612</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.1695785903280702</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.06112635443914895</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>419.266</v>
+      </c>
+      <c r="F16" t="n">
+        <v>60</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6.987766666666667</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5.973</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8.657999999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1280514832529865</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.04615747976580005</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>384.538</v>
+      </c>
+      <c r="F17" t="n">
+        <v>60</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6.408966666666667</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.091</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8.659000000000001</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.1174449186605566</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0423342340046205</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>355.711</v>
+      </c>
+      <c r="F18" t="n">
+        <v>60</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.928516666666667</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.609</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7.857</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.108640627094501</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.03916063617124332</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>aten::miopen_convolution</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Cijk_Ailk_Bljk_BBS_BH_MT64x64x64_MI16x16x16x1_SN_1LDSB0_APM1_ABV0_ACED0_AF0EM1_AF1EM1_AMAS0_ASE_ASGT_ASLT_ASM_ASAE01_ASCE01_ASEM1_AAC0_BL1_BS1_CLR1_DTLA0_DTLB0_DTVA0_DTVB0_DVO0_ETSP_EPS1_ELFLR0_EMLL0_FSSC10_FL0_GLVWA2_GLVWB8_GRCGA1_GRCGB1_GRPM1_GRVWn1_GSU1_GSUASB_GLS0_ISA942_IU1_K1_KLA_LBSPPA1024_LBSPPB128_LPA16_LPB16_LDL1_LRVW8_LWPMn1_LDW0_FMA_MIAV0_MDA2_MO40_MMFSC_MKFGSU256_NTA0_NTB0_NTC0_NTD0_NEPBS0_NLCA1_NLCB1_ONLL1_OPLV0_PK0_PAP0_PGR1_PLR5_PKA0_SIA3_SLW1_SS0_SU16_SUM0_SUS512_SCIUI1_SPO0_SRVW0_SSO0_SVW4_SNLL0_TSGRA0_TSGRB0_TT1_64_TLDS1_UMLDSA0_UMLDSB1_U64SL1_USFGROn1_VAW1_VSn1_VW1_VWB1_VFLRP1_WSGRA0_WSGRB0_WS64_WG64_4_1_WGMn16</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>298.641</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>59.7282</v>
+      </c>
+      <c r="H19" t="n">
+        <v>56.328</v>
+      </c>
+      <c r="I19" t="n">
+        <v>60.899</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.09121040821377152</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.03287773374120079</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>294.657</v>
+      </c>
+      <c r="F20" t="n">
+        <v>60</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4.91095</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.249</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.093</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.08999362195092191</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.03243913056472822</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>289.404</v>
+      </c>
+      <c r="F21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14.4702</v>
+      </c>
+      <c r="H21" t="n">
+        <v>9.461</v>
+      </c>
+      <c r="I21" t="n">
+        <v>20.085</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.08838925994320382</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0318608217077979</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA1_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB4_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS0_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_1</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>282.956</v>
+      </c>
+      <c r="F22" t="n">
+        <v>15</v>
+      </c>
+      <c r="G22" t="n">
+        <v>18.86373333333334</v>
+      </c>
+      <c r="H22" t="n">
+        <v>15.234</v>
+      </c>
+      <c r="I22" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.08641992314027858</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.03115095391615757</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>aten::miopen_convolution</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Im2d2Col_v2</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>219.258</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>43.8516</v>
+      </c>
+      <c r="H23" t="n">
+        <v>40.372</v>
+      </c>
+      <c r="I23" t="n">
+        <v>45.063</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.06696539217366375</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.02413836728589914</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>aten::cat</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>149.136</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>29.8272</v>
+      </c>
+      <c r="H24" t="n">
+        <v>29.306</v>
+      </c>
+      <c r="I24" t="n">
+        <v>30.789</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.04554885444185168</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.01641855505181044</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x64x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB4_WSGRA0_WSGRB0_WS64_WG64_4_1</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>136.148</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>27.2296</v>
+      </c>
+      <c r="H25" t="n">
+        <v>26.139</v>
+      </c>
+      <c r="I25" t="n">
+        <v>28.104</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.04158208235804382</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.01498869108192447</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>aten::div</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>122.944</v>
+      </c>
+      <c r="F26" t="n">
+        <v>20</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6.1472</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.088</v>
+      </c>
+      <c r="I26" t="n">
+        <v>10.544</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.03754933993468387</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.01353504742174782</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>reduce</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>aten::linalg_vector_norm</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>101.612</v>
+      </c>
+      <c r="F27" t="n">
+        <v>20</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.0806</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.848</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6.895</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.031034158067438</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.01118658282322553</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>89.11500000000001</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8.9115</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5.411</v>
+      </c>
+      <c r="I28" t="n">
+        <v>36.603</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.02721734633881566</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.009810773612287358</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>83.667</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>16.7334</v>
+      </c>
+      <c r="H29" t="n">
+        <v>15.595</v>
+      </c>
+      <c r="I29" t="n">
+        <v>18.161</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.02555342777455748</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.009210996979400171</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>69.666</v>
+      </c>
+      <c r="F30" t="n">
+        <v>15</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4.6444</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.248</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.02127726701497988</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.007669610665697256</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>68.78400000000001</v>
+      </c>
+      <c r="F31" t="n">
+        <v>15</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4.5856</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.048</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5.171</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.02100788812847553</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.007572510263676975</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA1_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB4_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS0_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_1</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>60.253</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>12.0506</v>
+      </c>
+      <c r="H32" t="n">
+        <v>11.345</v>
+      </c>
+      <c r="I32" t="n">
+        <v>12.628</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.01840236513440678</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.006633322588353814</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>59.888</v>
+      </c>
+      <c r="F33" t="n">
+        <v>10</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5.988799999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6.574</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.0182908874772933</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.006593139315408912</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>59.051</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>11.8102</v>
+      </c>
+      <c r="H34" t="n">
+        <v>11.345</v>
+      </c>
+      <c r="I34" t="n">
+        <v>12.387</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.01803525241152897</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.006500993015532522</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>aten::where</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>55.763</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>11.1526</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="I35" t="n">
+        <v>35.961</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.01703103724279165</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.00613901328555215</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bjlk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x16x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB1_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>47.143</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>9.428599999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10.062</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.01439833202548153</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.00519002749709996</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>aten::arange</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>45.574</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4.557399999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="I37" t="n">
+        <v>5.171</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.0139191308090129</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.00501729446901626</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>reduce</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>aten::argmax</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4, 4&gt; &gt;(at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>37.76300000000001</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>7.552600000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>7.256</v>
+      </c>
+      <c r="I38" t="n">
+        <v>8.057</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.01153350894678445</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.004157372427995372</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>aten::index</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>void at::native::index_elementwise_kernel&lt;128, 4, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1}&gt;(long, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6.581999999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>6.253</v>
+      </c>
+      <c r="I39" t="n">
+        <v>6.975</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.01005131423453317</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.003623100034566312</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>31.067</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>6.2134</v>
+      </c>
+      <c r="H40" t="n">
+        <v>6.013</v>
+      </c>
+      <c r="I40" t="n">
+        <v>6.775</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.009488428420669765</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.003420202028984249</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>26.455</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5.290999999999999</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I41" t="n">
+        <v>5.732</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.008079839503937253</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.0029124616048147</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>25.814</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5.1628</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5.451</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.007884066412951665</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.002841893172053928</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>aten::sub</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>25.655</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5.131</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5.652</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.007835504913003602</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.002824388677812177</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>aten::fill_</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>4.938</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4.449</v>
+      </c>
+      <c r="I44" t="n">
+        <v>5.251</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.00754077631268988</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.002718150709615383</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4.842000000000001</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4.489</v>
+      </c>
+      <c r="I45" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.007394175558129689</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.002665306953413869</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>24.131</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4.8262</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="I46" t="n">
+        <v>5.251</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.00737004751727499</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.00265660975187237</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>aten::exp</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>24.051</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>4.8102</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5.211</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.007345614058181626</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.002647802459172118</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2})</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>23.769</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4.7538</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4.529</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5.051</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.007259486114877511</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.002616756752403727</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>aten::lt</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>23.769</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.7538</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4.409</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.007259486114877511</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.002616756752403727</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>aten::gt</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>23.568</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4.7136</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4.329</v>
+      </c>
+      <c r="I50" t="n">
+        <v>5.251</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.007198097048905431</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.002594628429494344</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>23.369</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4.6738</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4.449</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.007137318819410684</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.002572720288902466</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>aten::masked_fill_</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4.489</v>
+      </c>
+      <c r="I52" t="n">
+        <v>4.851</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.007100974049009304</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.002559619441010841</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>aten::add_</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>22.928</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4.585599999999999</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4.169</v>
+      </c>
+      <c r="I53" t="n">
+        <v>5.291</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.007002629376158508</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.002524170087892325</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>aten::fill_</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>22.646</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4.5292</v>
+      </c>
+      <c r="H54" t="n">
+        <v>4.088</v>
+      </c>
+      <c r="I54" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.006916501432854396</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.002493124381123936</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>aten::masked_fill_</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>22.366</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>4.4732</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4.289</v>
+      </c>
+      <c r="I55" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.006830984326027616</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.002462298856673052</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>aten::elu</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>21.964</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>4.392799999999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="I56" t="n">
+        <v>4.689</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.006708206194083456</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.002418042210854284</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>aten::eq</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>21.845</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>4.369</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3.888</v>
+      </c>
+      <c r="I57" t="n">
+        <v>5.091</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.006671861423682076</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.002404941362962658</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>bin_start</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>bin_end</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2.83717</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.83717</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2.90934</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2.90934</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2.98151</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2.98151</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3.05368</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3.05368</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3.12585</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3.12585</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3.19802</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3.19802</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3.27019</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3.27019</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3.34236</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3.34236</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3.41453</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3.41453</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3.4867</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3.4867</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3.55887</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3.55887</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3.63104</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3.63104</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3.70321</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3.70321</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3.77538</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3.77538</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3.84755</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3.84755</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3.91972</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3.91972</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3.99189</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3.99189</v>
+      </c>
+      <c r="B19" t="n">
+        <v>4.06406</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4.06406</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4.136229999999999</v>
+      </c>
+      <c r="C20" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4.136229999999999</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4.208399999999999</v>
+      </c>
+      <c r="C21" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4.208399999999999</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4.28057</v>
+      </c>
+      <c r="C22" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4.28057</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4.35274</v>
+      </c>
+      <c r="C23" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.35274</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4.42491</v>
+      </c>
+      <c r="C24" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.42491</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4.49708</v>
+      </c>
+      <c r="C25" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4.49708</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4.56925</v>
+      </c>
+      <c r="C26" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>4.56925</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4.64142</v>
+      </c>
+      <c r="C27" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>4.64142</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4.71359</v>
+      </c>
+      <c r="C28" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>4.71359</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4.78576</v>
+      </c>
+      <c r="C29" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>4.78576</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4.85793</v>
+      </c>
+      <c r="C30" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>4.85793</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4.930099999999999</v>
+      </c>
+      <c r="C31" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>4.930099999999999</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5.002269999999999</v>
+      </c>
+      <c r="C32" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>5.002269999999999</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5.074439999999999</v>
+      </c>
+      <c r="C33" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>5.074439999999999</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5.146609999999999</v>
+      </c>
+      <c r="C34" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>5.146609999999999</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5.21878</v>
+      </c>
+      <c r="C35" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5.21878</v>
+      </c>
+      <c r="B36" t="n">
+        <v>5.29095</v>
+      </c>
+      <c r="C36" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>5.29095</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5.363119999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5.363119999999999</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5.43529</v>
+      </c>
+      <c r="C38" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>5.43529</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5.50746</v>
+      </c>
+      <c r="C39" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>5.50746</v>
+      </c>
+      <c r="B40" t="n">
+        <v>5.57963</v>
+      </c>
+      <c r="C40" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>5.57963</v>
+      </c>
+      <c r="B41" t="n">
+        <v>5.6518</v>
+      </c>
+      <c r="C41" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5.6518</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5.72397</v>
+      </c>
+      <c r="C42" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5.72397</v>
+      </c>
+      <c r="B43" t="n">
+        <v>5.796139999999999</v>
+      </c>
+      <c r="C43" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>5.796139999999999</v>
+      </c>
+      <c r="B44" t="n">
+        <v>5.868309999999999</v>
+      </c>
+      <c r="C44" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>5.868309999999999</v>
+      </c>
+      <c r="B45" t="n">
+        <v>5.940479999999999</v>
+      </c>
+      <c r="C45" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5.940479999999999</v>
+      </c>
+      <c r="B46" t="n">
+        <v>6.012649999999999</v>
+      </c>
+      <c r="C46" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>6.012649999999999</v>
+      </c>
+      <c r="B47" t="n">
+        <v>6.084819999999999</v>
+      </c>
+      <c r="C47" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>6.084819999999999</v>
+      </c>
+      <c r="B48" t="n">
+        <v>6.15699</v>
+      </c>
+      <c r="C48" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>6.15699</v>
+      </c>
+      <c r="B49" t="n">
+        <v>6.229159999999999</v>
+      </c>
+      <c r="C49" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>6.229159999999999</v>
+      </c>
+      <c r="B50" t="n">
+        <v>6.301329999999999</v>
+      </c>
+      <c r="C50" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>6.301329999999999</v>
+      </c>
+      <c r="B51" t="n">
+        <v>6.3735</v>
+      </c>
+      <c r="C51" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>6.3735</v>
+      </c>
+      <c r="B52" t="n">
+        <v>6.44567</v>
+      </c>
+      <c r="C52" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>6.44567</v>
+      </c>
+      <c r="B53" t="n">
+        <v>6.51784</v>
+      </c>
+      <c r="C53" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>6.51784</v>
+      </c>
+      <c r="B54" t="n">
+        <v>6.590009999999999</v>
+      </c>
+      <c r="C54" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>6.590009999999999</v>
+      </c>
+      <c r="B55" t="n">
+        <v>6.662179999999999</v>
+      </c>
+      <c r="C55" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>6.662179999999999</v>
+      </c>
+      <c r="B56" t="n">
+        <v>6.734349999999999</v>
+      </c>
+      <c r="C56" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>6.734349999999999</v>
+      </c>
+      <c r="B57" t="n">
+        <v>6.806519999999999</v>
+      </c>
+      <c r="C57" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>6.806519999999999</v>
+      </c>
+      <c r="B58" t="n">
+        <v>6.878689999999999</v>
+      </c>
+      <c r="C58" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>6.878689999999999</v>
+      </c>
+      <c r="B59" t="n">
+        <v>6.950859999999999</v>
+      </c>
+      <c r="C59" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>6.950859999999999</v>
+      </c>
+      <c r="B60" t="n">
+        <v>7.023029999999999</v>
+      </c>
+      <c r="C60" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>7.023029999999999</v>
+      </c>
+      <c r="B61" t="n">
+        <v>7.095199999999998</v>
+      </c>
+      <c r="C61" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>7.095199999999998</v>
+      </c>
+      <c r="B62" t="n">
+        <v>7.16737</v>
+      </c>
+      <c r="C62" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>7.16737</v>
+      </c>
+      <c r="B63" t="n">
+        <v>7.23954</v>
+      </c>
+      <c r="C63" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>7.23954</v>
+      </c>
+      <c r="B64" t="n">
+        <v>7.31171</v>
+      </c>
+      <c r="C64" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>7.31171</v>
+      </c>
+      <c r="B65" t="n">
+        <v>7.38388</v>
+      </c>
+      <c r="C65" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>7.38388</v>
+      </c>
+      <c r="B66" t="n">
+        <v>7.456049999999999</v>
+      </c>
+      <c r="C66" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>7.456049999999999</v>
+      </c>
+      <c r="B67" t="n">
+        <v>7.528219999999999</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>7.528219999999999</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7.600389999999999</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>7.600389999999999</v>
+      </c>
+      <c r="B69" t="n">
+        <v>7.672559999999999</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>7.672559999999999</v>
+      </c>
+      <c r="B70" t="n">
+        <v>7.744729999999999</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>7.744729999999999</v>
+      </c>
+      <c r="B71" t="n">
+        <v>7.816899999999999</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>7.816899999999999</v>
+      </c>
+      <c r="B72" t="n">
+        <v>7.889069999999998</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>7.889069999999998</v>
+      </c>
+      <c r="B73" t="n">
+        <v>7.961239999999998</v>
+      </c>
+      <c r="C73" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>7.961239999999998</v>
+      </c>
+      <c r="B74" t="n">
+        <v>8.033409999999998</v>
+      </c>
+      <c r="C74" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>8.033409999999998</v>
+      </c>
+      <c r="B75" t="n">
+        <v>8.10558</v>
+      </c>
+      <c r="C75" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>8.10558</v>
+      </c>
+      <c r="B76" t="n">
+        <v>8.17775</v>
+      </c>
+      <c r="C76" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>8.17775</v>
+      </c>
+      <c r="B77" t="n">
+        <v>8.249919999999999</v>
+      </c>
+      <c r="C77" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>8.249919999999999</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8.322089999999999</v>
+      </c>
+      <c r="C78" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>8.322089999999999</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8.394259999999999</v>
+      </c>
+      <c r="C79" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>8.394259999999999</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8.466429999999999</v>
+      </c>
+      <c r="C80" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>8.466429999999999</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8.538599999999999</v>
+      </c>
+      <c r="C81" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>8.538599999999999</v>
+      </c>
+      <c r="B82" t="n">
+        <v>8.610769999999999</v>
+      </c>
+      <c r="C82" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>8.610769999999999</v>
+      </c>
+      <c r="B83" t="n">
+        <v>8.682939999999999</v>
+      </c>
+      <c r="C83" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>8.682939999999999</v>
+      </c>
+      <c r="B84" t="n">
+        <v>8.755109999999998</v>
+      </c>
+      <c r="C84" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>8.755109999999998</v>
+      </c>
+      <c r="B85" t="n">
+        <v>8.827279999999998</v>
+      </c>
+      <c r="C85" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>8.827279999999998</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8.899449999999998</v>
+      </c>
+      <c r="C86" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>8.899449999999998</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8.971619999999998</v>
+      </c>
+      <c r="C87" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>8.971619999999998</v>
+      </c>
+      <c r="B88" t="n">
+        <v>9.04379</v>
+      </c>
+      <c r="C88" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>9.04379</v>
+      </c>
+      <c r="B89" t="n">
+        <v>9.115959999999999</v>
+      </c>
+      <c r="C89" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>9.115959999999999</v>
+      </c>
+      <c r="B90" t="n">
+        <v>9.188129999999999</v>
+      </c>
+      <c r="C90" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>9.188129999999999</v>
+      </c>
+      <c r="B91" t="n">
+        <v>9.260299999999999</v>
+      </c>
+      <c r="C91" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>9.260299999999999</v>
+      </c>
+      <c r="B92" t="n">
+        <v>9.332469999999999</v>
+      </c>
+      <c r="C92" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>9.332469999999999</v>
+      </c>
+      <c r="B93" t="n">
+        <v>9.404639999999999</v>
+      </c>
+      <c r="C93" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>9.404639999999999</v>
+      </c>
+      <c r="B94" t="n">
+        <v>9.476809999999999</v>
+      </c>
+      <c r="C94" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>9.476809999999999</v>
+      </c>
+      <c r="B95" t="n">
+        <v>9.548979999999998</v>
+      </c>
+      <c r="C95" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>9.548979999999998</v>
+      </c>
+      <c r="B96" t="n">
+        <v>9.621149999999998</v>
+      </c>
+      <c r="C96" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>9.621149999999998</v>
+      </c>
+      <c r="B97" t="n">
+        <v>9.693319999999998</v>
+      </c>
+      <c r="C97" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>9.693319999999998</v>
+      </c>
+      <c r="B98" t="n">
+        <v>9.765489999999998</v>
+      </c>
+      <c r="C98" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>9.765489999999998</v>
+      </c>
+      <c r="B99" t="n">
+        <v>9.837659999999998</v>
+      </c>
+      <c r="C99" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>9.837659999999998</v>
+      </c>
+      <c r="B100" t="n">
+        <v>9.909829999999998</v>
+      </c>
+      <c r="C100" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>9.909829999999998</v>
+      </c>
+      <c r="B101" t="n">
+        <v>9.981999999999999</v>
+      </c>
+      <c r="C101" t="n">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parent cpu_op</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Input dims</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Input strides</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) sum</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel count</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) mean</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) percent of total time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>((768,), (5, 768), (768, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>((1,), (768, 1), (1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1649.788</v>
+      </c>
+      <c r="G2" t="n">
+        <v>240</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6.874116666666667</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1816270726170491</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>((1, 5185, 1024), (1, 5185, 1024), ())</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>((5309440, 1024, 1), (5309440, 1024, 1), ())</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1202.107</v>
+      </c>
+      <c r="G3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9.3914609375</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1323413525752782</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>((1, 12, 5, 64), (1, 12, 5, 64), ())</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>((3840, 320, 64, 1), (3840, 64, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1058.898</v>
+      </c>
+      <c r="G4" t="n">
+        <v>180</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.882766666666666</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1165753078213977</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>((1, 5185, 1024), ())</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>((5309440, 1024, 1), ())</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>857.976</v>
+      </c>
+      <c r="G5" t="n">
+        <v>119</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7.209882352941176</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.09445557202239642</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>((1, 5, 768), (), (768,), (768,), ())</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>((3840, 768, 1), (), (1,), (1,), ())</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>('', '[768]', '', '', '1.0000000000000001e-05')</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>646.436</v>
+      </c>
+      <c r="G6" t="n">
+        <v>125</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.171488</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.07116688829975415</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>((1, 5, 768), (1, 5, 768), ())</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>((3840, 768, 1), (3840, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>572.149</v>
+      </c>
+      <c r="G7" t="n">
+        <v>125</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.577192</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.06298854638945856</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>((1, 12, 5, 5), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>((300, 25, 5, 1), (25, 25, 5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>555.234</v>
+      </c>
+      <c r="G8" t="n">
+        <v>120</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.62695</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.06112635443914895</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>((768,), (5, 3072), (3072, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>((1,), (3072, 1), (1, 3072), (), ())</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>514.482</v>
+      </c>
+      <c r="G9" t="n">
+        <v>60</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8.5747</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.05663991953764039</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>((3072,), (5, 768), (768, 3072), (), ())</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>((1,), (768, 1), (1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>419.266</v>
+      </c>
+      <c r="G10" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.987766666666667</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.04615747976580005</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>((1, 5, 12, 64), (1, 5, 12, 64), ())</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>((3840, 768, 64, 1), (3840, 64, 320, 1), ())</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>401.827</v>
+      </c>
+      <c r="G11" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.697116666666667</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.04423760004830379</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>((12, 5, 5), (12, 5, 64))</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>((25, 5, 1), (320, 64, 1))</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>384.538</v>
+      </c>
+      <c r="G12" t="n">
+        <v>60</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.408966666666667</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0423342340046205</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>((12, 5, 64), (12, 64, 5))</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>((320, 64, 1), (320, 1, 64))</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>355.711</v>
+      </c>
+      <c r="G13" t="n">
+        <v>60</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5.928516666666667</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.03916063617124332</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>((1, 5, 3072), (1, 5, 3072))</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>((15360, 3072, 1), (15360, 3072, 1))</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>308.848</v>
+      </c>
+      <c r="G14" t="n">
+        <v>60</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.147466666666667</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.03400143419859424</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>((12, 5, 5), (), ())</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>((25, 5, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>('', '-1', 'False')</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>294.657</v>
+      </c>
+      <c r="G15" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.91095</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.03243913056472822</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>aten::sigmoid</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>((1, 5, 3072),)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>((15360, 3072, 1),)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>('',)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>292.09</v>
+      </c>
+      <c r="G16" t="n">
+        <v>60</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.868166666666667</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.03215652656020888</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>((1, 5, 768), ())</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>((3840, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>291.332</v>
+      </c>
+      <c r="G17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.855533333333333</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.03207307746187398</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>((1, 5, 3072), ())</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>((15360, 3072, 1), ())</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>291.329</v>
+      </c>
+      <c r="G18" t="n">
+        <v>60</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.855483333333334</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.03207274718839773</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>((1,), (5184, 1024), (1024, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>((1,), (1024, 1), (1, 1024), (), ())</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>69.666</v>
+      </c>
+      <c r="G19" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.6444</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.007669610665697256</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1024), ())</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>((5308416, 1024, 1), ())</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>67.949</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>9.706999999999999</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.00748058414611809</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>aten::div</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>((1, 768), (1, 1))</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>((768, 1), (1, 1))</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>49.504</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.9504</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.005449952722916158</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>aten::linalg_vector_norm</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>((1, 768), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>((768, 1), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>('', '2', '[-1]', 'True', '')</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.814</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.005299788382376855</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>46.297</v>
+      </c>
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.6297</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.00509689037679479</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>aten::argmax</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>((1, 5), (), ())</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>((5, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>('', '-1', 'False')</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4, 4&gt; &gt;(at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>37.76300000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7.552600000000001</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.004157372427995372</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>((1, 5184, 768), (1, 768, 1))</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>((3981312, 768, 1), (768, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bjlk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x16x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB1_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>37.081</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>9.270250000000001</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.00408229025772572</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>aten::index</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>((1, 5, 768), ())</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>((3840, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>void at::native::index_elementwise_kernel&lt;128, 4, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1}&gt;(long, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6.581999999999999</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.003623100034566312</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>aten::linalg_vector_norm</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>((1, 5184, 768), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>((3981312, 768, 1), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>('', '2.', '[-1]', 'True', '')</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>32.149</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6.4298</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.003539320662755162</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>((49408, 768), (), (5,))</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>((768, 1), (), (1,))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>('', '0', '')</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>31.828</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>6.3656</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.003503981400795399</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>((4,), (5184, 1024), (1024, 4), (), ())</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>((1,), (1024, 1), (1, 1024), (), ())</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>31.067</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6.2134</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.003420202028984249</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>((1, 1024), (1024, 768))</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>((1024, 1), (1, 1024))</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>30.145</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>6.029</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.00331869798061384</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>aten::div</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>((1, 5184, 768), (1, 5184, 1))</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>((3981312, 768, 1), (5184, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>28.583</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>9.527666666666667</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.003146735590641413</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>((16, 768), (), (5,))</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>((768, 1), (), (1,))</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>('', '0', '')</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5.612</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.003089157914613513</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>((1, 1, 5, 5), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>((25, 25, 5, 1), (25, 25, 5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>26.455</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5.290999999999999</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.0029124616048147</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>((1, 5), (1, 5), ())</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>((5, 1), (5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>25.814</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>5.1628</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.002841893172053928</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>aten::sub</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>((), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>((), (25, 25, 5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>25.655</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5.131</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.002824388677812177</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>((1, 1024), (), (1024,), (1024,), ())</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>((5309440, 1), (), (1,), (1,), ())</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>('', '[1024]', '', '', '1.0000000000000001e-05')</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>25.093</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>5.0186</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.002762517446592904</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>aten::fill_</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>((5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>((5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>('', '-3.3895313892515355e+38')</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4.938</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.002718150709615383</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>((5, 5), (5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>((5, 1), (5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4.842000000000001</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.002665306953413869</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>((5,), (), ())</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>((1,), (), ())</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>24.131</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4.8262</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.00265660975187237</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>aten::exp</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>((),)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>((),)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>('',)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>24.051</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4.8102</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.002647802459172118</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (1, 5184, 1))</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (5184, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>24.011</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4.802200000000001</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.002643398812821991</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>aten::div</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>((1, 1, 768), (1, 1, 1))</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>((768, 768, 1), (1, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>23.931</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.7862</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.002634591520121739</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>aten::lt</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>((5,), (5, 1))</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>((1,), (1, 1))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>23.769</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4.7538</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.002616756752403727</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>((1, 1, 5, 5), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>((25, 25, 5, 1), (5, 5, 0, 1), ())</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2})</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>23.769</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4.7538</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.002616756752403727</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>aten::gt</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>((1, 1), ())</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>((5, 5), ())</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>('', '0')</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>23.568</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4.7136</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.002594628429494344</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (1, 5184, 1), ())</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (5184, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>23.369</v>
+      </c>
+      <c r="G46" t="n">
+        <v>5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4.6738</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.002572720288902466</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>aten::masked_fill_</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>((5, 5), (5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>((5, 1), (5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>('', '', '0')</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.002559619441010841</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (1, 5184, 1), ())</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (5184, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>23.167</v>
+      </c>
+      <c r="G48" t="n">
+        <v>5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4.6334</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.002550481874834329</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>aten::arange</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>((), (), (), (0,))</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>((), (), (), (1,))</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>('0', '5', '1', '')</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>23.088</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4.6176</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.00254178467329283</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>aten::add_</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>((1, 5184, 4), (5184, 4), ())</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>((20736, 4, 1), (4, 1), ())</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>22.928</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4.585599999999999</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.002524170087892325</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>aten::fill_</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>((), ())</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>((), ())</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>('', '-3.3895313892515355e+38')</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>22.646</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4.5292</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.002493124381123936</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>22.487</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4.497400000000001</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.002475619886882184</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>aten::arange</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>((), (), (), (0,))</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>((), (), (), (1,))</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>('0', '1', '1', '')</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>22.486</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4.497199999999999</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.00247550979572343</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>((1, 768), (768, 768))</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>((768, 1), (1, 768))</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>22.367</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" t="n">
+        <v>5.59175</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.002462408947831805</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>aten::masked_fill_</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>((1, 1, 5, 5), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>((25, 25, 5, 1), (25, 25, 5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>('', '', '-3.3895313892515355e+38')</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>22.366</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4.4732</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.002462298856673052</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>aten::elu</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>('', '1.', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>21.964</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>4.392799999999999</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.002418042210854284</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>((1, 1), ())</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>((1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>21.885</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4.377</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.002409345009312785</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>aten::eq</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>('', '0')</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>21.845</v>
+      </c>
+      <c r="G58" t="n">
+        <v>5</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4.369</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.002404941362962658</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>aten::linalg_vector_norm</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>((1, 1, 768), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>((768, 768, 1), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>('', '2.', '[-1]', 'True', '')</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>21.323</v>
+      </c>
+      <c r="G59" t="n">
+        <v>5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4.2646</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.002347473778093512</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>aten::where</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), (), (1, 5184, 1))</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), (), (5184, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>('', '', '')</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>19.802</v>
+      </c>
+      <c r="G60" t="n">
+        <v>4</v>
+      </c>
+      <c r="H60" t="n">
+        <v>4.9505</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.002180025125629964</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>aten::sigmoid</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>((1, 5184, 4),)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>((20736, 4, 1),)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>('',)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>3.198</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.001760357628462939</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -21130,7 +27873,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>aten::linalg_vector_norm</t>
+          <t>aten::linalg_norm</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -21174,28 +27917,46 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>4583</v>
+        <v>4582</v>
       </c>
       <c r="K51" t="n">
         <v>10</v>
       </c>
       <c r="L51" t="n">
-        <v>137.38</v>
+        <v>175.202</v>
       </c>
       <c r="M51" t="n">
-        <v>13.738</v>
+        <v>17.5202</v>
       </c>
       <c r="N51" t="n">
-        <v>7.114041404933704</v>
-      </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+        <v>10.7939256662666</v>
+      </c>
+      <c r="O51" t="n">
+        <v>7.68e-07</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.0029296875</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="S51" t="n">
+        <v>0.000653363847306895</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.0001044819361624662</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.0001633409618267238</v>
+      </c>
+      <c r="V51" t="n">
+        <v>2.612048404061655e-05</v>
+      </c>
       <c r="W51" t="n">
         <v>4.814013671875</v>
       </c>
@@ -21206,20 +27967,32 @@
         <v>48.14013671875</v>
       </c>
       <c r="Z51" t="n">
-        <v>13.2545</v>
+        <v>15.724</v>
       </c>
       <c r="AA51" t="n">
-        <v>6.755</v>
+        <v>7.733</v>
       </c>
       <c r="AB51" t="n">
-        <v>21.943</v>
-      </c>
-      <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="inlineStr"/>
+        <v>38.577</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0.0006649950204568901</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.0005178579306938843</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0.0007983068138561096</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0.0001662487551142225</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0.0001294644826734711</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0.0001995767034640274</v>
+      </c>
       <c r="AI51" t="n">
         <v>4.630126953125</v>
       </c>
@@ -21239,9 +28012,13 @@
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(4.81)}]</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>{'num_input_elems': 768, 'num_output_elems': 768, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'norm'}</t>
+        </is>
+      </c>
       <c r="AO51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP51" t="n">
         <v>0.01450794100702804</v>
@@ -21809,7 +28586,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>aten::linalg_vector_norm</t>
+          <t>aten::linalg_norm</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -21839,7 +28616,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'Scalar', 'ScalarList', 'Scalar', '')</t>
+          <t>('c10::BFloat16', '', 'ScalarList', 'Scalar', '')</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -21849,32 +28626,50 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>('', '2.', '[-1]', 'True', '')</t>
+          <t>('', '', '[-1]', 'True', '')</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>4655</v>
+        <v>4654</v>
       </c>
       <c r="K56" t="n">
         <v>5</v>
       </c>
       <c r="L56" t="n">
-        <v>58.592</v>
+        <v>66.54900000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>11.7184</v>
+        <v>13.3098</v>
       </c>
       <c r="N56" t="n">
-        <v>1.607062631013489</v>
-      </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
+        <v>1.75570134134482</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.003981312</v>
+      </c>
+      <c r="P56" t="n">
+        <v>7.593751907348633</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.4999998744132903</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="S56" t="n">
+        <v>1.241544667684163</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.07091261215372953</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0.6207721779205716</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0.03545629717118316</v>
+      </c>
       <c r="W56" t="n">
         <v>6.4298828125</v>
       </c>
@@ -21885,20 +28680,32 @@
         <v>32.1494140625</v>
       </c>
       <c r="Z56" t="n">
-        <v>11.248</v>
+        <v>12.528</v>
       </c>
       <c r="AA56" t="n">
-        <v>10.682</v>
+        <v>12.119</v>
       </c>
       <c r="AB56" t="n">
-        <v>14.532</v>
-      </c>
-      <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr"/>
-      <c r="AE56" t="inlineStr"/>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="inlineStr"/>
+        <v>16.39</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.241432555420219</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.15483733786559</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.351409467804757</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0.6207161218026797</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0.5774185239005736</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0.6757045641833098</v>
+      </c>
       <c r="AI56" t="n">
         <v>6.4140625</v>
       </c>
@@ -21918,9 +28725,13 @@
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(6.43)}]</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr">
+        <is>
+          <t>{'num_input_elems': 3981312, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'norm'}</t>
+        </is>
+      </c>
       <c r="AO56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP56" t="n">
         <v>0.009688834191607149</v>
@@ -26911,7 +33722,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>aten::linalg_vector_norm</t>
+          <t>aten::linalg_norm</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -26941,7 +33752,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'Scalar', 'ScalarList', 'Scalar', '')</t>
+          <t>('c10::BFloat16', '', 'ScalarList', 'Scalar', '')</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -26951,32 +33762,50 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>('', '2.', '[-1]', 'True', '')</t>
+          <t>('', '', '[-1]', 'True', '')</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>4659</v>
+        <v>4658</v>
       </c>
       <c r="K92" t="n">
         <v>5</v>
       </c>
       <c r="L92" t="n">
-        <v>41.349</v>
+        <v>47.33</v>
       </c>
       <c r="M92" t="n">
-        <v>8.2698</v>
+        <v>9.465999999999999</v>
       </c>
       <c r="N92" t="n">
-        <v>0.637994670824138</v>
-      </c>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
+        <v>0.4908217599088287</v>
+      </c>
+      <c r="O92" t="n">
+        <v>7.68e-07</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.001466751098632812</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0.4993498049414825</v>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="S92" t="n">
+        <v>0.0003613396923387094</v>
+      </c>
+      <c r="T92" t="n">
+        <v>1.779948916443615e-05</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0.0001804349048869498</v>
+      </c>
+      <c r="V92" t="n">
+        <v>8.888171442319212e-06</v>
+      </c>
       <c r="W92" t="n">
         <v>4.26455078125</v>
       </c>
@@ -26987,20 +33816,32 @@
         <v>21.32275390625</v>
       </c>
       <c r="Z92" t="n">
-        <v>8.25</v>
+        <v>9.458</v>
       </c>
       <c r="AA92" t="n">
-        <v>7.348</v>
+        <v>8.738</v>
       </c>
       <c r="AB92" t="n">
-        <v>8.967000000000001</v>
-      </c>
-      <c r="AC92" t="inlineStr"/>
-      <c r="AD92" t="inlineStr"/>
-      <c r="AE92" t="inlineStr"/>
-      <c r="AF92" t="inlineStr"/>
-      <c r="AG92" t="inlineStr"/>
-      <c r="AH92" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>0.0003620487356321839</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>0.0003396036657681941</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>0.0003876229387152351</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>0.0001807889655172414</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>0.0001695810242587601</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>0.0001935594388382968</v>
+      </c>
       <c r="AI92" t="n">
         <v>4.248046875</v>
       </c>
@@ -27020,9 +33861,13 @@
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(4.26)}]</t>
         </is>
       </c>
-      <c r="AN92" t="inlineStr"/>
+      <c r="AN92" t="inlineStr">
+        <is>
+          <t>{'num_input_elems': 768, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'norm'}</t>
+        </is>
+      </c>
       <c r="AO92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP92" t="n">
         <v>0.006426015314135241</v>

--- a/tests/traces/mi300/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
+++ b/tests/traces/mi300/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
@@ -2069,7 +2069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2284,34 +2284,34 @@
         <v>7.68e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0029296875</v>
+        <v>0.001466751098632812</v>
       </c>
       <c r="H2" t="n">
-        <v>0.25</v>
+        <v>0.4993498049414825</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000653363847306895</v>
+        <v>0.0003385180912739285</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0006649950204568901</v>
+        <v>0.0003520143048725973</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001044819361624662</v>
+        <v>4.613609711649522e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005178579306938843</v>
+        <v>0.0002592661124372377</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007983068138561096</v>
+        <v>0.000399673137926659</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0001633409618267238</v>
+        <v>0.0001690389428467991</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0001662487551142225</v>
+        <v>0.000175778274474743</v>
       </c>
       <c r="P2" t="n">
-        <v>2.612048404061655e-05</v>
+        <v>2.303805109588318e-05</v>
       </c>
       <c r="Q2" t="n">
         <v>0.0001294644826734711</v>
@@ -2341,12 +2341,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 10, 'total_duration_us': np.float64(48.14), 'mean_duration_us': np.float64(4.814), 'median_duration_us': np.float64(4.63), 'std_dev_duration_us': np.float64(0.7427319839619135), 'min_duration_us': np.float64(3.848), 'max_duration_us': np.float64(5.932)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 15, 'total_duration_us': np.float64(69.463), 'mean_duration_us': np.float64(4.630866666666666), 'median_duration_us': np.float64(4.369), 'std_dev_duration_us': np.float64(0.6680712403795139), 'min_duration_us': np.float64(3.848), 'max_duration_us': np.float64(5.932)}]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(4.81)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(4.63)}]</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -2370,13 +2370,13 @@
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>4.814013671875</v>
+        <v>4.630859375</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.630126953125</v>
+        <v>4.369140625</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.7829011025606529</v>
+        <v>0.6915293684756548</v>
       </c>
       <c r="AF2" t="n">
         <v>3.84814453125</v>
@@ -2385,10 +2385,10 @@
         <v>5.93212890625</v>
       </c>
       <c r="AH2" t="n">
-        <v>48.14013671875</v>
+        <v>69.462890625</v>
       </c>
       <c r="AI2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AJ2" t="n">
         <v>4582</v>
@@ -2537,12 +2537,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>aten::linalg_norm</t>
+          <t>aten::max</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2552,53 +2552,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', None)</t>
+          <t>('float', None)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>norm</t>
+          <t>max</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7.68e-07</v>
+        <v>5.184e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001466751098632812</v>
+        <v>0.01977920532226562</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4993498049414825</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.0003613396923387094</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.0003620487356321839</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.779948916443615e-05</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.0003396036657681941</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.0003876229387152351</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.0001804349048869498</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.0001807889655172414</v>
-      </c>
-      <c r="P4" t="n">
-        <v>8.888171442319212e-06</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.0001695810242587601</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.0001935594388382968</v>
-      </c>
+        <v>0.2499517839922854</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>python3</t>
@@ -2616,62 +2596,58 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>vector_fp32</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(21.323), 'mean_duration_us': np.float64(4.2646), 'median_duration_us': np.float64(4.248), 'std_dev_duration_us': np.float64(0.1855506399881175), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(4.529)}]</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(4.26)}]</t>
-        </is>
-      </c>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[[1, 1, 768], [], [], [], []]</t>
+          <t>[[1, 5184, 1], [], []]</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', '', 'ScalarList', 'Scalar', '']</t>
+          <t>['float', 'Scalar', 'Scalar']</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>[[768, 768, 1], [], [], [], []]</t>
+          <t>[[5184, 1, 1], [], []]</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>['', '', '[-1]', 'True', '']</t>
+          <t>['', '-1', 'False']</t>
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>4.26455078125</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.248046875</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2074897726824681</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.9677734375</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.52880859375</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>21.32275390625</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4658</v>
+        <v>24159</v>
       </c>
     </row>
     <row r="5">
@@ -2682,17 +2658,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>('float', None)</t>
+          <t>('int', None)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2701,14 +2677,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.184e-06</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.03955078125</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.125</v>
-      </c>
+        <v>1e-09</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -2734,11 +2706,7 @@
           <t>thread 14646 (python3)</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>vector_fp32</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2747,22 +2715,22 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[[1, 5184, 1], [], []]</t>
+          <t>[[1], [1]]</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>['float', 'Scalar', 'Scalar']</t>
+          <t>['int', 'int']</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>[[5184, 1, 1], [], []]</t>
+          <t>[[2], [2]]</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>['', '-1', 'False']</t>
+          <t>['', '']</t>
         </is>
       </c>
       <c r="AC5" t="n">
@@ -2787,114 +2755,6 @@
         <v>5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24159</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>aten::max</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>('int', None)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1e-09</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>thread 14646 (python3)</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>[[1], [1]]</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>['int', 'int']</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>[[2], [2]]</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>['', '']</t>
-        </is>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ6" t="n">
         <v>24217</v>
       </c>
     </row>
@@ -27935,10 +27795,10 @@
         <v>7.68e-07</v>
       </c>
       <c r="P51" t="n">
-        <v>0.0029296875</v>
+        <v>0.001466751098632812</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.25</v>
+        <v>0.4993498049414825</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -27946,10 +27806,10 @@
         </is>
       </c>
       <c r="S51" t="n">
-        <v>0.000653363847306895</v>
+        <v>0.000327107290741538</v>
       </c>
       <c r="T51" t="n">
-        <v>0.0001044819361624662</v>
+        <v>5.230899017508888e-05</v>
       </c>
       <c r="U51" t="n">
         <v>0.0001633409618267238</v>
@@ -27976,13 +27836,13 @@
         <v>38.577</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.0006649950204568901</v>
+        <v>0.0003329304496948884</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.0005178579306938843</v>
+        <v>0.0002592661124372377</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.0007983068138561096</v>
+        <v>0.000399673137926659</v>
       </c>
       <c r="AF51" t="n">
         <v>0.0001662487551142225</v>
@@ -28014,7 +27874,7 @@
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>{'num_input_elems': 768, 'num_output_elems': 768, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'norm'}</t>
+          <t>{'num_input_elems': 768, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'norm'}</t>
         </is>
       </c>
       <c r="AO51" t="b">

--- a/tests/traces/mi300/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
+++ b/tests/traces/mi300/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2059,6 +2063,6605 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AJ5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_input_elems</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_output_elems</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>param: dtype_in_out</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>param: reduce_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GFLOPS_first</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Data Moved (MB)_first</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FLOPS/Byte_first</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_mean</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_median</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_std</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_min</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_max</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_mean</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_median</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_std</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_min</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_max</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Compute Spec</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details__summarize_kernel_stats</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_kernel_details</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Input Dims_first</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Input type_first</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Input Strides_first</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs_first</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>name_count</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>UID_first</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::linalg_norm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>norm</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>7.68e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001466751098632812</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4993498049414825</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0003385180912739285</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0003520143048725973</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.613609711649522e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0002592661124372377</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.000399673137926659</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0001690389428467991</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.000175778274474743</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.303805109588318e-05</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0001294644826734711</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0001995767034640274</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>thread 14646 (python3)</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 15, 'total_duration_us': np.float64(69.463), 'mean_duration_us': np.float64(4.630866666666666), 'median_duration_us': np.float64(4.369), 'std_dev_duration_us': np.float64(0.6680712403795139), 'min_duration_us': np.float64(3.848), 'max_duration_us': np.float64(5.932)}]</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(4.63)}]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>[[1, 768], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'Scalar', 'ScalarList', 'Scalar', '']</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>[[768, 1], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>['', '2', '[-1]', 'True', '']</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.630859375</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.369140625</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.6915293684756548</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3.84814453125</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>5.93212890625</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>69.462890625</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>4582</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::linalg_norm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3981312</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>norm</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.003981312</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.593751907348633</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4999998744132903</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.241544667684163</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.241432555420219</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.07091261215372953</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.15483733786559</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.351409467804757</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6207721779205716</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.6207161218026797</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.03545629717118316</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.5774185239005736</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.6757045641833098</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>thread 14646 (python3)</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(32.149), 'mean_duration_us': np.float64(6.4298), 'median_duration_us': np.float64(6.414), 'std_dev_duration_us': np.float64(0.32155770866206873), 'min_duration_us': np.float64(5.892), 'max_duration_us': np.float64(6.895)}]</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(6.43)}]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>[[1, 5184, 768], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', '', 'ScalarList', 'Scalar', '']</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>[[3981312, 768, 1], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>['', '', '[-1]', 'True', '']</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.4298828125</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>6.4140625</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.3594968174672817</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>5.89208984375</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>6.89501953125</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>32.1494140625</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>4654</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aten::max</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>5.184e-06</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01977920532226562</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2499517839922854</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>thread 14646 (python3)</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>vector_fp32</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>[[1, 5184, 1], [], []]</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>['float', 'Scalar', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>[[5184, 1, 1], [], []]</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>['', '-1', 'False']</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>24159</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aten::max</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('int', None)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1e-09</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>thread 14646 (python3)</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>[[1], [1]]</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>['int', 'int']</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>[[2], [2]]</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>['', '']</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>24217</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parent op category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Parent cpu_op</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel stream</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_sum</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_count</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_mean</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_min</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_max</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Percent of kernels time (%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Percent of total time (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::cunn_SoftMaxForwardReg&lt;c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue, long, 6&gt;(c10::BFloat16*, c10::BFloat16 const*, long)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>153698.475</v>
+      </c>
+      <c r="F2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1280.820625</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1151.523</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1475.988</v>
+      </c>
+      <c r="J2" t="n">
+        <v>46.94231752031421</v>
+      </c>
+      <c r="K2" t="n">
+        <v>16.92084321134274</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x288x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA32_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_9_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>55056.329</v>
+      </c>
+      <c r="F3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G3" t="n">
+        <v>458.8027416666666</v>
+      </c>
+      <c r="H3" t="n">
+        <v>399.316</v>
+      </c>
+      <c r="I3" t="n">
+        <v>559.804</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16.81520703065455</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.0612150563049</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB256_LBSPPM0_LPA4_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>40460.247</v>
+      </c>
+      <c r="F4" t="n">
+        <v>120</v>
+      </c>
+      <c r="G4" t="n">
+        <v>337.1687250000001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>322.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>377.545</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12.35729737477448</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.454315475668841</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_5_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>15828.359</v>
+      </c>
+      <c r="F5" t="n">
+        <v>500</v>
+      </c>
+      <c r="G5" t="n">
+        <v>31.656718</v>
+      </c>
+      <c r="H5" t="n">
+        <v>28.705</v>
+      </c>
+      <c r="I5" t="n">
+        <v>38.488</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.834269526770016</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.742562383470921</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT160x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT5_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12190.583</v>
+      </c>
+      <c r="F6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G6" t="n">
+        <v>101.5881916666667</v>
+      </c>
+      <c r="H6" t="n">
+        <v>96.98099999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>110.813</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.723226388184688</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.342075408346506</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x288x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_9_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>11587.363</v>
+      </c>
+      <c r="F7" t="n">
+        <v>120</v>
+      </c>
+      <c r="G7" t="n">
+        <v>96.56135833333333</v>
+      </c>
+      <c r="H7" t="n">
+        <v>93.81399999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>105.121</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.538991998255939</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.275666219563428</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9666.441000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>720</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13.4256125</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I8" t="n">
+        <v>23.693</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.952307384399121</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.064189690709001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NORM_fwd</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5852.737</v>
+      </c>
+      <c r="F9" t="n">
+        <v>385</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15.20191428571429</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.409</v>
+      </c>
+      <c r="I9" t="n">
+        <v>28.384</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.787532625921573</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.6443345982074608</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4818.482</v>
+      </c>
+      <c r="F10" t="n">
+        <v>190</v>
+      </c>
+      <c r="G10" t="n">
+        <v>25.36043157894737</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.848</v>
+      </c>
+      <c r="I10" t="n">
+        <v>50.435</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.471652285488966</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5304722668112171</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4459.415</v>
+      </c>
+      <c r="F11" t="n">
+        <v>360</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12.38726388888889</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.209</v>
+      </c>
+      <c r="I11" t="n">
+        <v>33.957</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.361986674785498</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.4909421647111982</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>aten::sigmoid</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3837.21</v>
+      </c>
+      <c r="F12" t="n">
+        <v>185</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20.74167567567568</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="I12" t="n">
+        <v>33.035</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.171953919595656</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.4224428952791917</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3045.33</v>
+      </c>
+      <c r="F13" t="n">
+        <v>375</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8.12088</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.048</v>
+      </c>
+      <c r="I13" t="n">
+        <v>13.429</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9300993247599787</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.3352639084857438</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2164.27</v>
+      </c>
+      <c r="F14" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7.214233333333333</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.812</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6610075313999727</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.2382669921546895</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>555.234</v>
+      </c>
+      <c r="F15" t="n">
+        <v>120</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.62695</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.008</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.612</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.1695785903280702</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.06112635443914895</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>419.266</v>
+      </c>
+      <c r="F16" t="n">
+        <v>60</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6.987766666666667</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5.973</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8.657999999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1280514832529865</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.04615747976580005</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>384.538</v>
+      </c>
+      <c r="F17" t="n">
+        <v>60</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6.408966666666667</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.091</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8.659000000000001</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.1174449186605566</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0423342340046205</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>355.711</v>
+      </c>
+      <c r="F18" t="n">
+        <v>60</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.928516666666667</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.609</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7.857</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.108640627094501</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.03916063617124332</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>aten::miopen_convolution</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Cijk_Ailk_Bljk_BBS_BH_MT64x64x64_MI16x16x16x1_SN_1LDSB0_APM1_ABV0_ACED0_AF0EM1_AF1EM1_AMAS0_ASE_ASGT_ASLT_ASM_ASAE01_ASCE01_ASEM1_AAC0_BL1_BS1_CLR1_DTLA0_DTLB0_DTVA0_DTVB0_DVO0_ETSP_EPS1_ELFLR0_EMLL0_FSSC10_FL0_GLVWA2_GLVWB8_GRCGA1_GRCGB1_GRPM1_GRVWn1_GSU1_GSUASB_GLS0_ISA942_IU1_K1_KLA_LBSPPA1024_LBSPPB128_LPA16_LPB16_LDL1_LRVW8_LWPMn1_LDW0_FMA_MIAV0_MDA2_MO40_MMFSC_MKFGSU256_NTA0_NTB0_NTC0_NTD0_NEPBS0_NLCA1_NLCB1_ONLL1_OPLV0_PK0_PAP0_PGR1_PLR5_PKA0_SIA3_SLW1_SS0_SU16_SUM0_SUS512_SCIUI1_SPO0_SRVW0_SSO0_SVW4_SNLL0_TSGRA0_TSGRB0_TT1_64_TLDS1_UMLDSA0_UMLDSB1_U64SL1_USFGROn1_VAW1_VSn1_VW1_VWB1_VFLRP1_WSGRA0_WSGRB0_WS64_WG64_4_1_WGMn16</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>298.641</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>59.7282</v>
+      </c>
+      <c r="H19" t="n">
+        <v>56.328</v>
+      </c>
+      <c r="I19" t="n">
+        <v>60.899</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.09121040821377152</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.03287773374120079</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>294.657</v>
+      </c>
+      <c r="F20" t="n">
+        <v>60</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4.91095</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.249</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.093</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.08999362195092191</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.03243913056472822</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>289.404</v>
+      </c>
+      <c r="F21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14.4702</v>
+      </c>
+      <c r="H21" t="n">
+        <v>9.461</v>
+      </c>
+      <c r="I21" t="n">
+        <v>20.085</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.08838925994320382</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0318608217077979</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA1_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB4_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS0_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_1</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>282.956</v>
+      </c>
+      <c r="F22" t="n">
+        <v>15</v>
+      </c>
+      <c r="G22" t="n">
+        <v>18.86373333333334</v>
+      </c>
+      <c r="H22" t="n">
+        <v>15.234</v>
+      </c>
+      <c r="I22" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.08641992314027858</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.03115095391615757</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>aten::miopen_convolution</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Im2d2Col_v2</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>219.258</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>43.8516</v>
+      </c>
+      <c r="H23" t="n">
+        <v>40.372</v>
+      </c>
+      <c r="I23" t="n">
+        <v>45.063</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.06696539217366375</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.02413836728589914</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>aten::cat</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>149.136</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>29.8272</v>
+      </c>
+      <c r="H24" t="n">
+        <v>29.306</v>
+      </c>
+      <c r="I24" t="n">
+        <v>30.789</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.04554885444185168</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.01641855505181044</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x64x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB4_WSGRA0_WSGRB0_WS64_WG64_4_1</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>136.148</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>27.2296</v>
+      </c>
+      <c r="H25" t="n">
+        <v>26.139</v>
+      </c>
+      <c r="I25" t="n">
+        <v>28.104</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.04158208235804382</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.01498869108192447</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>aten::div</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>122.944</v>
+      </c>
+      <c r="F26" t="n">
+        <v>20</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6.1472</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.088</v>
+      </c>
+      <c r="I26" t="n">
+        <v>10.544</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.03754933993468387</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.01353504742174782</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>reduce</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>aten::linalg_vector_norm</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>101.612</v>
+      </c>
+      <c r="F27" t="n">
+        <v>20</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.0806</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.848</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6.895</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.031034158067438</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.01118658282322553</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>89.11500000000001</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8.9115</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5.411</v>
+      </c>
+      <c r="I28" t="n">
+        <v>36.603</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.02721734633881566</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.009810773612287358</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>83.667</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>16.7334</v>
+      </c>
+      <c r="H29" t="n">
+        <v>15.595</v>
+      </c>
+      <c r="I29" t="n">
+        <v>18.161</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.02555342777455748</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.009210996979400171</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>69.666</v>
+      </c>
+      <c r="F30" t="n">
+        <v>15</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4.6444</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.248</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.02127726701497988</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.007669610665697256</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>68.78400000000001</v>
+      </c>
+      <c r="F31" t="n">
+        <v>15</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4.5856</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.048</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5.171</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.02100788812847553</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.007572510263676975</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA1_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB4_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS0_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_1</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>60.253</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>12.0506</v>
+      </c>
+      <c r="H32" t="n">
+        <v>11.345</v>
+      </c>
+      <c r="I32" t="n">
+        <v>12.628</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.01840236513440678</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.006633322588353814</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>59.888</v>
+      </c>
+      <c r="F33" t="n">
+        <v>10</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5.988799999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6.574</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.0182908874772933</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.006593139315408912</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>59.051</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>11.8102</v>
+      </c>
+      <c r="H34" t="n">
+        <v>11.345</v>
+      </c>
+      <c r="I34" t="n">
+        <v>12.387</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.01803525241152897</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.006500993015532522</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>aten::where</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>55.763</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>11.1526</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="I35" t="n">
+        <v>35.961</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.01703103724279165</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.00613901328555215</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bjlk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x16x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB1_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>47.143</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>9.428599999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10.062</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.01439833202548153</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.00519002749709996</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>aten::arange</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>45.574</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4.557399999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="I37" t="n">
+        <v>5.171</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.0139191308090129</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.00501729446901626</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>reduce</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>aten::argmax</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4, 4&gt; &gt;(at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>37.76300000000001</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>7.552600000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>7.256</v>
+      </c>
+      <c r="I38" t="n">
+        <v>8.057</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.01153350894678445</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.004157372427995372</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>aten::index</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>void at::native::index_elementwise_kernel&lt;128, 4, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1}&gt;(long, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6.581999999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>6.253</v>
+      </c>
+      <c r="I39" t="n">
+        <v>6.975</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.01005131423453317</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.003623100034566312</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>31.067</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>6.2134</v>
+      </c>
+      <c r="H40" t="n">
+        <v>6.013</v>
+      </c>
+      <c r="I40" t="n">
+        <v>6.775</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.009488428420669765</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.003420202028984249</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>26.455</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5.290999999999999</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I41" t="n">
+        <v>5.732</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.008079839503937253</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.0029124616048147</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>25.814</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5.1628</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5.451</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.007884066412951665</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.002841893172053928</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>aten::sub</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>25.655</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5.131</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5.652</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.007835504913003602</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.002824388677812177</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>aten::fill_</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>4.938</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4.449</v>
+      </c>
+      <c r="I44" t="n">
+        <v>5.251</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.00754077631268988</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.002718150709615383</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4.842000000000001</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4.489</v>
+      </c>
+      <c r="I45" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.007394175558129689</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.002665306953413869</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>24.131</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4.8262</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="I46" t="n">
+        <v>5.251</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.00737004751727499</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.00265660975187237</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>aten::exp</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>24.051</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>4.8102</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5.211</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.007345614058181626</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.002647802459172118</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2})</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>23.769</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4.7538</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4.529</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5.051</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.007259486114877511</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.002616756752403727</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>aten::lt</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>23.769</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.7538</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4.409</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.007259486114877511</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.002616756752403727</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>aten::gt</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>23.568</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4.7136</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4.329</v>
+      </c>
+      <c r="I50" t="n">
+        <v>5.251</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.007198097048905431</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.002594628429494344</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>23.369</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4.6738</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4.449</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.007137318819410684</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.002572720288902466</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>aten::masked_fill_</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4.489</v>
+      </c>
+      <c r="I52" t="n">
+        <v>4.851</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.007100974049009304</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.002559619441010841</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>aten::add_</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>22.928</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4.585599999999999</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4.169</v>
+      </c>
+      <c r="I53" t="n">
+        <v>5.291</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.007002629376158508</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.002524170087892325</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>aten::fill_</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>22.646</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4.5292</v>
+      </c>
+      <c r="H54" t="n">
+        <v>4.088</v>
+      </c>
+      <c r="I54" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.006916501432854396</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.002493124381123936</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>aten::masked_fill_</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>22.366</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>4.4732</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4.289</v>
+      </c>
+      <c r="I55" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.006830984326027616</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.002462298856673052</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>aten::elu</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>21.964</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>4.392799999999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="I56" t="n">
+        <v>4.689</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.006708206194083456</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.002418042210854284</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>aten::eq</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>21.845</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>4.369</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3.888</v>
+      </c>
+      <c r="I57" t="n">
+        <v>5.091</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.006671861423682076</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.002404941362962658</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>bin_start</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>bin_end</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2.83717</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.83717</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2.90934</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2.90934</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2.98151</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2.98151</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3.05368</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3.05368</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3.12585</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3.12585</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3.19802</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3.19802</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3.27019</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3.27019</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3.34236</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3.34236</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3.41453</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3.41453</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3.4867</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3.4867</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3.55887</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3.55887</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3.63104</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3.63104</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3.70321</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3.70321</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3.77538</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3.77538</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3.84755</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3.84755</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3.91972</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3.91972</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3.99189</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3.99189</v>
+      </c>
+      <c r="B19" t="n">
+        <v>4.06406</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4.06406</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4.136229999999999</v>
+      </c>
+      <c r="C20" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4.136229999999999</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4.208399999999999</v>
+      </c>
+      <c r="C21" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4.208399999999999</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4.28057</v>
+      </c>
+      <c r="C22" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4.28057</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4.35274</v>
+      </c>
+      <c r="C23" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.35274</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4.42491</v>
+      </c>
+      <c r="C24" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.42491</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4.49708</v>
+      </c>
+      <c r="C25" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4.49708</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4.56925</v>
+      </c>
+      <c r="C26" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>4.56925</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4.64142</v>
+      </c>
+      <c r="C27" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>4.64142</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4.71359</v>
+      </c>
+      <c r="C28" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>4.71359</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4.78576</v>
+      </c>
+      <c r="C29" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>4.78576</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4.85793</v>
+      </c>
+      <c r="C30" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>4.85793</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4.930099999999999</v>
+      </c>
+      <c r="C31" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>4.930099999999999</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5.002269999999999</v>
+      </c>
+      <c r="C32" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>5.002269999999999</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5.074439999999999</v>
+      </c>
+      <c r="C33" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>5.074439999999999</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5.146609999999999</v>
+      </c>
+      <c r="C34" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>5.146609999999999</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5.21878</v>
+      </c>
+      <c r="C35" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5.21878</v>
+      </c>
+      <c r="B36" t="n">
+        <v>5.29095</v>
+      </c>
+      <c r="C36" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>5.29095</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5.363119999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5.363119999999999</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5.43529</v>
+      </c>
+      <c r="C38" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>5.43529</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5.50746</v>
+      </c>
+      <c r="C39" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>5.50746</v>
+      </c>
+      <c r="B40" t="n">
+        <v>5.57963</v>
+      </c>
+      <c r="C40" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>5.57963</v>
+      </c>
+      <c r="B41" t="n">
+        <v>5.6518</v>
+      </c>
+      <c r="C41" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5.6518</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5.72397</v>
+      </c>
+      <c r="C42" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5.72397</v>
+      </c>
+      <c r="B43" t="n">
+        <v>5.796139999999999</v>
+      </c>
+      <c r="C43" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>5.796139999999999</v>
+      </c>
+      <c r="B44" t="n">
+        <v>5.868309999999999</v>
+      </c>
+      <c r="C44" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>5.868309999999999</v>
+      </c>
+      <c r="B45" t="n">
+        <v>5.940479999999999</v>
+      </c>
+      <c r="C45" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5.940479999999999</v>
+      </c>
+      <c r="B46" t="n">
+        <v>6.012649999999999</v>
+      </c>
+      <c r="C46" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>6.012649999999999</v>
+      </c>
+      <c r="B47" t="n">
+        <v>6.084819999999999</v>
+      </c>
+      <c r="C47" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>6.084819999999999</v>
+      </c>
+      <c r="B48" t="n">
+        <v>6.15699</v>
+      </c>
+      <c r="C48" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>6.15699</v>
+      </c>
+      <c r="B49" t="n">
+        <v>6.229159999999999</v>
+      </c>
+      <c r="C49" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>6.229159999999999</v>
+      </c>
+      <c r="B50" t="n">
+        <v>6.301329999999999</v>
+      </c>
+      <c r="C50" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>6.301329999999999</v>
+      </c>
+      <c r="B51" t="n">
+        <v>6.3735</v>
+      </c>
+      <c r="C51" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>6.3735</v>
+      </c>
+      <c r="B52" t="n">
+        <v>6.44567</v>
+      </c>
+      <c r="C52" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>6.44567</v>
+      </c>
+      <c r="B53" t="n">
+        <v>6.51784</v>
+      </c>
+      <c r="C53" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>6.51784</v>
+      </c>
+      <c r="B54" t="n">
+        <v>6.590009999999999</v>
+      </c>
+      <c r="C54" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>6.590009999999999</v>
+      </c>
+      <c r="B55" t="n">
+        <v>6.662179999999999</v>
+      </c>
+      <c r="C55" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>6.662179999999999</v>
+      </c>
+      <c r="B56" t="n">
+        <v>6.734349999999999</v>
+      </c>
+      <c r="C56" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>6.734349999999999</v>
+      </c>
+      <c r="B57" t="n">
+        <v>6.806519999999999</v>
+      </c>
+      <c r="C57" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>6.806519999999999</v>
+      </c>
+      <c r="B58" t="n">
+        <v>6.878689999999999</v>
+      </c>
+      <c r="C58" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>6.878689999999999</v>
+      </c>
+      <c r="B59" t="n">
+        <v>6.950859999999999</v>
+      </c>
+      <c r="C59" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>6.950859999999999</v>
+      </c>
+      <c r="B60" t="n">
+        <v>7.023029999999999</v>
+      </c>
+      <c r="C60" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>7.023029999999999</v>
+      </c>
+      <c r="B61" t="n">
+        <v>7.095199999999998</v>
+      </c>
+      <c r="C61" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>7.095199999999998</v>
+      </c>
+      <c r="B62" t="n">
+        <v>7.16737</v>
+      </c>
+      <c r="C62" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>7.16737</v>
+      </c>
+      <c r="B63" t="n">
+        <v>7.23954</v>
+      </c>
+      <c r="C63" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>7.23954</v>
+      </c>
+      <c r="B64" t="n">
+        <v>7.31171</v>
+      </c>
+      <c r="C64" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>7.31171</v>
+      </c>
+      <c r="B65" t="n">
+        <v>7.38388</v>
+      </c>
+      <c r="C65" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>7.38388</v>
+      </c>
+      <c r="B66" t="n">
+        <v>7.456049999999999</v>
+      </c>
+      <c r="C66" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>7.456049999999999</v>
+      </c>
+      <c r="B67" t="n">
+        <v>7.528219999999999</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>7.528219999999999</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7.600389999999999</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>7.600389999999999</v>
+      </c>
+      <c r="B69" t="n">
+        <v>7.672559999999999</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>7.672559999999999</v>
+      </c>
+      <c r="B70" t="n">
+        <v>7.744729999999999</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>7.744729999999999</v>
+      </c>
+      <c r="B71" t="n">
+        <v>7.816899999999999</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>7.816899999999999</v>
+      </c>
+      <c r="B72" t="n">
+        <v>7.889069999999998</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>7.889069999999998</v>
+      </c>
+      <c r="B73" t="n">
+        <v>7.961239999999998</v>
+      </c>
+      <c r="C73" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>7.961239999999998</v>
+      </c>
+      <c r="B74" t="n">
+        <v>8.033409999999998</v>
+      </c>
+      <c r="C74" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>8.033409999999998</v>
+      </c>
+      <c r="B75" t="n">
+        <v>8.10558</v>
+      </c>
+      <c r="C75" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>8.10558</v>
+      </c>
+      <c r="B76" t="n">
+        <v>8.17775</v>
+      </c>
+      <c r="C76" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>8.17775</v>
+      </c>
+      <c r="B77" t="n">
+        <v>8.249919999999999</v>
+      </c>
+      <c r="C77" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>8.249919999999999</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8.322089999999999</v>
+      </c>
+      <c r="C78" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>8.322089999999999</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8.394259999999999</v>
+      </c>
+      <c r="C79" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>8.394259999999999</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8.466429999999999</v>
+      </c>
+      <c r="C80" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>8.466429999999999</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8.538599999999999</v>
+      </c>
+      <c r="C81" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>8.538599999999999</v>
+      </c>
+      <c r="B82" t="n">
+        <v>8.610769999999999</v>
+      </c>
+      <c r="C82" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>8.610769999999999</v>
+      </c>
+      <c r="B83" t="n">
+        <v>8.682939999999999</v>
+      </c>
+      <c r="C83" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>8.682939999999999</v>
+      </c>
+      <c r="B84" t="n">
+        <v>8.755109999999998</v>
+      </c>
+      <c r="C84" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>8.755109999999998</v>
+      </c>
+      <c r="B85" t="n">
+        <v>8.827279999999998</v>
+      </c>
+      <c r="C85" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>8.827279999999998</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8.899449999999998</v>
+      </c>
+      <c r="C86" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>8.899449999999998</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8.971619999999998</v>
+      </c>
+      <c r="C87" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>8.971619999999998</v>
+      </c>
+      <c r="B88" t="n">
+        <v>9.04379</v>
+      </c>
+      <c r="C88" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>9.04379</v>
+      </c>
+      <c r="B89" t="n">
+        <v>9.115959999999999</v>
+      </c>
+      <c r="C89" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>9.115959999999999</v>
+      </c>
+      <c r="B90" t="n">
+        <v>9.188129999999999</v>
+      </c>
+      <c r="C90" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>9.188129999999999</v>
+      </c>
+      <c r="B91" t="n">
+        <v>9.260299999999999</v>
+      </c>
+      <c r="C91" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>9.260299999999999</v>
+      </c>
+      <c r="B92" t="n">
+        <v>9.332469999999999</v>
+      </c>
+      <c r="C92" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>9.332469999999999</v>
+      </c>
+      <c r="B93" t="n">
+        <v>9.404639999999999</v>
+      </c>
+      <c r="C93" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>9.404639999999999</v>
+      </c>
+      <c r="B94" t="n">
+        <v>9.476809999999999</v>
+      </c>
+      <c r="C94" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>9.476809999999999</v>
+      </c>
+      <c r="B95" t="n">
+        <v>9.548979999999998</v>
+      </c>
+      <c r="C95" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>9.548979999999998</v>
+      </c>
+      <c r="B96" t="n">
+        <v>9.621149999999998</v>
+      </c>
+      <c r="C96" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>9.621149999999998</v>
+      </c>
+      <c r="B97" t="n">
+        <v>9.693319999999998</v>
+      </c>
+      <c r="C97" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>9.693319999999998</v>
+      </c>
+      <c r="B98" t="n">
+        <v>9.765489999999998</v>
+      </c>
+      <c r="C98" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>9.765489999999998</v>
+      </c>
+      <c r="B99" t="n">
+        <v>9.837659999999998</v>
+      </c>
+      <c r="C99" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>9.837659999999998</v>
+      </c>
+      <c r="B100" t="n">
+        <v>9.909829999999998</v>
+      </c>
+      <c r="C100" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>9.909829999999998</v>
+      </c>
+      <c r="B101" t="n">
+        <v>9.981999999999999</v>
+      </c>
+      <c r="C101" t="n">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parent cpu_op</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Input dims</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Input strides</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) sum</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel count</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) mean</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) percent of total time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>((768,), (5, 768), (768, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>((1,), (768, 1), (1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1649.788</v>
+      </c>
+      <c r="G2" t="n">
+        <v>240</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6.874116666666667</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1816270726170491</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>((1, 5185, 1024), (1, 5185, 1024), ())</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>((5309440, 1024, 1), (5309440, 1024, 1), ())</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1202.107</v>
+      </c>
+      <c r="G3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9.3914609375</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1323413525752782</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>((1, 12, 5, 64), (1, 12, 5, 64), ())</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>((3840, 320, 64, 1), (3840, 64, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1058.898</v>
+      </c>
+      <c r="G4" t="n">
+        <v>180</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.882766666666666</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1165753078213977</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>((1, 5185, 1024), ())</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>((5309440, 1024, 1), ())</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>857.976</v>
+      </c>
+      <c r="G5" t="n">
+        <v>119</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7.209882352941176</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.09445557202239642</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>((1, 5, 768), (), (768,), (768,), ())</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>((3840, 768, 1), (), (1,), (1,), ())</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>('', '[768]', '', '', '1.0000000000000001e-05')</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>646.436</v>
+      </c>
+      <c r="G6" t="n">
+        <v>125</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.171488</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.07116688829975415</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>((1, 5, 768), (1, 5, 768), ())</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>((3840, 768, 1), (3840, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>572.149</v>
+      </c>
+      <c r="G7" t="n">
+        <v>125</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.577192</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.06298854638945856</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>((1, 12, 5, 5), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>((300, 25, 5, 1), (25, 25, 5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>555.234</v>
+      </c>
+      <c r="G8" t="n">
+        <v>120</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.62695</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.06112635443914895</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>((768,), (5, 3072), (3072, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>((1,), (3072, 1), (1, 3072), (), ())</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>514.482</v>
+      </c>
+      <c r="G9" t="n">
+        <v>60</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8.5747</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.05663991953764039</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>((3072,), (5, 768), (768, 3072), (), ())</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>((1,), (768, 1), (1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>419.266</v>
+      </c>
+      <c r="G10" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.987766666666667</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.04615747976580005</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>((1, 5, 12, 64), (1, 5, 12, 64), ())</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>((3840, 768, 64, 1), (3840, 64, 320, 1), ())</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>401.827</v>
+      </c>
+      <c r="G11" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.697116666666667</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.04423760004830379</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>((12, 5, 5), (12, 5, 64))</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>((25, 5, 1), (320, 64, 1))</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>384.538</v>
+      </c>
+      <c r="G12" t="n">
+        <v>60</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.408966666666667</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0423342340046205</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>((12, 5, 64), (12, 64, 5))</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>((320, 64, 1), (320, 1, 64))</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>355.711</v>
+      </c>
+      <c r="G13" t="n">
+        <v>60</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5.928516666666667</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.03916063617124332</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>((1, 5, 3072), (1, 5, 3072))</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>((15360, 3072, 1), (15360, 3072, 1))</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>308.848</v>
+      </c>
+      <c r="G14" t="n">
+        <v>60</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.147466666666667</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.03400143419859424</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>((12, 5, 5), (), ())</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>((25, 5, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>('', '-1', 'False')</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>294.657</v>
+      </c>
+      <c r="G15" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.91095</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.03243913056472822</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>aten::sigmoid</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>((1, 5, 3072),)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>((15360, 3072, 1),)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>('',)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>292.09</v>
+      </c>
+      <c r="G16" t="n">
+        <v>60</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.868166666666667</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.03215652656020888</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>((1, 5, 768), ())</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>((3840, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>291.332</v>
+      </c>
+      <c r="G17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.855533333333333</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.03207307746187398</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>((1, 5, 3072), ())</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>((15360, 3072, 1), ())</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>291.329</v>
+      </c>
+      <c r="G18" t="n">
+        <v>60</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.855483333333334</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.03207274718839773</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>((1,), (5184, 1024), (1024, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>((1,), (1024, 1), (1, 1024), (), ())</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>69.666</v>
+      </c>
+      <c r="G19" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.6444</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.007669610665697256</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1024), ())</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>((5308416, 1024, 1), ())</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>67.949</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>9.706999999999999</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.00748058414611809</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>aten::div</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>((1, 768), (1, 1))</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>((768, 1), (1, 1))</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>49.504</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.9504</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.005449952722916158</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>aten::linalg_vector_norm</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>((1, 768), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>((768, 1), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>('', '2', '[-1]', 'True', '')</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.814</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.005299788382376855</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>46.297</v>
+      </c>
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.6297</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.00509689037679479</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>aten::argmax</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>((1, 5), (), ())</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>((5, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>('', '-1', 'False')</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4, 4&gt; &gt;(at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>37.76300000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7.552600000000001</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.004157372427995372</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>((1, 5184, 768), (1, 768, 1))</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>((3981312, 768, 1), (768, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bjlk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x16x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB1_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>37.081</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>9.270250000000001</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.00408229025772572</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>aten::index</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>((1, 5, 768), ())</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>((3840, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>void at::native::index_elementwise_kernel&lt;128, 4, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1}&gt;(long, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6.581999999999999</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.003623100034566312</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>aten::linalg_vector_norm</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>((1, 5184, 768), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>((3981312, 768, 1), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>('', '2.', '[-1]', 'True', '')</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>32.149</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6.4298</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.003539320662755162</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>((49408, 768), (), (5,))</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>((768, 1), (), (1,))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>('', '0', '')</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>31.828</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>6.3656</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.003503981400795399</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>((4,), (5184, 1024), (1024, 4), (), ())</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>((1,), (1024, 1), (1, 1024), (), ())</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>31.067</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6.2134</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.003420202028984249</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>((1, 1024), (1024, 768))</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>((1024, 1), (1, 1024))</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>30.145</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>6.029</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.00331869798061384</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>aten::div</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>((1, 5184, 768), (1, 5184, 1))</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>((3981312, 768, 1), (5184, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>28.583</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>9.527666666666667</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.003146735590641413</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>aten::index_select</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>((16, 768), (), (5,))</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>((768, 1), (), (1,))</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>('', '0', '')</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5.612</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.003089157914613513</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>((1, 1, 5, 5), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>((25, 25, 5, 1), (25, 25, 5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>26.455</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5.290999999999999</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.0029124616048147</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>((1, 5), (1, 5), ())</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>((5, 1), (5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>25.814</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>5.1628</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.002841893172053928</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>aten::sub</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>((), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>((), (25, 25, 5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>25.655</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5.131</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.002824388677812177</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>((1, 1024), (), (1024,), (1024,), ())</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>((5309440, 1), (), (1,), (1,), ())</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>('', '[1024]', '', '', '1.0000000000000001e-05')</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>25.093</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>5.0186</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.002762517446592904</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>aten::fill_</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>((5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>((5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>('', '-3.3895313892515355e+38')</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4.938</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.002718150709615383</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>((5, 5), (5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>((5, 1), (5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4.842000000000001</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.002665306953413869</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>((5,), (), ())</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>((1,), (), ())</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>24.131</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4.8262</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.00265660975187237</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>aten::exp</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>((),)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>((),)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>('',)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>24.051</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4.8102</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.002647802459172118</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (1, 5184, 1))</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (5184, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>24.011</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4.802200000000001</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.002643398812821991</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>aten::div</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>((1, 1, 768), (1, 1, 1))</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>((768, 768, 1), (1, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>23.931</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.7862</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.002634591520121739</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>aten::lt</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>((5,), (5, 1))</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>((1,), (1, 1))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>23.769</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4.7538</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.002616756752403727</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>((1, 1, 5, 5), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>((25, 25, 5, 1), (5, 5, 0, 1), ())</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2})</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>23.769</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4.7538</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.002616756752403727</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>aten::gt</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>((1, 1), ())</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>((5, 5), ())</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>('', '0')</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>23.568</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4.7136</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.002594628429494344</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (1, 5184, 1), ())</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (5184, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>23.369</v>
+      </c>
+      <c r="G46" t="n">
+        <v>5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4.6738</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.002572720288902466</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>aten::masked_fill_</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>((5, 5), (5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>((5, 1), (5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>('', '', '0')</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.002559619441010841</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (1, 5184, 1), ())</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (5184, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>23.167</v>
+      </c>
+      <c r="G48" t="n">
+        <v>5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4.6334</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.002550481874834329</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>aten::arange</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>((), (), (), (0,))</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>((), (), (), (1,))</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>('0', '5', '1', '')</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>23.088</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4.6176</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.00254178467329283</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>aten::add_</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>((1, 5184, 4), (5184, 4), ())</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>((20736, 4, 1), (4, 1), ())</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>22.928</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4.585599999999999</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.002524170087892325</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>aten::fill_</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>((), ())</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>((), ())</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>('', '-3.3895313892515355e+38')</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>22.646</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4.5292</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.002493124381123936</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>('', '', '1')</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>22.487</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4.497400000000001</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.002475619886882184</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>aten::arange</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>((), (), (), (0,))</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>((), (), (), (1,))</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>('0', '1', '1', '')</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>22.486</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4.497199999999999</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.00247550979572343</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>((1, 768), (768, 768))</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>((768, 1), (1, 768))</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>22.367</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" t="n">
+        <v>5.59175</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.002462408947831805</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>aten::masked_fill_</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>((1, 1, 5, 5), (1, 1, 5, 5), ())</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>((25, 25, 5, 1), (25, 25, 5, 1), ())</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>('', '', '-3.3895313892515355e+38')</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>22.366</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4.4732</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.002462298856673052</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>aten::elu</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>((1, 5184, 1), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>((5184, 1, 1), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>('', '1.', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>21.964</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>4.392799999999999</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.002418042210854284</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>((1, 1), ())</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>((1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>21.885</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4.377</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.002409345009312785</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>aten::eq</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), ())</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>('', '0')</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>21.845</v>
+      </c>
+      <c r="G58" t="n">
+        <v>5</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4.369</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.002404941362962658</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>aten::linalg_vector_norm</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>((1, 1, 768), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>((768, 768, 1), (), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>('', '2.', '[-1]', 'True', '')</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>21.323</v>
+      </c>
+      <c r="G59" t="n">
+        <v>5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4.2646</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.002347473778093512</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>aten::where</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), (), (1, 5184, 1))</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>((1, 1, 1), (), (5184, 1, 1))</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>('', '', '')</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>19.802</v>
+      </c>
+      <c r="G60" t="n">
+        <v>4</v>
+      </c>
+      <c r="H60" t="n">
+        <v>4.9505</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.002180025125629964</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>aten::sigmoid</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>((1, 5184, 4),)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>((20736, 4, 1),)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>('',)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>3.198</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.001760357628462939</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -21130,7 +27733,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>aten::linalg_vector_norm</t>
+          <t>aten::linalg_norm</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -21174,28 +27777,46 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>4583</v>
+        <v>4582</v>
       </c>
       <c r="K51" t="n">
         <v>10</v>
       </c>
       <c r="L51" t="n">
-        <v>137.38</v>
+        <v>175.202</v>
       </c>
       <c r="M51" t="n">
-        <v>13.738</v>
+        <v>17.5202</v>
       </c>
       <c r="N51" t="n">
-        <v>7.114041404933704</v>
-      </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+        <v>10.7939256662666</v>
+      </c>
+      <c r="O51" t="n">
+        <v>7.68e-07</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.001466751098632812</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.4993498049414825</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="S51" t="n">
+        <v>0.000327107290741538</v>
+      </c>
+      <c r="T51" t="n">
+        <v>5.230899017508888e-05</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.0001633409618267238</v>
+      </c>
+      <c r="V51" t="n">
+        <v>2.612048404061655e-05</v>
+      </c>
       <c r="W51" t="n">
         <v>4.814013671875</v>
       </c>
@@ -21206,20 +27827,32 @@
         <v>48.14013671875</v>
       </c>
       <c r="Z51" t="n">
-        <v>13.2545</v>
+        <v>15.724</v>
       </c>
       <c r="AA51" t="n">
-        <v>6.755</v>
+        <v>7.733</v>
       </c>
       <c r="AB51" t="n">
-        <v>21.943</v>
-      </c>
-      <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="inlineStr"/>
+        <v>38.577</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0.0003329304496948884</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.0002592661124372377</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0.000399673137926659</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0.0001662487551142225</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0.0001294644826734711</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0.0001995767034640274</v>
+      </c>
       <c r="AI51" t="n">
         <v>4.630126953125</v>
       </c>
@@ -21239,9 +27872,13 @@
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(4.81)}]</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>{'num_input_elems': 768, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'norm'}</t>
+        </is>
+      </c>
       <c r="AO51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP51" t="n">
         <v>0.01450794100702804</v>
@@ -21809,7 +28446,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>aten::linalg_vector_norm</t>
+          <t>aten::linalg_norm</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -21839,7 +28476,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'Scalar', 'ScalarList', 'Scalar', '')</t>
+          <t>('c10::BFloat16', '', 'ScalarList', 'Scalar', '')</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -21849,32 +28486,50 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>('', '2.', '[-1]', 'True', '')</t>
+          <t>('', '', '[-1]', 'True', '')</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>4655</v>
+        <v>4654</v>
       </c>
       <c r="K56" t="n">
         <v>5</v>
       </c>
       <c r="L56" t="n">
-        <v>58.592</v>
+        <v>66.54900000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>11.7184</v>
+        <v>13.3098</v>
       </c>
       <c r="N56" t="n">
-        <v>1.607062631013489</v>
-      </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
+        <v>1.75570134134482</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.003981312</v>
+      </c>
+      <c r="P56" t="n">
+        <v>7.593751907348633</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.4999998744132903</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="S56" t="n">
+        <v>1.241544667684163</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.07091261215372953</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0.6207721779205716</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0.03545629717118316</v>
+      </c>
       <c r="W56" t="n">
         <v>6.4298828125</v>
       </c>
@@ -21885,20 +28540,32 @@
         <v>32.1494140625</v>
       </c>
       <c r="Z56" t="n">
-        <v>11.248</v>
+        <v>12.528</v>
       </c>
       <c r="AA56" t="n">
-        <v>10.682</v>
+        <v>12.119</v>
       </c>
       <c r="AB56" t="n">
-        <v>14.532</v>
-      </c>
-      <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr"/>
-      <c r="AE56" t="inlineStr"/>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="inlineStr"/>
+        <v>16.39</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.241432555420219</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.15483733786559</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.351409467804757</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0.6207161218026797</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0.5774185239005736</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0.6757045641833098</v>
+      </c>
       <c r="AI56" t="n">
         <v>6.4140625</v>
       </c>
@@ -21918,9 +28585,13 @@
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(6.43)}]</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr">
+        <is>
+          <t>{'num_input_elems': 3981312, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'norm'}</t>
+        </is>
+      </c>
       <c r="AO56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP56" t="n">
         <v>0.009688834191607149</v>
@@ -26911,7 +33582,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>aten::linalg_vector_norm</t>
+          <t>aten::linalg_norm</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -26941,7 +33612,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'Scalar', 'ScalarList', 'Scalar', '')</t>
+          <t>('c10::BFloat16', '', 'ScalarList', 'Scalar', '')</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -26951,32 +33622,50 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>('', '2.', '[-1]', 'True', '')</t>
+          <t>('', '', '[-1]', 'True', '')</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>4659</v>
+        <v>4658</v>
       </c>
       <c r="K92" t="n">
         <v>5</v>
       </c>
       <c r="L92" t="n">
-        <v>41.349</v>
+        <v>47.33</v>
       </c>
       <c r="M92" t="n">
-        <v>8.2698</v>
+        <v>9.465999999999999</v>
       </c>
       <c r="N92" t="n">
-        <v>0.637994670824138</v>
-      </c>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
+        <v>0.4908217599088287</v>
+      </c>
+      <c r="O92" t="n">
+        <v>7.68e-07</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.001466751098632812</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0.4993498049414825</v>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="S92" t="n">
+        <v>0.0003613396923387094</v>
+      </c>
+      <c r="T92" t="n">
+        <v>1.779948916443615e-05</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0.0001804349048869498</v>
+      </c>
+      <c r="V92" t="n">
+        <v>8.888171442319212e-06</v>
+      </c>
       <c r="W92" t="n">
         <v>4.26455078125</v>
       </c>
@@ -26987,20 +33676,32 @@
         <v>21.32275390625</v>
       </c>
       <c r="Z92" t="n">
-        <v>8.25</v>
+        <v>9.458</v>
       </c>
       <c r="AA92" t="n">
-        <v>7.348</v>
+        <v>8.738</v>
       </c>
       <c r="AB92" t="n">
-        <v>8.967000000000001</v>
-      </c>
-      <c r="AC92" t="inlineStr"/>
-      <c r="AD92" t="inlineStr"/>
-      <c r="AE92" t="inlineStr"/>
-      <c r="AF92" t="inlineStr"/>
-      <c r="AG92" t="inlineStr"/>
-      <c r="AH92" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>0.0003620487356321839</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>0.0003396036657681941</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>0.0003876229387152351</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>0.0001807889655172414</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>0.0001695810242587601</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>0.0001935594388382968</v>
+      </c>
       <c r="AI92" t="n">
         <v>4.248046875</v>
       </c>
@@ -27020,9 +33721,13 @@
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(4.26)}]</t>
         </is>
       </c>
-      <c r="AN92" t="inlineStr"/>
+      <c r="AN92" t="inlineStr">
+        <is>
+          <t>{'num_input_elems': 768, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'norm'}</t>
+        </is>
+      </c>
       <c r="AO92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP92" t="n">
         <v>0.006426015314135241</v>

--- a/tests/traces/mi300/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
+++ b/tests/traces/mi300/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7919,27 +7919,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>aten::lt</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>((5,), (5, 1))</t>
+          <t>((1, 1, 5, 5), (1, 1, 5, 5), ())</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>((1,), (1, 1))</t>
+          <t>((25, 25, 5, 1), (5, 5, 0, 1), ())</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>('', '')</t>
+          <t>('', '', 'False')</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1})</t>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2})</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -7958,27 +7958,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::lt</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>((1, 1, 5, 5), (1, 1, 5, 5), ())</t>
+          <t>((5,), (5, 1))</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>((25, 25, 5, 1), (5, 5, 0, 1), ())</t>
+          <t>((1,), (1, 1))</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>('', '', 'False')</t>
+          <t>('', '')</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2})</t>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1})</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>{'elementwise', 'other'}</t>
+          <t>{'other', 'elementwise'}</t>
         </is>
       </c>
       <c r="H5" t="n">

--- a/tests/traces/mi300/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
+++ b/tests/traces/mi300/google_owlv2-large-patch14-ensemble__1016001_perf_report.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,13 +30,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,7 +50,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,12 +58,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,17 +442,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>time ms</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
@@ -565,202 +577,202 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>param: op_shape</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>param: dtype_in_out</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>param: stride_input</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>param: stride_output</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>param: num_channels</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>param: has_bias</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>param: is_affine</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>param: is_training</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>process_name_first</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>process_label_first</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>thread_name_first</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -787,7 +799,11 @@
           <t>(5309440, 1024, 1)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>1024</t>
@@ -869,12 +885,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 250, 'total_duration_us': np.float64(5090.484), 'mean_duration_us': np.float64(20.361936), 'median_duration_us': np.float64(20.165), 'std_dev_duration_us': np.float64(1.2402476574878099), 'min_duration_us': np.float64(18.0), 'max_duration_us': np.float64(28.384)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 250, 'total_duration_us': 5090.484, 'mean_duration_us': 20.361936, 'median_duration_us': 20.165, 'std_dev_duration_us': 1.2402476574878099, 'min_duration_us': 18.0, 'max_duration_us': 28.384}]</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(20.36)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': 20.36}]</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -943,7 +959,11 @@
           <t>(5309440, 1024, 1)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>1024</t>
@@ -1025,12 +1045,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 250, 'total_duration_us': np.float64(5090.484), 'mean_duration_us': np.float64(20.361936), 'median_duration_us': np.float64(20.165), 'std_dev_duration_us': np.float64(1.2402476574878099), 'min_duration_us': np.float64(18.0), 'max_duration_us': np.float64(28.384)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 250, 'total_duration_us': 5090.484, 'mean_duration_us': 20.361936, 'median_duration_us': 20.165, 'std_dev_duration_us': 1.2402476574878099, 'min_duration_us': 18.0, 'max_duration_us': 28.384}]</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(20.36)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': 20.36}]</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1099,7 +1119,11 @@
           <t>(3840, 768, 1)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>768</t>
@@ -1181,12 +1205,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 125, 'total_duration_us': np.float64(646.4359999999999), 'mean_duration_us': np.float64(5.171487999999999), 'median_duration_us': np.float64(5.13), 'std_dev_duration_us': np.float64(0.3605603331704697), 'min_duration_us': np.float64(4.409), 'max_duration_us': np.float64(6.293)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 125, 'total_duration_us': 646.4359999999999, 'mean_duration_us': 5.171487999999999, 'median_duration_us': 5.13, 'std_dev_duration_us': 0.3605603331704697, 'min_duration_us': 4.409, 'max_duration_us': 6.293}]</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(5.17)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': 5.17}]</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1255,7 +1279,11 @@
           <t>(3840, 768, 1)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>768</t>
@@ -1337,12 +1365,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 125, 'total_duration_us': np.float64(646.4359999999999), 'mean_duration_us': np.float64(5.171487999999999), 'median_duration_us': np.float64(5.13), 'std_dev_duration_us': np.float64(0.3605603331704697), 'min_duration_us': np.float64(4.409), 'max_duration_us': np.float64(6.293)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 125, 'total_duration_us': 646.4359999999999, 'mean_duration_us': 5.171487999999999, 'median_duration_us': 5.13, 'std_dev_duration_us': 0.3605603331704697, 'min_duration_us': 4.409, 'max_duration_us': 6.293}]</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(5.17)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': 5.17}]</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1411,7 +1439,11 @@
           <t>(5308416, 1024, 1)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>1024</t>
@@ -1493,12 +1525,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(90.724), 'mean_duration_us': np.float64(18.1448), 'median_duration_us': np.float64(18.241), 'std_dev_duration_us': np.float64(0.2411509071100502), 'min_duration_us': np.float64(17.72), 'max_duration_us': np.float64(18.441)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 5, 'total_duration_us': 90.724, 'mean_duration_us': 18.1448, 'median_duration_us': 18.241, 'std_dev_duration_us': 0.2411509071100502, 'min_duration_us': 17.72, 'max_duration_us': 18.441}]</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(18.14)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': 18.14}]</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1567,7 +1599,11 @@
           <t>(5308416, 1024, 1)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>1024</t>
@@ -1649,12 +1685,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(90.724), 'mean_duration_us': np.float64(18.1448), 'median_duration_us': np.float64(18.241), 'std_dev_duration_us': np.float64(0.2411509071100502), 'min_duration_us': np.float64(17.72), 'max_duration_us': np.float64(18.441)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 5, 'total_duration_us': 90.724, 'mean_duration_us': 18.1448, 'median_duration_us': 18.241, 'std_dev_duration_us': 0.2411509071100502, 'min_duration_us': 17.72, 'max_duration_us': 18.441}]</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(18.14)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': 18.14}]</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1723,7 +1759,11 @@
           <t>(5309440, 1)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>1024</t>
@@ -1805,12 +1845,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(25.093000000000004), 'mean_duration_us': np.float64(5.018600000000001), 'median_duration_us': np.float64(5.051), 'std_dev_duration_us': np.float64(0.09307330444332598), 'min_duration_us': np.float64(4.89), 'max_duration_us': np.float64(5.131)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 5, 'total_duration_us': 25.093000000000004, 'mean_duration_us': 5.018600000000001, 'median_duration_us': 5.051, 'std_dev_duration_us': 0.09307330444332598, 'min_duration_us': 4.89, 'max_duration_us': 5.131}]</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(5.02)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': 5.02}]</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1879,7 +1919,11 @@
           <t>(5309440, 1)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>1024</t>
@@ -1961,12 +2005,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(25.093000000000004), 'mean_duration_us': np.float64(5.018600000000001), 'median_duration_us': np.float64(5.051), 'std_dev_duration_us': np.float64(0.09307330444332598), 'min_duration_us': np.float64(4.89), 'max_duration_us': np.float64(5.131)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 5, 'total_duration_us': 25.093000000000004, 'mean_duration_us': 5.018600000000001, 'median_duration_us': 5.051, 'std_dev_duration_us': 0.09307330444332598, 'min_duration_us': 4.89, 'max_duration_us': 5.131}]</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(5.02)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': 5.02}]</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -2029,182 +2073,182 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>param: num_input_elems</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>param: num_output_elems</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>param: dtype_in_out</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>param: reduce_type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>process_name_first</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>process_label_first</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>thread_name_first</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -2297,12 +2341,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 15, 'total_duration_us': np.float64(69.463), 'mean_duration_us': np.float64(4.630866666666666), 'median_duration_us': np.float64(4.369), 'std_dev_duration_us': np.float64(0.6680712403795139), 'min_duration_us': np.float64(3.848), 'max_duration_us': np.float64(5.932)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 15, 'total_duration_us': 69.463, 'mean_duration_us': 4.630866666666666, 'median_duration_us': 4.369, 'std_dev_duration_us': 0.6680712403795139, 'min_duration_us': 3.848, 'max_duration_us': 5.932}]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(4.63)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': 4.63}]</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -2437,12 +2481,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(32.149), 'mean_duration_us': np.float64(6.4298), 'median_duration_us': np.float64(6.414), 'std_dev_duration_us': np.float64(0.32155770866206873), 'min_duration_us': np.float64(5.892), 'max_duration_us': np.float64(6.895)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 32.149, 'mean_duration_us': 6.4298, 'median_duration_us': 6.414, 'std_dev_duration_us': 0.32155770866206873, 'min_duration_us': 5.892, 'max_duration_us': 6.895}]</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(6.43)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': 6.43}]</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -2729,57 +2773,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Parent op category</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Parent cpu_op</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Kernel name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Kernel stream</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Kernel duration (µs)_sum</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Kernel duration (µs)_count</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Kernel duration (µs)_mean</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Kernel duration (µs)_min</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Kernel duration (µs)_max</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Percent of kernels time (%)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Percent of total time (%)</t>
         </is>
@@ -5096,17 +5140,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>bin_start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>bin_end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -6227,47 +6271,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Parent cpu_op</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Input dims</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Input strides</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Kernel name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Short Kernel duration (µs) sum</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Short Kernel count</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Short Kernel duration (µs) mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Short Kernel duration (µs) percent of total time</t>
         </is>
@@ -7875,27 +7919,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>aten::lt</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>((5,), (5, 1))</t>
+          <t>((1, 1, 5, 5), (1, 1, 5, 5), ())</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>((1,), (1, 1))</t>
+          <t>((25, 25, 5, 1), (5, 5, 0, 1), ())</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>('', '')</t>
+          <t>('', '', 'False')</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1})</t>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2})</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -7914,27 +7958,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::lt</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>((1, 1, 5, 5), (1, 1, 5, 5), ())</t>
+          <t>((5,), (5, 1))</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>((25, 25, 5, 1), (5, 5, 0, 1), ())</t>
+          <t>((1,), (1, 1))</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>('', '', 'False')</t>
+          <t>('', '')</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2})</t>
+          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1})</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -8628,27 +8672,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>op category</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_ms</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -8783,37 +8827,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_sum</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_ms</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -9590,107 +9634,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>op category</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>process_label</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>thread_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Input Dims</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Input type</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Input Strides</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>operation_count</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_mean</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_median</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_std</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_min</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_max</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_sum</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ex_UID</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>kernel_details_summary</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -9768,12 +9812,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForwardReg&lt;c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue, long, 6&gt;(c10::BFloat16*, c10::BFloat16 const*, long)', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(153698.475), 'mean_duration_us': np.float64(1280.820625), 'median_duration_us': np.float64(1270.1954999999998), 'std_dev_duration_us': np.float64(53.79270149209564), 'min_duration_us': np.float64(1151.523), 'max_duration_us': np.float64(1475.988)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForwardReg&lt;c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue, long, 6&gt;(c10::BFloat16*, c10::BFloat16 const*, long)', 'stream': 0, 'count': 120, 'total_duration_us': 153698.475, 'mean_duration_us': 1280.820625, 'median_duration_us': 1270.1954999999998, 'std_dev_duration_us': 53.79270149209564, 'min_duration_us': 1151.523, 'max_duration_us': 1475.988}]</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForwardReg&lt;c...', 'stream': 0, 'mean_duration_us': np.float64(1280.82)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForwardReg&lt;c...', 'stream': 0, 'mean_duration_us': 1280.82}]</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -9855,12 +9899,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x288x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA32_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_9_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(55056.329), 'mean_duration_us': np.float64(458.80274166666663), 'median_duration_us': np.float64(459.394), 'std_dev_duration_us': np.float64(39.331859811628505), 'min_duration_us': np.float64(399.316), 'max_duration_us': np.float64(559.804)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x288x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA32_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_9_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': 55056.329, 'mean_duration_us': 458.80274166666663, 'median_duration_us': 459.394, 'std_dev_duration_us': 39.331859811628505, 'min_duration_us': 399.316, 'max_duration_us': 559.804}]</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x288x64_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(458.8)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x288x64_MI16x1...', 'stream': 0, 'mean_duration_us': 458.8}]</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -9942,12 +9986,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB256_LBSPPM0_LPA4_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(40460.247), 'mean_duration_us': np.float64(337.16872500000005), 'median_duration_us': np.float64(331.821), 'std_dev_duration_us': np.float64(11.541609001032239), 'min_duration_us': np.float64(322.5), 'max_duration_us': np.float64(377.545)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB256_LBSPPM0_LPA4_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': 40460.247, 'mean_duration_us': 337.16872500000005, 'median_duration_us': 331.821, 'std_dev_duration_us': 11.541609001032239, 'min_duration_us': 322.5, 'max_duration_us': 377.545}]</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x32_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(337.17)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x32_MI16x...', 'stream': 0, 'mean_duration_us': 337.17}]</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -10029,12 +10073,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_5_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 480, 'total_duration_us': np.float64(15205.791000000001), 'mean_duration_us': np.float64(31.678731250000002), 'median_duration_us': np.float64(31.2305), 'std_dev_duration_us': np.float64(1.291014259160901), 'min_duration_us': np.float64(29.667), 'max_duration_us': np.float64(38.488)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_5_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 480, 'total_duration_us': 15205.791000000001, 'mean_duration_us': 31.678731250000002, 'median_duration_us': 31.2305, 'std_dev_duration_us': 1.291014259160901, 'min_duration_us': 29.667, 'max_duration_us': 38.488}]</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(31.68)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x...', 'stream': 0, 'mean_duration_us': 31.68}]</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -10116,12 +10160,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT160x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT5_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(12190.582999999999), 'mean_duration_us': np.float64(101.58819166666666), 'median_duration_us': np.float64(101.071), 'std_dev_duration_us': np.float64(2.68756934575908), 'min_duration_us': np.float64(96.981), 'max_duration_us': np.float64(110.813)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT160x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT5_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': 12190.582999999999, 'mean_duration_us': 101.58819166666666, 'median_duration_us': 101.071, 'std_dev_duration_us': 2.68756934575908, 'min_duration_us': 96.981, 'max_duration_us': 110.813}]</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT160x128x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(101.59)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT160x128x64_MI16x...', 'stream': 0, 'mean_duration_us': 101.59}]</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -10203,12 +10247,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x288x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_9_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(11587.363), 'mean_duration_us': np.float64(96.56135833333333), 'median_duration_us': np.float64(95.899), 'std_dev_duration_us': np.float64(2.207858184590643), 'min_duration_us': np.float64(93.814), 'max_duration_us': np.float64(105.121)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x288x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_9_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': 11587.363, 'mean_duration_us': 96.56135833333333, 'median_duration_us': 95.899, 'std_dev_duration_us': 2.207858184590643, 'min_duration_us': 93.814, 'max_duration_us': 105.121}]</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x288x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(96.56)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x288x64_MI16x...', 'stream': 0, 'mean_duration_us': 96.56}]</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -10290,12 +10334,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 360, 'total_duration_us': np.float64(6226.331), 'mean_duration_us': np.float64(17.29536388888889), 'median_duration_us': np.float64(15.795), 'std_dev_duration_us': np.float64(2.8259221431687647), 'min_duration_us': np.float64(12.067), 'max_duration_us': np.float64(23.693)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 360, 'total_duration_us': 6226.331, 'mean_duration_us': 17.29536388888889, 'median_duration_us': 15.795, 'std_dev_duration_us': 2.8259221431687647, 'min_duration_us': 12.067, 'max_duration_us': 23.693}]</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(17.3)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 17.3}]</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -10377,12 +10421,12 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 250, 'total_duration_us': np.float64(5090.484), 'mean_duration_us': np.float64(20.361936), 'median_duration_us': np.float64(20.165), 'std_dev_duration_us': np.float64(1.2402476574878099), 'min_duration_us': np.float64(18.0), 'max_duration_us': np.float64(28.384)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 250, 'total_duration_us': 5090.484, 'mean_duration_us': 20.361936, 'median_duration_us': 20.165, 'std_dev_duration_us': 1.2402476574878099, 'min_duration_us': 18.0, 'max_duration_us': 28.384}]</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(20.36)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': 20.36}]</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -10464,12 +10508,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(4463.737999999999), 'mean_duration_us': np.float64(37.19781666666666), 'median_duration_us': np.float64(37.084), 'std_dev_duration_us': np.float64(4.0768960782751815), 'min_duration_us': np.float64(28.985), 'max_duration_us': np.float64(50.435)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': 4463.737999999999, 'mean_duration_us': 37.19781666666666, 'median_duration_us': 37.084, 'std_dev_duration_us': 4.0768960782751815, 'min_duration_us': 28.985, 'max_duration_us': 50.435}]</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': np.float64(37.2)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': 37.2}]</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -10551,12 +10595,12 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(3529.13), 'mean_duration_us': np.float64(29.40941666666667), 'median_duration_us': np.float64(29.1055), 'std_dev_duration_us': np.float64(1.2255553202754885), 'min_duration_us': np.float64(27.703), 'max_duration_us': np.float64(33.035)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': 3529.13, 'mean_duration_us': 29.40941666666667, 'median_duration_us': 29.1055, 'std_dev_duration_us': 1.2255553202754885, 'min_duration_us': 27.703, 'max_duration_us': 33.035}]</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': np.float64(29.41)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': 29.41}]</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -10638,12 +10682,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(3008.275), 'mean_duration_us': np.float64(25.068958333333335), 'median_duration_us': np.float64(24.8965), 'std_dev_duration_us': np.float64(2.5754997003683036), 'min_duration_us': np.float64(19.765), 'max_duration_us': np.float64(33.957)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': 3008.275, 'mean_duration_us': 25.068958333333335, 'median_duration_us': 24.8965, 'std_dev_duration_us': 2.5754997003683036, 'min_duration_us': 19.765, 'max_duration_us': 33.957}]</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(25.07)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': 25.07}]</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -10725,12 +10769,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 245, 'total_duration_us': np.float64(2450.014), 'mean_duration_us': np.float64(10.000057142857143), 'median_duration_us': np.float64(9.942), 'std_dev_duration_us': np.float64(0.8502293788941274), 'min_duration_us': np.float64(8.218), 'max_duration_us': np.float64(13.429)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 245, 'total_duration_us': 2450.014, 'mean_duration_us': 10.000057142857143, 'median_duration_us': 9.942, 'std_dev_duration_us': 0.8502293788941274, 'min_duration_us': 8.218, 'max_duration_us': 13.429}]</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(10.0)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 10.0}]</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -10812,12 +10856,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(1979.3850000000002), 'mean_duration_us': np.float64(16.494875), 'median_duration_us': np.float64(16.216), 'std_dev_duration_us': np.float64(0.889071627809031), 'min_duration_us': np.float64(14.673), 'max_duration_us': np.float64(18.802)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 120, 'total_duration_us': 1979.3850000000002, 'mean_duration_us': 16.494875, 'median_duration_us': 16.216, 'std_dev_duration_us': 0.889071627809031, 'min_duration_us': 14.673, 'max_duration_us': 18.802}]</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(16.49)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 16.49}]</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -10899,12 +10943,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 240, 'total_duration_us': np.float64(1649.788), 'mean_duration_us': np.float64(6.874116666666667), 'median_duration_us': np.float64(6.895), 'std_dev_duration_us': np.float64(0.40092175428075183), 'min_duration_us': np.float64(5.812), 'max_duration_us': np.float64(8.979)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 240, 'total_duration_us': 1649.788, 'mean_duration_us': 6.874116666666667, 'median_duration_us': 6.895, 'std_dev_duration_us': 0.40092175428075183, 'min_duration_us': 5.812, 'max_duration_us': 8.979}]</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(6.87)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 6.87}]</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -10986,12 +11030,12 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(1138.047), 'mean_duration_us': np.float64(227.6094), 'median_duration_us': np.float64(225.036), 'std_dev_duration_us': np.float64(4.802322254909601), 'min_duration_us': np.float64(224.634), 'max_duration_us': np.float64(237.144)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 1138.047, 'mean_duration_us': 227.6094, 'median_duration_us': 225.036, 'std_dev_duration_us': 4.802322254909601, 'min_duration_us': 224.634, 'max_duration_us': 237.144}]</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(227.61)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 227.61}]</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -11073,12 +11117,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(1136.443), 'mean_duration_us': np.float64(227.2886), 'median_duration_us': np.float64(226.238), 'std_dev_duration_us': np.float64(2.4922390415046425), 'min_duration_us': np.float64(224.715), 'max_duration_us': np.float64(230.528)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 1136.443, 'mean_duration_us': 227.2886, 'median_duration_us': 226.238, 'std_dev_duration_us': 2.4922390415046425, 'min_duration_us': 224.715, 'max_duration_us': 230.528}]</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(227.29)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 227.29}]</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -11160,12 +11204,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 180, 'total_duration_us': np.float64(1058.8980000000001), 'mean_duration_us': np.float64(5.882766666666668), 'median_duration_us': np.float64(5.893), 'std_dev_duration_us': np.float64(0.3655466545691078), 'min_duration_us': np.float64(4.81), 'max_duration_us': np.float64(6.775)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 180, 'total_duration_us': 1058.8980000000001, 'mean_duration_us': 5.882766666666668, 'median_duration_us': 5.893, 'std_dev_duration_us': 0.3655466545691078, 'min_duration_us': 4.81, 'max_duration_us': 6.775}]</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(5.88)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 5.88}]</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -11247,12 +11291,12 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(898.455), 'mean_duration_us': np.float64(179.691), 'median_duration_us': np.float64(189.314), 'std_dev_duration_us': np.float64(29.36311296167353), 'min_duration_us': np.float64(122.118), 'max_duration_us': np.float64(204.147)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': 898.455, 'mean_duration_us': 179.691, 'median_duration_us': 189.314, 'std_dev_duration_us': 29.36311296167353, 'min_duration_us': 122.118, 'max_duration_us': 204.147}]</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(179.69)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': 179.69}]</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -11334,12 +11378,12 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(868.479), 'mean_duration_us': np.float64(7.237325), 'median_duration_us': np.float64(7.175), 'std_dev_duration_us': np.float64(0.5774263757181518), 'min_duration_us': np.float64(6.414), 'max_duration_us': np.float64(10.503)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': 868.479, 'mean_duration_us': 7.237325, 'median_duration_us': 7.175, 'std_dev_duration_us': 0.5774263757181518, 'min_duration_us': 6.414, 'max_duration_us': 10.503}]</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(7.24)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': 7.24}]</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -11421,12 +11465,12 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(848.183), 'mean_duration_us': np.float64(169.6366), 'median_duration_us': np.float64(169.549), 'std_dev_duration_us': np.float64(0.12531017516545753), 'min_duration_us': np.float64(169.508), 'max_duration_us': np.float64(169.789)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 848.183, 'mean_duration_us': 169.6366, 'median_duration_us': 169.549, 'std_dev_duration_us': 0.12531017516545753, 'min_duration_us': 169.508, 'max_duration_us': 169.789}]</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(169.64)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 169.64}]</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -11508,12 +11552,12 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 125, 'total_duration_us': np.float64(646.4359999999999), 'mean_duration_us': np.float64(5.171487999999999), 'median_duration_us': np.float64(5.13), 'std_dev_duration_us': np.float64(0.3605603331704697), 'min_duration_us': np.float64(4.409), 'max_duration_us': np.float64(6.293)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 125, 'total_duration_us': 646.4359999999999, 'mean_duration_us': 5.171487999999999, 'median_duration_us': 5.13, 'std_dev_duration_us': 0.3605603331704697, 'min_duration_us': 4.409, 'max_duration_us': 6.293}]</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(5.17)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': 5.17}]</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -11595,12 +11639,12 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_5_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 20, 'total_duration_us': np.float64(622.568), 'mean_duration_us': np.float64(31.1284), 'median_duration_us': np.float64(30.448999999999998), 'std_dev_duration_us': np.float64(1.3790227119231941), 'min_duration_us': np.float64(28.705), 'max_duration_us': np.float64(33.516)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_5_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 20, 'total_duration_us': 622.568, 'mean_duration_us': 31.1284, 'median_duration_us': 30.448999999999998, 'std_dev_duration_us': 1.3790227119231941, 'min_duration_us': 28.705, 'max_duration_us': 33.516}]</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(31.13)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x...', 'stream': 0, 'mean_duration_us': 31.13}]</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -11682,12 +11726,12 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 125, 'total_duration_us': np.float64(572.1489999999999), 'mean_duration_us': np.float64(4.577191999999999), 'median_duration_us': np.float64(4.489), 'std_dev_duration_us': np.float64(0.3315058659149187), 'min_duration_us': np.float64(4.048), 'max_duration_us': np.float64(5.452)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 125, 'total_duration_us': 572.1489999999999, 'mean_duration_us': 4.577191999999999, 'median_duration_us': 4.489, 'std_dev_duration_us': 0.3315058659149187, 'min_duration_us': 4.048, 'max_duration_us': 5.452}]</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.58)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.58}]</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -11769,12 +11813,12 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(555.2339999999999), 'mean_duration_us': np.float64(4.626949999999999), 'median_duration_us': np.float64(4.569), 'std_dev_duration_us': np.float64(0.3686557755323161), 'min_duration_us': np.float64(4.008), 'max_duration_us': np.float64(5.612)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 120, 'total_duration_us': 555.2339999999999, 'mean_duration_us': 4.626949999999999, 'median_duration_us': 4.569, 'std_dev_duration_us': 0.3686557755323161, 'min_duration_us': 4.008, 'max_duration_us': 5.612}]</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.63)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 4.63}]</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -11856,12 +11900,12 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>[{'name': 'Im2d2Col_v2', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(219.258), 'mean_duration_us': np.float64(43.851600000000005), 'median_duration_us': np.float64(44.621), 'std_dev_duration_us': np.float64(1.7498733211292758), 'min_duration_us': np.float64(40.372), 'max_duration_us': np.float64(45.063)}, {'name': 'Cijk_Ailk_Bljk_BBS_BH_MT64x64x64_MI16x16x16x1_SN_1LDSB0_APM1_ABV0_ACED0_AF0EM1_AF1EM1_AMAS0_ASE_ASGT_ASLT_ASM_ASAE01_ASCE01_ASEM1_AAC0_BL1_BS1_CLR1_DTLA0_DTLB0_DTVA0_DTVB0_DVO0_ETSP_EPS1_ELFLR0_EMLL0_FSSC10_FL0_GLVWA2_GLVWB8_GRCGA1_GRCGB1_GRPM1_GRVWn1_GSU1_GSUASB_GLS0_ISA942_IU1_K1_KLA_LBSPPA1024_LBSPPB128_LPA16_LPB16_LDL1_LRVW8_LWPMn1_LDW0_FMA_MIAV0_MDA2_MO40_MMFSC_MKFGSU256_NTA0_NTB0_NTC0_NTD0_NEPBS0_NLCA1_NLCB1_ONLL1_OPLV0_PK0_PAP0_PGR1_PLR5_PKA0_SIA3_SLW1_SS0_SU16_SUM0_SUS512_SCIUI1_SPO0_SRVW0_SSO0_SVW4_SNLL0_TSGRA0_TSGRB0_TT1_64_TLDS1_UMLDSA0_UMLDSB1_U64SL1_USFGROn1_VAW1_VSn1_VW1_VWB1_VFLRP1_WSGRA0_WSGRB0_WS64_WG64_4_1_WGMn16', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(298.64099999999996), 'mean_duration_us': np.float64(59.728199999999994), 'median_duration_us': np.float64(60.458), 'std_dev_duration_us': np.float64(1.7082119774782034), 'min_duration_us': np.float64(56.328), 'max_duration_us': np.float64(60.899)}]</t>
+          <t>[{'name': 'Im2d2Col_v2', 'stream': 0, 'count': 5, 'total_duration_us': 219.258, 'mean_duration_us': 43.851600000000005, 'median_duration_us': 44.621, 'std_dev_duration_us': 1.7498733211292758, 'min_duration_us': 40.372, 'max_duration_us': 45.063}, {'name': 'Cijk_Ailk_Bljk_BBS_BH_MT64x64x64_MI16x16x16x1_SN_1LDSB0_APM1_ABV0_ACED0_AF0EM1_AF1EM1_AMAS0_ASE_ASGT_ASLT_ASM_ASAE01_ASCE01_ASEM1_AAC0_BL1_BS1_CLR1_DTLA0_DTLB0_DTVA0_DTVB0_DVO0_ETSP_EPS1_ELFLR0_EMLL0_FSSC10_FL0_GLVWA2_GLVWB8_GRCGA1_GRCGB1_GRPM1_GRVWn1_GSU1_GSUASB_GLS0_ISA942_IU1_K1_KLA_LBSPPA1024_LBSPPB128_LPA16_LPB16_LDL1_LRVW8_LWPMn1_LDW0_FMA_MIAV0_MDA2_MO40_MMFSC_MKFGSU256_NTA0_NTB0_NTC0_NTD0_NEPBS0_NLCA1_NLCB1_ONLL1_OPLV0_PK0_PAP0_PGR1_PLR5_PKA0_SIA3_SLW1_SS0_SU16_SUM0_SUS512_SCIUI1_SPO0_SRVW0_SSO0_SVW4_SNLL0_TSGRA0_TSGRB0_TT1_64_TLDS1_UMLDSA0_UMLDSB1_U64SL1_USFGROn1_VAW1_VSn1_VW1_VWB1_VFLRP1_WSGRA0_WSGRB0_WS64_WG64_4_1_WGMn16', 'stream': 0, 'count': 5, 'total_duration_us': 298.64099999999996, 'mean_duration_us': 59.728199999999994, 'median_duration_us': 60.458, 'std_dev_duration_us': 1.7082119774782034, 'min_duration_us': 56.328, 'max_duration_us': 60.899}]</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>[{'name': 'Im2d2Col_v2', 'stream': 0, 'mean_duration_us': np.float64(43.85)}, {'name': 'Cijk_Ailk_Bljk_BBS_BH_MT64x64x64_MI16x16x16x1_SN_1LDSB0_APM1_ABV...', 'stream': 0, 'mean_duration_us': np.float64(59.73)}]</t>
+          <t>[{'name': 'Im2d2Col_v2', 'stream': 0, 'mean_duration_us': 43.85}, {'name': 'Cijk_Ailk_Bljk_BBS_BH_MT64x64x64_MI16x16x16x1_SN_1LDSB0_APM1_ABV...', 'stream': 0, 'mean_duration_us': 59.73}]</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -11943,12 +11987,12 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(514.482), 'mean_duration_us': np.float64(8.5747), 'median_duration_us': np.float64(8.6385), 'std_dev_duration_us': np.float64(0.3650420660691038), 'min_duration_us': np.float64(7.657), 'max_duration_us': np.float64(9.18)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': 514.482, 'mean_duration_us': 8.5747, 'median_duration_us': 8.6385, 'std_dev_duration_us': 0.3650420660691038, 'min_duration_us': 7.657, 'max_duration_us': 9.18}]</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(8.57)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 8.57}]</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -12030,12 +12074,12 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(419.266), 'mean_duration_us': np.float64(6.987766666666667), 'median_duration_us': np.float64(6.895), 'std_dev_duration_us': np.float64(0.5233797654561062), 'min_duration_us': np.float64(5.973), 'max_duration_us': np.float64(8.658)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': 419.266, 'mean_duration_us': 6.987766666666667, 'median_duration_us': 6.895, 'std_dev_duration_us': 0.5233797654561062, 'min_duration_us': 5.973, 'max_duration_us': 8.658}]</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(6.99)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 6.99}]</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -12117,12 +12161,12 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(401.82699999999994), 'mean_duration_us': np.float64(6.697116666666665), 'median_duration_us': np.float64(6.775), 'std_dev_duration_us': np.float64(0.31499709478378085), 'min_duration_us': np.float64(5.973), 'max_duration_us': np.float64(7.296)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 60, 'total_duration_us': 401.82699999999994, 'mean_duration_us': 6.697116666666665, 'median_duration_us': 6.775, 'std_dev_duration_us': 0.31499709478378085, 'min_duration_us': 5.973, 'max_duration_us': 7.296}]</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(6.7)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 6.7}]</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -12204,12 +12248,12 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(384.538), 'mean_duration_us': np.float64(6.408966666666667), 'median_duration_us': np.float64(6.273), 'std_dev_duration_us': np.float64(0.7107715049312417), 'min_duration_us': np.float64(5.091), 'max_duration_us': np.float64(8.659)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': 384.538, 'mean_duration_us': 6.408966666666667, 'median_duration_us': 6.273, 'std_dev_duration_us': 0.7107715049312417, 'min_duration_us': 5.091, 'max_duration_us': 8.659}]</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(6.41)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 6.41}]</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -12291,12 +12335,12 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(355.711), 'mean_duration_us': np.float64(5.928516666666667), 'median_duration_us': np.float64(5.812), 'std_dev_duration_us': np.float64(0.600517262912196), 'min_duration_us': np.float64(4.609), 'max_duration_us': np.float64(7.857)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': 355.711, 'mean_duration_us': 5.928516666666667, 'median_duration_us': 5.812, 'std_dev_duration_us': 0.600517262912196, 'min_duration_us': 4.609, 'max_duration_us': 7.857}]</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(5.93)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 5.93}]</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -12378,12 +12422,12 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 15, 'total_duration_us': np.float64(69.66600000000001), 'mean_duration_us': np.float64(4.644400000000001), 'median_duration_us': np.float64(4.689), 'std_dev_duration_us': np.float64(0.2239195688932374), 'min_duration_us': np.float64(4.248), 'max_duration_us': np.float64(5.01)}, {'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA1_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB4_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS0_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_1', 'stream': 0, 'count': 15, 'total_duration_us': np.float64(282.956), 'mean_duration_us': np.float64(18.863733333333336), 'median_duration_us': np.float64(17.158), 'std_dev_duration_us': np.float64(7.847680162244695), 'min_duration_us': np.float64(15.234), 'max_duration_us': np.float64(47.99)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 15, 'total_duration_us': 69.66600000000001, 'mean_duration_us': 4.644400000000001, 'median_duration_us': 4.689, 'std_dev_duration_us': 0.2239195688932374, 'min_duration_us': 4.248, 'max_duration_us': 5.01}, {'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA1_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB4_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS0_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_1', 'stream': 0, 'count': 15, 'total_duration_us': 282.956, 'mean_duration_us': 18.863733333333336, 'median_duration_us': 17.158, 'std_dev_duration_us': 7.847680162244695, 'min_duration_us': 15.234, 'max_duration_us': 47.99}]</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.64)}, {'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16...', 'stream': 0, 'mean_duration_us': np.float64(18.86)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 4.64}, {'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16...', 'stream': 0, 'mean_duration_us': 18.86}]</t>
         </is>
       </c>
       <c r="T32" t="n">
@@ -12465,12 +12509,12 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(308.848), 'mean_duration_us': np.float64(5.147466666666667), 'median_duration_us': np.float64(5.051), 'std_dev_duration_us': np.float64(0.35748615202394757), 'min_duration_us': np.float64(4.369), 'max_duration_us': np.float64(6.093)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': 308.848, 'mean_duration_us': 5.147466666666667, 'median_duration_us': 5.051, 'std_dev_duration_us': 0.35748615202394757, 'min_duration_us': 4.369, 'max_duration_us': 6.093}]</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': np.float64(5.15)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': 5.15}]</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -12552,12 +12596,12 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(294.65700000000004), 'mean_duration_us': np.float64(4.910950000000001), 'median_duration_us': np.float64(4.810499999999999), 'std_dev_duration_us': np.float64(0.34617815379753053), 'min_duration_us': np.float64(4.249), 'max_duration_us': np.float64(6.093)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)', 'stream': 0, 'count': 60, 'total_duration_us': 294.65700000000004, 'mean_duration_us': 4.910950000000001, 'median_duration_us': 4.810499999999999, 'std_dev_duration_us': 0.34617815379753053, 'min_duration_us': 4.249, 'max_duration_us': 6.093}]</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, ...', 'stream': 0, 'mean_duration_us': np.float64(4.91)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, ...', 'stream': 0, 'mean_duration_us': 4.91}]</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -12639,12 +12683,12 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(292.09), 'mean_duration_us': np.float64(4.868166666666666), 'median_duration_us': np.float64(4.77), 'std_dev_duration_us': np.float64(0.40604807460310527), 'min_duration_us': np.float64(4.128), 'max_duration_us': np.float64(5.852)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': 292.09, 'mean_duration_us': 4.868166666666666, 'median_duration_us': 4.77, 'std_dev_duration_us': 0.40604807460310527, 'min_duration_us': 4.128, 'max_duration_us': 5.852}]</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': np.float64(4.87)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': 4.87}]</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -12726,12 +12770,12 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(291.33199999999994), 'mean_duration_us': np.float64(4.855533333333332), 'median_duration_us': np.float64(4.73), 'std_dev_duration_us': np.float64(0.32905027309245954), 'min_duration_us': np.float64(4.289), 'max_duration_us': np.float64(5.532)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': 291.33199999999994, 'mean_duration_us': 4.855533333333332, 'median_duration_us': 4.73, 'std_dev_duration_us': 0.32905027309245954, 'min_duration_us': 4.289, 'max_duration_us': 5.532}]</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(4.86)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': 4.86}]</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -12813,12 +12857,12 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(291.32899999999995), 'mean_duration_us': np.float64(4.855483333333333), 'median_duration_us': np.float64(4.69), 'std_dev_duration_us': np.float64(0.34405471908145985), 'min_duration_us': np.float64(4.209), 'max_duration_us': np.float64(5.773)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': 291.32899999999995, 'mean_duration_us': 4.855483333333333, 'median_duration_us': 4.69, 'std_dev_duration_us': 0.34405471908145985, 'min_duration_us': 4.209, 'max_duration_us': 5.773}]</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(4.86)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': 4.86}]</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -12900,12 +12944,12 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 20, 'total_duration_us': np.float64(289.404), 'mean_duration_us': np.float64(14.4702), 'median_duration_us': np.float64(14.1715), 'std_dev_duration_us': np.float64(4.524248375144759), 'min_duration_us': np.float64(9.461), 'max_duration_us': np.float64(20.085)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 20, 'total_duration_us': 289.404, 'mean_duration_us': 14.4702, 'median_duration_us': 14.1715, 'std_dev_duration_us': 4.524248375144759, 'min_duration_us': 9.461, 'max_duration_us': 20.085}]</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Ge...', 'stream': 0, 'mean_duration_us': np.float64(14.47)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Ge...', 'stream': 0, 'mean_duration_us': 14.47}]</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -12987,12 +13031,12 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(149.136), 'mean_duration_us': np.float64(29.827199999999998), 'median_duration_us': np.float64(29.667), 'std_dev_duration_us': np.float64(0.5100754453999921), 'min_duration_us': np.float64(29.306), 'max_duration_us': np.float64(30.789)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'count': 5, 'total_duration_us': 149.136, 'mean_duration_us': 29.827199999999998, 'median_duration_us': 29.667, 'std_dev_duration_us': 0.5100754453999921, 'min_duration_us': 29.306, 'max_duration_us': 30.789}]</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 0, 'mean_duration_us': np.float64(29.83)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 0, 'mean_duration_us': 29.83}]</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -13074,12 +13118,12 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x64x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB4_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(136.148), 'mean_duration_us': np.float64(27.229599999999998), 'median_duration_us': np.float64(27.262), 'std_dev_duration_us': np.float64(0.7408710009171641), 'min_duration_us': np.float64(26.139), 'max_duration_us': np.float64(28.104)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x64x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB4_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 5, 'total_duration_us': 136.148, 'mean_duration_us': 27.229599999999998, 'median_duration_us': 27.262, 'std_dev_duration_us': 0.7408710009171641, 'min_duration_us': 26.139, 'max_duration_us': 28.104}]</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x64x64_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(27.23)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x64x64_MI16x1...', 'stream': 0, 'mean_duration_us': 27.23}]</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -13161,12 +13205,12 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 10, 'total_duration_us': np.float64(95.929), 'mean_duration_us': np.float64(9.5929), 'median_duration_us': np.float64(5.912), 'std_dev_duration_us': np.float64(9.921683712455259), 'min_duration_us': np.float64(4.049), 'max_duration_us': np.float64(38.407)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 10, 'total_duration_us': 95.929, 'mean_duration_us': 9.5929, 'median_duration_us': 5.912, 'std_dev_duration_us': 9.921683712455259, 'min_duration_us': 4.049, 'max_duration_us': 38.407}]</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(9.59)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': 9.59}]</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -13248,12 +13292,12 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(90.724), 'mean_duration_us': np.float64(18.1448), 'median_duration_us': np.float64(18.241), 'std_dev_duration_us': np.float64(0.2411509071100502), 'min_duration_us': np.float64(17.72), 'max_duration_us': np.float64(18.441)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 5, 'total_duration_us': 90.724, 'mean_duration_us': 18.1448, 'median_duration_us': 18.241, 'std_dev_duration_us': 0.2411509071100502, 'min_duration_us': 17.72, 'max_duration_us': 18.441}]</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(18.14)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': 18.14}]</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -13335,12 +13379,12 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(83.667), 'mean_duration_us': np.float64(16.7334), 'median_duration_us': np.float64(16.557), 'std_dev_duration_us': np.float64(0.8273663275720137), 'min_duration_us': np.float64(15.595), 'max_duration_us': np.float64(18.161)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 0, 'count': 5, 'total_duration_us': 83.667, 'mean_duration_us': 16.7334, 'median_duration_us': 16.557, 'std_dev_duration_us': 0.8273663275720137, 'min_duration_us': 15.595, 'max_duration_us': 18.161}]</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c1...', 'stream': 0, 'mean_duration_us': np.float64(16.73)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c1...', 'stream': 0, 'mean_duration_us': 16.73}]</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -13422,12 +13466,12 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(75.429), 'mean_duration_us': np.float64(15.0858), 'median_duration_us': np.float64(14.823), 'std_dev_duration_us': np.float64(0.4742212142028235), 'min_duration_us': np.float64(14.603), 'max_duration_us': np.float64(15.755)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': 75.429, 'mean_duration_us': 15.0858, 'median_duration_us': 14.823, 'std_dev_duration_us': 0.4742212142028235, 'min_duration_us': 14.603, 'max_duration_us': 15.755}]</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(15.09)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': 15.09}]</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -13509,12 +13553,12 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA1_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB4_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS0_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_1', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(60.253), 'mean_duration_us': np.float64(12.0506), 'median_duration_us': np.float64(11.906), 'std_dev_duration_us': np.float64(0.49213477828741153), 'min_duration_us': np.float64(11.345), 'max_duration_us': np.float64(12.628)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA1_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB4_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS0_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_1', 'stream': 0, 'count': 5, 'total_duration_us': 60.253, 'mean_duration_us': 12.0506, 'median_duration_us': 11.906, 'std_dev_duration_us': 0.49213477828741153, 'min_duration_us': 11.345, 'max_duration_us': 12.628}]</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16...', 'stream': 0, 'mean_duration_us': np.float64(12.05)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16...', 'stream': 0, 'mean_duration_us': 12.05}]</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -13596,12 +13640,12 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(59.051), 'mean_duration_us': np.float64(11.8102), 'median_duration_us': np.float64(11.826), 'std_dev_duration_us': np.float64(0.3424951970466156), 'min_duration_us': np.float64(11.345), 'max_duration_us': np.float64(12.387)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 59.051, 'mean_duration_us': 11.8102, 'median_duration_us': 11.826, 'std_dev_duration_us': 0.3424951970466156, 'min_duration_us': 11.345, 'max_duration_us': 12.387}]</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(11.81)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 11.81}]</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -13683,12 +13727,12 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(58.97), 'mean_duration_us': np.float64(11.794), 'median_duration_us': np.float64(5.772), 'std_dev_duration_us': np.float64(12.405547646113815), 'min_duration_us': np.float64(5.411), 'max_duration_us': np.float64(36.603)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': 58.97, 'mean_duration_us': 11.794, 'median_duration_us': 5.772, 'std_dev_duration_us': 12.405547646113815, 'min_duration_us': 5.411, 'max_duration_us': 36.603}]</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(11.79)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 11.79}]</t>
         </is>
       </c>
       <c r="T47" t="n">
@@ -13770,12 +13814,12 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(55.763), 'mean_duration_us': np.float64(11.1526), 'median_duration_us': np.float64(5.171), 'std_dev_duration_us': np.float64(12.406593804908741), 'min_duration_us': np.float64(4.53), 'max_duration_us': np.float64(35.961)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 55.763, 'mean_duration_us': 11.1526, 'median_duration_us': 5.171, 'std_dev_duration_us': 12.406593804908741, 'min_duration_us': 4.53, 'max_duration_us': 35.961}]</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(11.15)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 11.15}]</t>
         </is>
       </c>
       <c r="T48" t="n">
@@ -13857,12 +13901,12 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(49.509), 'mean_duration_us': np.float64(9.9018), 'median_duration_us': np.float64(9.662), 'std_dev_duration_us': np.float64(0.483819966516472), 'min_duration_us': np.float64(9.26), 'max_duration_us': np.float64(10.544)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 49.509, 'mean_duration_us': 9.9018, 'median_duration_us': 9.662, 'std_dev_duration_us': 0.483819966516472, 'min_duration_us': 9.26, 'max_duration_us': 10.544}]</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(9.9)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 9.9}]</t>
         </is>
       </c>
       <c r="T49" t="n">
@@ -13944,12 +13988,12 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 10, 'total_duration_us': np.float64(49.504000000000005), 'mean_duration_us': np.float64(4.9504), 'median_duration_us': np.float64(5.091), 'std_dev_duration_us': np.float64(0.4543756595593562), 'min_duration_us': np.float64(4.088), 'max_duration_us': np.float64(5.491)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 10, 'total_duration_us': 49.504000000000005, 'mean_duration_us': 4.9504, 'median_duration_us': 5.091, 'std_dev_duration_us': 0.4543756595593562, 'min_duration_us': 4.088, 'max_duration_us': 5.491}]</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.95)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 4.95}]</t>
         </is>
       </c>
       <c r="T50" t="n">
@@ -14031,12 +14075,12 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 10, 'total_duration_us': np.float64(48.14), 'mean_duration_us': np.float64(4.814), 'median_duration_us': np.float64(4.63), 'std_dev_duration_us': np.float64(0.7427319839619135), 'min_duration_us': np.float64(3.848), 'max_duration_us': np.float64(5.932)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 10, 'total_duration_us': 48.14, 'mean_duration_us': 4.814, 'median_duration_us': 4.63, 'std_dev_duration_us': 0.7427319839619135, 'min_duration_us': 3.848, 'max_duration_us': 5.932}]</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(4.81)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': 4.81}]</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -14118,12 +14162,12 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bjlk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x16x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB1_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(47.143), 'mean_duration_us': np.float64(9.4286), 'median_duration_us': np.float64(9.14), 'std_dev_duration_us': np.float64(0.45920696858823895), 'min_duration_us': np.float64(8.94), 'max_duration_us': np.float64(10.062)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bjlk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x16x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB1_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 5, 'total_duration_us': 47.143, 'mean_duration_us': 9.4286, 'median_duration_us': 9.14, 'std_dev_duration_us': 0.45920696858823895, 'min_duration_us': 8.94, 'max_duration_us': 10.062}]</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bjlk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x16x128_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(9.43)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bjlk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x16x128_MI16x1...', 'stream': 0, 'mean_duration_us': 9.43}]</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -14205,12 +14249,12 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 10, 'total_duration_us': np.float64(42.248), 'mean_duration_us': np.float64(4.2248), 'median_duration_us': np.float64(4.148999999999999), 'std_dev_duration_us': np.float64(0.4044254690298325), 'min_duration_us': np.float64(3.808), 'max_duration_us': np.float64(5.292)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 10, 'total_duration_us': 42.248, 'mean_duration_us': 4.2248, 'median_duration_us': 4.148999999999999, 'std_dev_duration_us': 0.4044254690298325, 'min_duration_us': 3.808, 'max_duration_us': 5.292}]</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(4.22)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': 4.22}]</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -14292,12 +14336,12 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4, 4&gt; &gt;(at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(37.763000000000005), 'mean_duration_us': np.float64(7.552600000000001), 'median_duration_us': np.float64(7.457), 'std_dev_duration_us': np.float64(0.2960490499900313), 'min_duration_us': np.float64(7.256), 'max_duration_us': np.float64(8.057)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4, 4&gt; &gt;(at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 37.763000000000005, 'mean_duration_us': 7.552600000000001, 'median_duration_us': 7.457, 'std_dev_duration_us': 0.2960490499900313, 'min_duration_us': 7.256, 'max_duration_us': 8.057}]</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int,...', 'stream': 0, 'mean_duration_us': np.float64(7.55)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int,...', 'stream': 0, 'mean_duration_us': 7.55}]</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -14379,12 +14423,12 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::index_elementwise_kernel&lt;128, 4, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1}&gt;(long, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(32.910000000000004), 'mean_duration_us': np.float64(6.582000000000001), 'median_duration_us': np.float64(6.655), 'std_dev_duration_us': np.float64(0.26174949856685475), 'min_duration_us': np.float64(6.253), 'max_duration_us': np.float64(6.975)}]</t>
+          <t>[{'name': 'void at::native::index_elementwise_kernel&lt;128, 4, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1}&gt;(long, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 32.910000000000004, 'mean_duration_us': 6.582000000000001, 'median_duration_us': 6.655, 'std_dev_duration_us': 0.26174949856685475, 'min_duration_us': 6.253, 'max_duration_us': 6.975}]</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::index_elementwise_kernel&lt;128, 4, at::native::gp...', 'stream': 0, 'mean_duration_us': np.float64(6.58)}]</t>
+          <t>[{'name': 'void at::native::index_elementwise_kernel&lt;128, 4, at::native::gp...', 'stream': 0, 'mean_duration_us': 6.58}]</t>
         </is>
       </c>
       <c r="T55" t="n">
@@ -14466,12 +14510,12 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(32.149), 'mean_duration_us': np.float64(6.4298), 'median_duration_us': np.float64(6.414), 'std_dev_duration_us': np.float64(0.32155770866206873), 'min_duration_us': np.float64(5.892), 'max_duration_us': np.float64(6.895)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 32.149, 'mean_duration_us': 6.4298, 'median_duration_us': 6.414, 'std_dev_duration_us': 0.32155770866206873, 'min_duration_us': 5.892, 'max_duration_us': 6.895}]</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(6.43)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': 6.43}]</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -14553,12 +14597,12 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(31.827999999999996), 'mean_duration_us': np.float64(6.365599999999999), 'median_duration_us': np.float64(6.334), 'std_dev_duration_us': np.float64(0.16319877450520262), 'min_duration_us': np.float64(6.173), 'max_duration_us': np.float64(6.574)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)', 'stream': 0, 'count': 5, 'total_duration_us': 31.827999999999996, 'mean_duration_us': 6.365599999999999, 'median_duration_us': 6.334, 'std_dev_duration_us': 0.16319877450520262, 'min_duration_us': 6.173, 'max_duration_us': 6.574}]</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c1...', 'stream': 0, 'mean_duration_us': np.float64(6.37)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c1...', 'stream': 0, 'mean_duration_us': 6.37}]</t>
         </is>
       </c>
       <c r="T57" t="n">
@@ -14640,12 +14684,12 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(31.067), 'mean_duration_us': np.float64(6.2134), 'median_duration_us': np.float64(6.093), 'std_dev_duration_us': np.float64(0.28699937282161453), 'min_duration_us': np.float64(6.013), 'max_duration_us': np.float64(6.775)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': 31.067, 'mean_duration_us': 6.2134, 'median_duration_us': 6.093, 'std_dev_duration_us': 0.28699937282161453, 'min_duration_us': 6.013, 'max_duration_us': 6.775}]</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(6.21)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 6.21}]</t>
         </is>
       </c>
       <c r="T58" t="n">
@@ -14727,12 +14771,12 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(30.145000000000003), 'mean_duration_us': np.float64(6.029000000000001), 'median_duration_us': np.float64(6.093), 'std_dev_duration_us': np.float64(0.2632732420888988), 'min_duration_us': np.float64(5.652), 'max_duration_us': np.float64(6.374)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': 30.145000000000003, 'mean_duration_us': 6.029000000000001, 'median_duration_us': 6.093, 'std_dev_duration_us': 0.2632732420888988, 'min_duration_us': 5.652, 'max_duration_us': 6.374}]</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(6.03)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 6.03}]</t>
         </is>
       </c>
       <c r="T59" t="n">
@@ -14814,12 +14858,12 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(28.06), 'mean_duration_us': np.float64(5.612), 'median_duration_us': np.float64(5.572), 'std_dev_duration_us': np.float64(0.10158936952260311), 'min_duration_us': np.float64(5.492), 'max_duration_us': np.float64(5.733)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)', 'stream': 0, 'count': 5, 'total_duration_us': 28.06, 'mean_duration_us': 5.612, 'median_duration_us': 5.572, 'std_dev_duration_us': 0.10158936952260311, 'min_duration_us': 5.492, 'max_duration_us': 5.733}]</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c1...', 'stream': 0, 'mean_duration_us': np.float64(5.61)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c1...', 'stream': 0, 'mean_duration_us': 5.61}]</t>
         </is>
       </c>
       <c r="T60" t="n">
@@ -14901,12 +14945,12 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(27.898), 'mean_duration_us': np.float64(5.5796), 'median_duration_us': np.float64(5.572), 'std_dev_duration_us': np.float64(0.0162061716639064), 'min_duration_us': np.float64(5.571), 'max_duration_us': np.float64(5.612)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 27.898, 'mean_duration_us': 5.5796, 'median_duration_us': 5.572, 'std_dev_duration_us': 0.0162061716639064, 'min_duration_us': 5.571, 'max_duration_us': 5.612}]</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(5.58)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 5.58}]</t>
         </is>
       </c>
       <c r="T61" t="n">
@@ -14988,12 +15032,12 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(26.455), 'mean_duration_us': np.float64(5.2909999999999995), 'median_duration_us': np.float64(5.251), 'std_dev_duration_us': np.float64(0.30444835358398653), 'min_duration_us': np.float64(4.93), 'max_duration_us': np.float64(5.732)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 26.455, 'mean_duration_us': 5.2909999999999995, 'median_duration_us': 5.251, 'std_dev_duration_us': 0.30444835358398653, 'min_duration_us': 4.93, 'max_duration_us': 5.732}]</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(5.29)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 5.29}]</t>
         </is>
       </c>
       <c r="T62" t="n">
@@ -15075,12 +15119,12 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(25.814), 'mean_duration_us': np.float64(5.1628), 'median_duration_us': np.float64(5.171), 'std_dev_duration_us': np.float64(0.1816726726835932), 'min_duration_us': np.float64(4.89), 'max_duration_us': np.float64(5.451)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 25.814, 'mean_duration_us': 5.1628, 'median_duration_us': 5.171, 'std_dev_duration_us': 0.1816726726835932, 'min_duration_us': 4.89, 'max_duration_us': 5.451}]</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(5.16)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 5.16}]</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -15162,12 +15206,12 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(25.654999999999998), 'mean_duration_us': np.float64(5.130999999999999), 'median_duration_us': np.float64(5.371), 'std_dev_duration_us': np.float64(0.43609265070624603), 'min_duration_us': np.float64(4.61), 'max_duration_us': np.float64(5.652)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 25.654999999999998, 'mean_duration_us': 5.130999999999999, 'median_duration_us': 5.371, 'std_dev_duration_us': 0.43609265070624603, 'min_duration_us': 4.61, 'max_duration_us': 5.652}]</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(5.13)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 5.13}]</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -15249,12 +15293,12 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(25.655), 'mean_duration_us': np.float64(5.131), 'median_duration_us': np.float64(5.131), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(5.131), 'max_duration_us': np.float64(5.131)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 25.655, 'mean_duration_us': 5.131, 'median_duration_us': 5.131, 'std_dev_duration_us': 0.0, 'min_duration_us': 5.131, 'max_duration_us': 5.131}]</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(5.13)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 5.13}]</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -15336,12 +15380,12 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(25.093000000000004), 'mean_duration_us': np.float64(5.018600000000001), 'median_duration_us': np.float64(5.051), 'std_dev_duration_us': np.float64(0.09307330444332598), 'min_duration_us': np.float64(4.89), 'max_duration_us': np.float64(5.131)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 5, 'total_duration_us': 25.093000000000004, 'mean_duration_us': 5.018600000000001, 'median_duration_us': 5.051, 'std_dev_duration_us': 0.09307330444332598, 'min_duration_us': 4.89, 'max_duration_us': 5.131}]</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(5.02)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': 5.02}]</t>
         </is>
       </c>
       <c r="T66" t="n">
@@ -15423,12 +15467,12 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(24.689999999999998), 'mean_duration_us': np.float64(4.938), 'median_duration_us': np.float64(5.05), 'std_dev_duration_us': np.float64(0.26999333325102687), 'min_duration_us': np.float64(4.449), 'max_duration_us': np.float64(5.251)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 24.689999999999998, 'mean_duration_us': 4.938, 'median_duration_us': 5.05, 'std_dev_duration_us': 0.26999333325102687, 'min_duration_us': 4.449, 'max_duration_us': 5.251}]</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 0, 'mean_duration_us': np.float64(4.94)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 0, 'mean_duration_us': 4.94}]</t>
         </is>
       </c>
       <c r="T67" t="n">
@@ -15510,12 +15554,12 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(24.21), 'mean_duration_us': np.float64(4.8420000000000005), 'median_duration_us': np.float64(4.529), 'std_dev_duration_us': np.float64(0.4251691428125987), 'min_duration_us': np.float64(4.489), 'max_duration_us': np.float64(5.491)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 24.21, 'mean_duration_us': 4.8420000000000005, 'median_duration_us': 4.529, 'std_dev_duration_us': 0.4251691428125987, 'min_duration_us': 4.489, 'max_duration_us': 5.491}]</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 0, 'mean_duration_us': np.float64(4.84)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 0, 'mean_duration_us': 4.84}]</t>
         </is>
       </c>
       <c r="T68" t="n">
@@ -15597,12 +15641,12 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(24.131), 'mean_duration_us': np.float64(4.8262), 'median_duration_us': np.float64(4.69), 'std_dev_duration_us': np.float64(0.2316759806281177), 'min_duration_us': np.float64(4.61), 'max_duration_us': np.float64(5.251)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 24.131, 'mean_duration_us': 4.8262, 'median_duration_us': 4.69, 'std_dev_duration_us': 0.2316759806281177, 'min_duration_us': 4.61, 'max_duration_us': 5.251}]</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.83)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.83}]</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -15684,12 +15728,12 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(24.051000000000002), 'mean_duration_us': np.float64(4.8102), 'median_duration_us': np.float64(4.73), 'std_dev_duration_us': np.float64(0.2619926716532353), 'min_duration_us': np.float64(4.53), 'max_duration_us': np.float64(5.211)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 24.051000000000002, 'mean_duration_us': 4.8102, 'median_duration_us': 4.73, 'std_dev_duration_us': 0.2619926716532353, 'min_duration_us': 4.53, 'max_duration_us': 5.211}]</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::ex...', 'stream': 0, 'mean_duration_us': np.float64(4.81)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::ex...', 'stream': 0, 'mean_duration_us': 4.81}]</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -15771,12 +15815,12 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(24.011000000000003), 'mean_duration_us': np.float64(4.802200000000001), 'median_duration_us': np.float64(4.57), 'std_dev_duration_us': np.float64(0.5108465131524341), 'min_duration_us': np.float64(4.41), 'max_duration_us': np.float64(5.812)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 24.011000000000003, 'mean_duration_us': 4.802200000000001, 'median_duration_us': 4.57, 'std_dev_duration_us': 0.5108465131524341, 'min_duration_us': 4.41, 'max_duration_us': 5.812}]</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': np.float64(4.8)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': 4.8}]</t>
         </is>
       </c>
       <c r="T71" t="n">
@@ -15858,12 +15902,12 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.931), 'mean_duration_us': np.float64(4.7862), 'median_duration_us': np.float64(4.61), 'std_dev_duration_us': np.float64(0.5367853947342459), 'min_duration_us': np.float64(4.249), 'max_duration_us': np.float64(5.812)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 23.931, 'mean_duration_us': 4.7862, 'median_duration_us': 4.61, 'std_dev_duration_us': 0.5367853947342459, 'min_duration_us': 4.249, 'max_duration_us': 5.812}]</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.79)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 4.79}]</t>
         </is>
       </c>
       <c r="T72" t="n">
@@ -15945,12 +15989,12 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.85), 'mean_duration_us': np.float64(4.7700000000000005), 'median_duration_us': np.float64(4.61), 'std_dev_duration_us': np.float64(0.3218459258713711), 'min_duration_us': np.float64(4.449), 'max_duration_us': np.float64(5.251)}]</t>
+          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': 23.85, 'mean_duration_us': 4.7700000000000005, 'median_duration_us': 4.61, 'std_dev_duration_us': 0.3218459258713711, 'min_duration_us': 4.449, 'max_duration_us': 5.251}]</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(4.77)}]</t>
+          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'mean_duration_us': 4.77}]</t>
         </is>
       </c>
       <c r="T73" t="n">
@@ -16032,12 +16076,12 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.769), 'mean_duration_us': np.float64(4.7538), 'median_duration_us': np.float64(4.931), 'std_dev_duration_us': np.float64(0.25055570238970815), 'min_duration_us': np.float64(4.409), 'max_duration_us': np.float64(4.97)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 23.769, 'mean_duration_us': 4.7538, 'median_duration_us': 4.931, 'std_dev_duration_us': 0.25055570238970815, 'min_duration_us': 4.409, 'max_duration_us': 4.97}]</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.75)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 4.75}]</t>
         </is>
       </c>
       <c r="T74" t="n">
@@ -16119,12 +16163,12 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.769), 'mean_duration_us': np.float64(4.7538), 'median_duration_us': np.float64(4.57), 'std_dev_duration_us': np.float64(0.2427059125773412), 'min_duration_us': np.float64(4.529), 'max_duration_us': np.float64(5.051)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2})', 'stream': 0, 'count': 5, 'total_duration_us': 23.769, 'mean_duration_us': 4.7538, 'median_duration_us': 4.57, 'std_dev_duration_us': 0.2427059125773412, 'min_duration_us': 4.529, 'max_duration_us': 5.051}]</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(4.75)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 4.75}]</t>
         </is>
       </c>
       <c r="T75" t="n">
@@ -16206,12 +16250,12 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.568), 'mean_duration_us': np.float64(4.7136000000000005), 'median_duration_us': np.float64(4.489), 'std_dev_duration_us': np.float64(0.35368324811899154), 'min_duration_us': np.float64(4.329), 'max_duration_us': np.float64(5.251)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 23.568, 'mean_duration_us': 4.7136000000000005, 'median_duration_us': 4.489, 'std_dev_duration_us': 0.35368324811899154, 'min_duration_us': 4.329, 'max_duration_us': 5.251}]</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::co...', 'stream': 0, 'mean_duration_us': np.float64(4.71)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::co...', 'stream': 0, 'mean_duration_us': 4.71}]</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -16293,12 +16337,12 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.368999999999996), 'mean_duration_us': np.float64(4.673799999999999), 'median_duration_us': np.float64(4.73), 'std_dev_duration_us': np.float64(0.19056169604618856), 'min_duration_us': np.float64(4.449), 'max_duration_us': np.float64(4.89)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 23.368999999999996, 'mean_duration_us': 4.673799999999999, 'median_duration_us': 4.73, 'std_dev_duration_us': 0.19056169604618856, 'min_duration_us': 4.449, 'max_duration_us': 4.89}]</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(4.67)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 4.67}]</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -16380,12 +16424,12 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.25), 'mean_duration_us': np.float64(4.65), 'median_duration_us': np.float64(4.61), 'std_dev_duration_us': np.float64(0.13908414719154719), 'min_duration_us': np.float64(4.489), 'max_duration_us': np.float64(4.851)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 23.25, 'mean_duration_us': 4.65, 'median_duration_us': 4.61, 'std_dev_duration_us': 0.13908414719154719, 'min_duration_us': 4.489, 'max_duration_us': 4.851}]</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 0, 'mean_duration_us': np.float64(4.65)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 0, 'mean_duration_us': 4.65}]</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -16467,12 +16511,12 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.21), 'mean_duration_us': np.float64(4.642), 'median_duration_us': np.float64(4.57), 'std_dev_duration_us': np.float64(0.28190920524168783), 'min_duration_us': np.float64(4.329), 'max_duration_us': np.float64(5.011)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 23.21, 'mean_duration_us': 4.642, 'median_duration_us': 4.57, 'std_dev_duration_us': 0.28190920524168783, 'min_duration_us': 4.329, 'max_duration_us': 5.011}]</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.64)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.64}]</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -16554,12 +16598,12 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.167), 'mean_duration_us': np.float64(4.6334), 'median_duration_us': np.float64(4.489), 'std_dev_duration_us': np.float64(0.36638482501326386), 'min_duration_us': np.float64(4.128), 'max_duration_us': np.float64(5.131)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 23.167, 'mean_duration_us': 4.6334, 'median_duration_us': 4.489, 'std_dev_duration_us': 0.36638482501326386, 'min_duration_us': 4.128, 'max_duration_us': 5.131}]</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.63)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.63}]</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -16641,12 +16685,12 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.088), 'mean_duration_us': np.float64(4.6176), 'median_duration_us': np.float64(4.489), 'std_dev_duration_us': np.float64(0.2929693499327193), 'min_duration_us': np.float64(4.369), 'max_duration_us': np.float64(5.171)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 0, 'count': 5, 'total_duration_us': 23.088, 'mean_duration_us': 4.6176, 'median_duration_us': 4.489, 'std_dev_duration_us': 0.2929693499327193, 'min_duration_us': 4.369, 'max_duration_us': 5.171}]</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 0, 'mean_duration_us': np.float64(4.62)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 0, 'mean_duration_us': 4.62}]</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -16728,12 +16772,12 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.087000000000003), 'mean_duration_us': np.float64(4.617400000000001), 'median_duration_us': np.float64(4.569), 'std_dev_duration_us': np.float64(0.2909203327373321), 'min_duration_us': np.float64(4.328), 'max_duration_us': np.float64(5.171)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 23.087000000000003, 'mean_duration_us': 4.617400000000001, 'median_duration_us': 4.569, 'std_dev_duration_us': 0.2909203327373321, 'min_duration_us': 4.328, 'max_duration_us': 5.171}]</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.62)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.62}]</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -16815,12 +16859,12 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(22.929000000000002), 'mean_duration_us': np.float64(4.585800000000001), 'median_duration_us': np.float64(3.647), 'std_dev_duration_us': np.float64(2.16479425350309), 'min_duration_us': np.float64(2.525), 'max_duration_us': np.float64(8.739)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 22.929000000000002, 'mean_duration_us': 4.585800000000001, 'median_duration_us': 3.647, 'std_dev_duration_us': 2.16479425350309, 'min_duration_us': 2.525, 'max_duration_us': 8.739}]</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(4.59)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 4.59}]</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -16902,12 +16946,12 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(22.928), 'mean_duration_us': np.float64(4.5856), 'median_duration_us': np.float64(4.329), 'std_dev_duration_us': np.float64(0.4130828488330158), 'min_duration_us': np.float64(4.169), 'max_duration_us': np.float64(5.291)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 22.928, 'mean_duration_us': 4.5856, 'median_duration_us': 4.329, 'std_dev_duration_us': 0.4130828488330158, 'min_duration_us': 4.169, 'max_duration_us': 5.291}]</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(4.59)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 4.59}]</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -16989,12 +17033,12 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(22.646), 'mean_duration_us': np.float64(4.5292), 'median_duration_us': np.float64(4.649), 'std_dev_duration_us': np.float64(0.24465600340069316), 'min_duration_us': np.float64(4.088), 'max_duration_us': np.float64(4.77)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 22.646, 'mean_duration_us': 4.5292, 'median_duration_us': 4.649, 'std_dev_duration_us': 0.24465600340069316, 'min_duration_us': 4.088, 'max_duration_us': 4.77}]</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Fi...', 'stream': 0, 'mean_duration_us': np.float64(4.53)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Fi...', 'stream': 0, 'mean_duration_us': 4.53}]</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -17076,12 +17120,12 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(22.487000000000002), 'mean_duration_us': np.float64(4.497400000000001), 'median_duration_us': np.float64(4.369), 'std_dev_duration_us': np.float64(0.3635748066079388), 'min_duration_us': np.float64(4.048), 'max_duration_us': np.float64(5.131)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 22.487000000000002, 'mean_duration_us': 4.497400000000001, 'median_duration_us': 4.369, 'std_dev_duration_us': 0.3635748066079388, 'min_duration_us': 4.048, 'max_duration_us': 5.131}]</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.5)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.5}]</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -17163,12 +17207,12 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(22.485999999999997), 'mean_duration_us': np.float64(4.497199999999999), 'median_duration_us': np.float64(4.449), 'std_dev_duration_us': np.float64(0.331947827225906), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(4.89)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 0, 'count': 5, 'total_duration_us': 22.485999999999997, 'mean_duration_us': 4.497199999999999, 'median_duration_us': 4.449, 'std_dev_duration_us': 0.331947827225906, 'min_duration_us': 3.968, 'max_duration_us': 4.89}]</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 0, 'mean_duration_us': np.float64(4.5)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 0, 'mean_duration_us': 4.5}]</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -17250,12 +17294,12 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(22.366), 'mean_duration_us': np.float64(4.4732), 'median_duration_us': np.float64(4.369), 'std_dev_duration_us': np.float64(0.19400659782595026), 'min_duration_us': np.float64(4.289), 'max_duration_us': np.float64(4.81)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 22.366, 'mean_duration_us': 4.4732, 'median_duration_us': 4.369, 'std_dev_duration_us': 0.19400659782595026, 'min_duration_us': 4.289, 'max_duration_us': 4.81}]</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(a...', 'stream': 0, 'mean_duration_us': np.float64(4.47)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(a...', 'stream': 0, 'mean_duration_us': 4.47}]</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -17337,12 +17381,12 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(21.964), 'mean_duration_us': np.float64(4.392799999999999), 'median_duration_us': np.float64(4.449), 'std_dev_duration_us': np.float64(0.24247424605512233), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(4.689)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 21.964, 'mean_duration_us': 4.392799999999999, 'median_duration_us': 4.449, 'std_dev_duration_us': 0.24247424605512233, 'min_duration_us': 3.968, 'max_duration_us': 4.689}]</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(a...', 'stream': 0, 'mean_duration_us': np.float64(4.39)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(a...', 'stream': 0, 'mean_duration_us': 4.39}]</t>
         </is>
       </c>
       <c r="T89" t="n">
@@ -17424,12 +17468,12 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(21.884999999999998), 'mean_duration_us': np.float64(4.377), 'median_duration_us': np.float64(4.329), 'std_dev_duration_us': np.float64(0.3979557764375334), 'min_duration_us': np.float64(3.848), 'max_duration_us': np.float64(4.97)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 21.884999999999998, 'mean_duration_us': 4.377, 'median_duration_us': 4.329, 'std_dev_duration_us': 0.3979557764375334, 'min_duration_us': 3.848, 'max_duration_us': 4.97}]</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': np.float64(4.38)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': 4.38}]</t>
         </is>
       </c>
       <c r="T90" t="n">
@@ -17511,12 +17555,12 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(21.845), 'mean_duration_us': np.float64(4.369), 'median_duration_us': np.float64(4.288), 'std_dev_duration_us': np.float64(0.39618329091469784), 'min_duration_us': np.float64(3.888), 'max_duration_us': np.float64(5.091)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 21.845, 'mean_duration_us': 4.369, 'median_duration_us': 4.288, 'std_dev_duration_us': 0.39618329091469784, 'min_duration_us': 3.888, 'max_duration_us': 5.091}]</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(4.37)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 4.37}]</t>
         </is>
       </c>
       <c r="T91" t="n">
@@ -17598,12 +17642,12 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(21.323), 'mean_duration_us': np.float64(4.2646), 'median_duration_us': np.float64(4.248), 'std_dev_duration_us': np.float64(0.1855506399881175), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(4.529)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 21.323, 'mean_duration_us': 4.2646, 'median_duration_us': 4.248, 'std_dev_duration_us': 0.1855506399881175, 'min_duration_us': 3.968, 'max_duration_us': 4.529}]</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(4.26)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': 4.26}]</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -17685,12 +17729,12 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(17.916), 'mean_duration_us': np.float64(3.5832), 'median_duration_us': np.float64(3.407), 'std_dev_duration_us': np.float64(0.6221727734319463), 'min_duration_us': np.float64(2.886), 'max_duration_us': np.float64(4.609)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 17.916, 'mean_duration_us': 3.5832, 'median_duration_us': 3.407, 'std_dev_duration_us': 0.6221727734319463, 'min_duration_us': 2.886, 'max_duration_us': 4.609}]</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(3.58)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 3.58}]</t>
         </is>
       </c>
       <c r="T93" t="n">
@@ -17772,12 +17816,12 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(15.99), 'mean_duration_us': np.float64(3.198), 'median_duration_us': np.float64(3.126), 'std_dev_duration_us': np.float64(0.3572125417731018), 'min_duration_us': np.float64(2.765), 'max_duration_us': np.float64(3.687)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 15.99, 'mean_duration_us': 3.198, 'median_duration_us': 3.126, 'std_dev_duration_us': 0.3572125417731018, 'min_duration_us': 2.765, 'max_duration_us': 3.687}]</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': np.float64(3.2)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': 3.2}]</t>
         </is>
       </c>
       <c r="T94" t="n">
@@ -17859,12 +17903,12 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(15.951), 'mean_duration_us': np.float64(3.1902), 'median_duration_us': np.float64(3.006), 'std_dev_duration_us': np.float64(0.5261100265153668), 'min_duration_us': np.float64(2.605), 'max_duration_us': np.float64(3.928)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 15.951, 'mean_duration_us': 3.1902, 'median_duration_us': 3.006, 'std_dev_duration_us': 0.5261100265153668, 'min_duration_us': 2.605, 'max_duration_us': 3.928}]</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(3.19)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 3.19}]</t>
         </is>
       </c>
       <c r="T95" t="n">
@@ -17946,12 +17990,12 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(15.391), 'mean_duration_us': np.float64(3.0782), 'median_duration_us': np.float64(2.926), 'std_dev_duration_us': np.float64(0.3955605642629204), 'min_duration_us': np.float64(2.726), 'max_duration_us': np.float64(3.848)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 15.391, 'mean_duration_us': 3.0782, 'median_duration_us': 2.926, 'std_dev_duration_us': 0.3955605642629204, 'min_duration_us': 2.726, 'max_duration_us': 3.848}]</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(3.08)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 3.08}]</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -18033,12 +18077,12 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(15.030000000000001), 'mean_duration_us': np.float64(3.0060000000000002), 'median_duration_us': np.float64(2.926), 'std_dev_duration_us': np.float64(0.3119506371206829), 'min_duration_us': np.float64(2.725), 'max_duration_us': np.float64(3.568)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 15.030000000000001, 'mean_duration_us': 3.0060000000000002, 'median_duration_us': 2.926, 'std_dev_duration_us': 0.3119506371206829, 'min_duration_us': 2.725, 'max_duration_us': 3.568}]</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(3.01)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 3.01}]</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -18063,217 +18107,217 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>op category</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>process_label</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>thread_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Input Dims</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Input type</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Input Strides</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ex_UID</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>operation_count</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>total_duration_us</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>mean_duration_us</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>std_duration_us</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>GFLOPS</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>duration_us_median</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>duration_us_min</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>duration_us_max</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>kernel_details_summary</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>perf_params</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>has_perf_model</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -18383,12 +18427,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForwardReg&lt;c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue, long, 6&gt;(c10::BFloat16*, c10::BFloat16 const*, long)', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(153698.475), 'mean_duration_us': np.float64(1280.820625), 'median_duration_us': np.float64(1270.1954999999998), 'std_dev_duration_us': np.float64(53.79270149209564), 'min_duration_us': np.float64(1151.523), 'max_duration_us': np.float64(1475.988)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForwardReg&lt;c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue, long, 6&gt;(c10::BFloat16*, c10::BFloat16 const*, long)', 'stream': 0, 'count': 120, 'total_duration_us': 153698.475, 'mean_duration_us': 1280.820625, 'median_duration_us': 1270.1954999999998, 'std_dev_duration_us': 53.79270149209564, 'min_duration_us': 1151.523, 'max_duration_us': 1475.988}]</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForwardReg&lt;c...', 'stream': 0, 'mean_duration_us': np.float64(1280.82)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForwardReg&lt;c...', 'stream': 0, 'mean_duration_us': 1280.82}]</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr"/>
@@ -18536,12 +18580,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x288x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA32_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_9_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(55056.329), 'mean_duration_us': np.float64(458.80274166666663), 'median_duration_us': np.float64(459.394), 'std_dev_duration_us': np.float64(39.331859811628505), 'min_duration_us': np.float64(399.316), 'max_duration_us': np.float64(559.804)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x288x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA32_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_9_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': 55056.329, 'mean_duration_us': 458.80274166666663, 'median_duration_us': 459.394, 'std_dev_duration_us': 39.331859811628505, 'min_duration_us': 399.316, 'max_duration_us': 559.804}]</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x288x64_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(458.8)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x288x64_MI16x1...', 'stream': 0, 'mean_duration_us': 458.8}]</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -18693,12 +18737,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB256_LBSPPM0_LPA4_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(40460.247), 'mean_duration_us': np.float64(337.16872500000005), 'median_duration_us': np.float64(331.821), 'std_dev_duration_us': np.float64(11.541609001032239), 'min_duration_us': np.float64(322.5), 'max_duration_us': np.float64(377.545)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB256_LBSPPM0_LPA4_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': 40460.247, 'mean_duration_us': 337.16872500000005, 'median_duration_us': 331.821, 'std_dev_duration_us': 11.541609001032239, 'min_duration_us': 322.5, 'max_duration_us': 377.545}]</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x32_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(337.17)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x32_MI16x...', 'stream': 0, 'mean_duration_us': 337.17}]</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -18850,12 +18894,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_5_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 480, 'total_duration_us': np.float64(15205.791000000001), 'mean_duration_us': np.float64(31.678731250000002), 'median_duration_us': np.float64(31.2305), 'std_dev_duration_us': np.float64(1.291014259160901), 'min_duration_us': np.float64(29.667), 'max_duration_us': np.float64(38.488)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_5_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 480, 'total_duration_us': 15205.791000000001, 'mean_duration_us': 31.678731250000002, 'median_duration_us': 31.2305, 'std_dev_duration_us': 1.291014259160901, 'min_duration_us': 29.667, 'max_duration_us': 38.488}]</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(31.68)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x...', 'stream': 0, 'mean_duration_us': 31.68}]</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -19007,12 +19051,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT160x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT5_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(12190.582999999999), 'mean_duration_us': np.float64(101.58819166666666), 'median_duration_us': np.float64(101.071), 'std_dev_duration_us': np.float64(2.68756934575908), 'min_duration_us': np.float64(96.981), 'max_duration_us': np.float64(110.813)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT160x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT5_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': 12190.582999999999, 'mean_duration_us': 101.58819166666666, 'median_duration_us': 101.071, 'std_dev_duration_us': 2.68756934575908, 'min_duration_us': 96.981, 'max_duration_us': 110.813}]</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT160x128x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(101.59)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT160x128x64_MI16x...', 'stream': 0, 'mean_duration_us': 101.59}]</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -19164,12 +19208,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x288x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_9_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(11587.363), 'mean_duration_us': np.float64(96.56135833333333), 'median_duration_us': np.float64(95.899), 'std_dev_duration_us': np.float64(2.207858184590643), 'min_duration_us': np.float64(93.814), 'max_duration_us': np.float64(105.121)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x288x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_9_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': 11587.363, 'mean_duration_us': 96.56135833333333, 'median_duration_us': 95.899, 'std_dev_duration_us': 2.207858184590643, 'min_duration_us': 93.814, 'max_duration_us': 105.121}]</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x288x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(96.56)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x288x64_MI16x...', 'stream': 0, 'mean_duration_us': 96.56}]</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -19321,12 +19365,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 360, 'total_duration_us': np.float64(6226.331), 'mean_duration_us': np.float64(17.29536388888889), 'median_duration_us': np.float64(15.795), 'std_dev_duration_us': np.float64(2.8259221431687647), 'min_duration_us': np.float64(12.067), 'max_duration_us': np.float64(23.693)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 360, 'total_duration_us': 6226.331, 'mean_duration_us': 17.29536388888889, 'median_duration_us': 15.795, 'std_dev_duration_us': 2.8259221431687647, 'min_duration_us': 12.067, 'max_duration_us': 23.693}]</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(17.3)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 17.3}]</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -19478,12 +19522,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 250, 'total_duration_us': np.float64(5090.484), 'mean_duration_us': np.float64(20.361936), 'median_duration_us': np.float64(20.165), 'std_dev_duration_us': np.float64(1.2402476574878099), 'min_duration_us': np.float64(18.0), 'max_duration_us': np.float64(28.384)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 250, 'total_duration_us': 5090.484, 'mean_duration_us': 20.361936, 'median_duration_us': 20.165, 'std_dev_duration_us': 1.2402476574878099, 'min_duration_us': 18.0, 'max_duration_us': 28.384}]</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(20.36)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': 20.36}]</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -19635,12 +19679,12 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(4463.737999999999), 'mean_duration_us': np.float64(37.19781666666666), 'median_duration_us': np.float64(37.084), 'std_dev_duration_us': np.float64(4.0768960782751815), 'min_duration_us': np.float64(28.985), 'max_duration_us': np.float64(50.435)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': 4463.737999999999, 'mean_duration_us': 37.19781666666666, 'median_duration_us': 37.084, 'std_dev_duration_us': 4.0768960782751815, 'min_duration_us': 28.985, 'max_duration_us': 50.435}]</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': np.float64(37.2)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': 37.2}]</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -19792,12 +19836,12 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(3529.13), 'mean_duration_us': np.float64(29.40941666666667), 'median_duration_us': np.float64(29.1055), 'std_dev_duration_us': np.float64(1.2255553202754885), 'min_duration_us': np.float64(27.703), 'max_duration_us': np.float64(33.035)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': 3529.13, 'mean_duration_us': 29.40941666666667, 'median_duration_us': 29.1055, 'std_dev_duration_us': 1.2255553202754885, 'min_duration_us': 27.703, 'max_duration_us': 33.035}]</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': np.float64(29.41)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': 29.41}]</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -19949,12 +19993,12 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(3008.275), 'mean_duration_us': np.float64(25.068958333333335), 'median_duration_us': np.float64(24.8965), 'std_dev_duration_us': np.float64(2.5754997003683036), 'min_duration_us': np.float64(19.765), 'max_duration_us': np.float64(33.957)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': 3008.275, 'mean_duration_us': 25.068958333333335, 'median_duration_us': 24.8965, 'std_dev_duration_us': 2.5754997003683036, 'min_duration_us': 19.765, 'max_duration_us': 33.957}]</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(25.07)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': 25.07}]</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -20106,12 +20150,12 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 245, 'total_duration_us': np.float64(2450.014), 'mean_duration_us': np.float64(10.000057142857143), 'median_duration_us': np.float64(9.942), 'std_dev_duration_us': np.float64(0.8502293788941274), 'min_duration_us': np.float64(8.218), 'max_duration_us': np.float64(13.429)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 245, 'total_duration_us': 2450.014, 'mean_duration_us': 10.000057142857143, 'median_duration_us': 9.942, 'std_dev_duration_us': 0.8502293788941274, 'min_duration_us': 8.218, 'max_duration_us': 13.429}]</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(10.0)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 10.0}]</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -20263,12 +20307,12 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(1979.3850000000002), 'mean_duration_us': np.float64(16.494875), 'median_duration_us': np.float64(16.216), 'std_dev_duration_us': np.float64(0.889071627809031), 'min_duration_us': np.float64(14.673), 'max_duration_us': np.float64(18.802)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 120, 'total_duration_us': 1979.3850000000002, 'mean_duration_us': 16.494875, 'median_duration_us': 16.216, 'std_dev_duration_us': 0.889071627809031, 'min_duration_us': 14.673, 'max_duration_us': 18.802}]</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(16.49)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 16.49}]</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -20420,12 +20464,12 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 240, 'total_duration_us': np.float64(1649.788), 'mean_duration_us': np.float64(6.874116666666667), 'median_duration_us': np.float64(6.895), 'std_dev_duration_us': np.float64(0.40092175428075183), 'min_duration_us': np.float64(5.812), 'max_duration_us': np.float64(8.979)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 240, 'total_duration_us': 1649.788, 'mean_duration_us': 6.874116666666667, 'median_duration_us': 6.895, 'std_dev_duration_us': 0.40092175428075183, 'min_duration_us': 5.812, 'max_duration_us': 8.979}]</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(6.87)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 6.87}]</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -20577,12 +20621,12 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(1138.047), 'mean_duration_us': np.float64(227.6094), 'median_duration_us': np.float64(225.036), 'std_dev_duration_us': np.float64(4.802322254909601), 'min_duration_us': np.float64(224.634), 'max_duration_us': np.float64(237.144)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 1138.047, 'mean_duration_us': 227.6094, 'median_duration_us': 225.036, 'std_dev_duration_us': 4.802322254909601, 'min_duration_us': 224.634, 'max_duration_us': 237.144}]</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(227.61)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 227.61}]</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -20734,12 +20778,12 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(1136.443), 'mean_duration_us': np.float64(227.2886), 'median_duration_us': np.float64(226.238), 'std_dev_duration_us': np.float64(2.4922390415046425), 'min_duration_us': np.float64(224.715), 'max_duration_us': np.float64(230.528)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 1136.443, 'mean_duration_us': 227.2886, 'median_duration_us': 226.238, 'std_dev_duration_us': 2.4922390415046425, 'min_duration_us': 224.715, 'max_duration_us': 230.528}]</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(227.29)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 227.29}]</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -20891,12 +20935,12 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 180, 'total_duration_us': np.float64(1058.8980000000001), 'mean_duration_us': np.float64(5.882766666666668), 'median_duration_us': np.float64(5.893), 'std_dev_duration_us': np.float64(0.3655466545691078), 'min_duration_us': np.float64(4.81), 'max_duration_us': np.float64(6.775)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 180, 'total_duration_us': 1058.8980000000001, 'mean_duration_us': 5.882766666666668, 'median_duration_us': 5.893, 'std_dev_duration_us': 0.3655466545691078, 'min_duration_us': 4.81, 'max_duration_us': 6.775}]</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(5.88)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 5.88}]</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -21048,12 +21092,12 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(898.455), 'mean_duration_us': np.float64(179.691), 'median_duration_us': np.float64(189.314), 'std_dev_duration_us': np.float64(29.36311296167353), 'min_duration_us': np.float64(122.118), 'max_duration_us': np.float64(204.147)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': 898.455, 'mean_duration_us': 179.691, 'median_duration_us': 189.314, 'std_dev_duration_us': 29.36311296167353, 'min_duration_us': 122.118, 'max_duration_us': 204.147}]</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(179.69)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': 179.69}]</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
@@ -21205,12 +21249,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(868.479), 'mean_duration_us': np.float64(7.237325), 'median_duration_us': np.float64(7.175), 'std_dev_duration_us': np.float64(0.5774263757181518), 'min_duration_us': np.float64(6.414), 'max_duration_us': np.float64(10.503)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': 868.479, 'mean_duration_us': 7.237325, 'median_duration_us': 7.175, 'std_dev_duration_us': 0.5774263757181518, 'min_duration_us': 6.414, 'max_duration_us': 10.503}]</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(7.24)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': 7.24}]</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -21362,12 +21406,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(848.183), 'mean_duration_us': np.float64(169.6366), 'median_duration_us': np.float64(169.549), 'std_dev_duration_us': np.float64(0.12531017516545753), 'min_duration_us': np.float64(169.508), 'max_duration_us': np.float64(169.789)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 848.183, 'mean_duration_us': 169.6366, 'median_duration_us': 169.549, 'std_dev_duration_us': 0.12531017516545753, 'min_duration_us': 169.508, 'max_duration_us': 169.789}]</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(169.64)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 169.64}]</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -21519,12 +21563,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 125, 'total_duration_us': np.float64(646.4359999999999), 'mean_duration_us': np.float64(5.171487999999999), 'median_duration_us': np.float64(5.13), 'std_dev_duration_us': np.float64(0.3605603331704697), 'min_duration_us': np.float64(4.409), 'max_duration_us': np.float64(6.293)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 125, 'total_duration_us': 646.4359999999999, 'mean_duration_us': 5.171487999999999, 'median_duration_us': 5.13, 'std_dev_duration_us': 0.3605603331704697, 'min_duration_us': 4.409, 'max_duration_us': 6.293}]</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(5.17)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': 5.17}]</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -21676,12 +21720,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_5_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 20, 'total_duration_us': np.float64(622.568), 'mean_duration_us': np.float64(31.1284), 'median_duration_us': np.float64(30.448999999999998), 'std_dev_duration_us': np.float64(1.3790227119231941), 'min_duration_us': np.float64(28.705), 'max_duration_us': np.float64(33.516)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_5_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 20, 'total_duration_us': 622.568, 'mean_duration_us': 31.1284, 'median_duration_us': 30.448999999999998, 'std_dev_duration_us': 1.3790227119231941, 'min_duration_us': 28.705, 'max_duration_us': 33.516}]</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(31.13)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x...', 'stream': 0, 'mean_duration_us': 31.13}]</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -21833,12 +21877,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 125, 'total_duration_us': np.float64(572.1489999999999), 'mean_duration_us': np.float64(4.577191999999999), 'median_duration_us': np.float64(4.489), 'std_dev_duration_us': np.float64(0.3315058659149187), 'min_duration_us': np.float64(4.048), 'max_duration_us': np.float64(5.452)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 125, 'total_duration_us': 572.1489999999999, 'mean_duration_us': 4.577191999999999, 'median_duration_us': 4.489, 'std_dev_duration_us': 0.3315058659149187, 'min_duration_us': 4.048, 'max_duration_us': 5.452}]</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.58)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.58}]</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
@@ -21990,12 +22034,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(555.2339999999999), 'mean_duration_us': np.float64(4.626949999999999), 'median_duration_us': np.float64(4.569), 'std_dev_duration_us': np.float64(0.3686557755323161), 'min_duration_us': np.float64(4.008), 'max_duration_us': np.float64(5.612)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 120, 'total_duration_us': 555.2339999999999, 'mean_duration_us': 4.626949999999999, 'median_duration_us': 4.569, 'std_dev_duration_us': 0.3686557755323161, 'min_duration_us': 4.008, 'max_duration_us': 5.612}]</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.63)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 4.63}]</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
@@ -22147,12 +22191,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>[{'name': 'Im2d2Col_v2', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(219.258), 'mean_duration_us': np.float64(43.851600000000005), 'median_duration_us': np.float64(44.621), 'std_dev_duration_us': np.float64(1.7498733211292758), 'min_duration_us': np.float64(40.372), 'max_duration_us': np.float64(45.063)}, {'name': 'Cijk_Ailk_Bljk_BBS_BH_MT64x64x64_MI16x16x16x1_SN_1LDSB0_APM1_ABV0_ACED0_AF0EM1_AF1EM1_AMAS0_ASE_ASGT_ASLT_ASM_ASAE01_ASCE01_ASEM1_AAC0_BL1_BS1_CLR1_DTLA0_DTLB0_DTVA0_DTVB0_DVO0_ETSP_EPS1_ELFLR0_EMLL0_FSSC10_FL0_GLVWA2_GLVWB8_GRCGA1_GRCGB1_GRPM1_GRVWn1_GSU1_GSUASB_GLS0_ISA942_IU1_K1_KLA_LBSPPA1024_LBSPPB128_LPA16_LPB16_LDL1_LRVW8_LWPMn1_LDW0_FMA_MIAV0_MDA2_MO40_MMFSC_MKFGSU256_NTA0_NTB0_NTC0_NTD0_NEPBS0_NLCA1_NLCB1_ONLL1_OPLV0_PK0_PAP0_PGR1_PLR5_PKA0_SIA3_SLW1_SS0_SU16_SUM0_SUS512_SCIUI1_SPO0_SRVW0_SSO0_SVW4_SNLL0_TSGRA0_TSGRB0_TT1_64_TLDS1_UMLDSA0_UMLDSB1_U64SL1_USFGROn1_VAW1_VSn1_VW1_VWB1_VFLRP1_WSGRA0_WSGRB0_WS64_WG64_4_1_WGMn16', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(298.64099999999996), 'mean_duration_us': np.float64(59.728199999999994), 'median_duration_us': np.float64(60.458), 'std_dev_duration_us': np.float64(1.7082119774782034), 'min_duration_us': np.float64(56.328), 'max_duration_us': np.float64(60.899)}]</t>
+          <t>[{'name': 'Im2d2Col_v2', 'stream': 0, 'count': 5, 'total_duration_us': 219.258, 'mean_duration_us': 43.851600000000005, 'median_duration_us': 44.621, 'std_dev_duration_us': 1.7498733211292758, 'min_duration_us': 40.372, 'max_duration_us': 45.063}, {'name': 'Cijk_Ailk_Bljk_BBS_BH_MT64x64x64_MI16x16x16x1_SN_1LDSB0_APM1_ABV0_ACED0_AF0EM1_AF1EM1_AMAS0_ASE_ASGT_ASLT_ASM_ASAE01_ASCE01_ASEM1_AAC0_BL1_BS1_CLR1_DTLA0_DTLB0_DTVA0_DTVB0_DVO0_ETSP_EPS1_ELFLR0_EMLL0_FSSC10_FL0_GLVWA2_GLVWB8_GRCGA1_GRCGB1_GRPM1_GRVWn1_GSU1_GSUASB_GLS0_ISA942_IU1_K1_KLA_LBSPPA1024_LBSPPB128_LPA16_LPB16_LDL1_LRVW8_LWPMn1_LDW0_FMA_MIAV0_MDA2_MO40_MMFSC_MKFGSU256_NTA0_NTB0_NTC0_NTD0_NEPBS0_NLCA1_NLCB1_ONLL1_OPLV0_PK0_PAP0_PGR1_PLR5_PKA0_SIA3_SLW1_SS0_SU16_SUM0_SUS512_SCIUI1_SPO0_SRVW0_SSO0_SVW4_SNLL0_TSGRA0_TSGRB0_TT1_64_TLDS1_UMLDSA0_UMLDSB1_U64SL1_USFGROn1_VAW1_VSn1_VW1_VWB1_VFLRP1_WSGRA0_WSGRB0_WS64_WG64_4_1_WGMn16', 'stream': 0, 'count': 5, 'total_duration_us': 298.64099999999996, 'mean_duration_us': 59.728199999999994, 'median_duration_us': 60.458, 'std_dev_duration_us': 1.7082119774782034, 'min_duration_us': 56.328, 'max_duration_us': 60.899}]</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>[{'name': 'Im2d2Col_v2', 'stream': 0, 'mean_duration_us': np.float64(43.85)}, {'name': 'Cijk_Ailk_Bljk_BBS_BH_MT64x64x64_MI16x16x16x1_SN_1LDSB0_APM1_ABV...', 'stream': 0, 'mean_duration_us': np.float64(59.73)}]</t>
+          <t>[{'name': 'Im2d2Col_v2', 'stream': 0, 'mean_duration_us': 43.85}, {'name': 'Cijk_Ailk_Bljk_BBS_BH_MT64x64x64_MI16x16x16x1_SN_1LDSB0_APM1_ABV...', 'stream': 0, 'mean_duration_us': 59.73}]</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
@@ -22304,12 +22348,12 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(514.482), 'mean_duration_us': np.float64(8.5747), 'median_duration_us': np.float64(8.6385), 'std_dev_duration_us': np.float64(0.3650420660691038), 'min_duration_us': np.float64(7.657), 'max_duration_us': np.float64(9.18)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': 514.482, 'mean_duration_us': 8.5747, 'median_duration_us': 8.6385, 'std_dev_duration_us': 0.3650420660691038, 'min_duration_us': 7.657, 'max_duration_us': 9.18}]</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(8.57)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 8.57}]</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
@@ -22461,12 +22505,12 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(419.266), 'mean_duration_us': np.float64(6.987766666666667), 'median_duration_us': np.float64(6.895), 'std_dev_duration_us': np.float64(0.5233797654561062), 'min_duration_us': np.float64(5.973), 'max_duration_us': np.float64(8.658)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': 419.266, 'mean_duration_us': 6.987766666666667, 'median_duration_us': 6.895, 'std_dev_duration_us': 0.5233797654561062, 'min_duration_us': 5.973, 'max_duration_us': 8.658}]</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(6.99)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 6.99}]</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
@@ -22618,12 +22662,12 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(401.82699999999994), 'mean_duration_us': np.float64(6.697116666666665), 'median_duration_us': np.float64(6.775), 'std_dev_duration_us': np.float64(0.31499709478378085), 'min_duration_us': np.float64(5.973), 'max_duration_us': np.float64(7.296)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 60, 'total_duration_us': 401.82699999999994, 'mean_duration_us': 6.697116666666665, 'median_duration_us': 6.775, 'std_dev_duration_us': 0.31499709478378085, 'min_duration_us': 5.973, 'max_duration_us': 7.296}]</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(6.7)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 6.7}]</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
@@ -22775,12 +22819,12 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(384.538), 'mean_duration_us': np.float64(6.408966666666667), 'median_duration_us': np.float64(6.273), 'std_dev_duration_us': np.float64(0.7107715049312417), 'min_duration_us': np.float64(5.091), 'max_duration_us': np.float64(8.659)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': 384.538, 'mean_duration_us': 6.408966666666667, 'median_duration_us': 6.273, 'std_dev_duration_us': 0.7107715049312417, 'min_duration_us': 5.091, 'max_duration_us': 8.659}]</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(6.41)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 6.41}]</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
@@ -22932,12 +22976,12 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(355.711), 'mean_duration_us': np.float64(5.928516666666667), 'median_duration_us': np.float64(5.812), 'std_dev_duration_us': np.float64(0.600517262912196), 'min_duration_us': np.float64(4.609), 'max_duration_us': np.float64(7.857)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': 355.711, 'mean_duration_us': 5.928516666666667, 'median_duration_us': 5.812, 'std_dev_duration_us': 0.600517262912196, 'min_duration_us': 4.609, 'max_duration_us': 7.857}]</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(5.93)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 5.93}]</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
@@ -23089,12 +23133,12 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 15, 'total_duration_us': np.float64(69.66600000000001), 'mean_duration_us': np.float64(4.644400000000001), 'median_duration_us': np.float64(4.689), 'std_dev_duration_us': np.float64(0.2239195688932374), 'min_duration_us': np.float64(4.248), 'max_duration_us': np.float64(5.01)}, {'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA1_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB4_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS0_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_1', 'stream': 0, 'count': 15, 'total_duration_us': np.float64(282.956), 'mean_duration_us': np.float64(18.863733333333336), 'median_duration_us': np.float64(17.158), 'std_dev_duration_us': np.float64(7.847680162244695), 'min_duration_us': np.float64(15.234), 'max_duration_us': np.float64(47.99)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 15, 'total_duration_us': 69.66600000000001, 'mean_duration_us': 4.644400000000001, 'median_duration_us': 4.689, 'std_dev_duration_us': 0.2239195688932374, 'min_duration_us': 4.248, 'max_duration_us': 5.01}, {'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA1_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB4_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS0_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_1', 'stream': 0, 'count': 15, 'total_duration_us': 282.956, 'mean_duration_us': 18.863733333333336, 'median_duration_us': 17.158, 'std_dev_duration_us': 7.847680162244695, 'min_duration_us': 15.234, 'max_duration_us': 47.99}]</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.64)}, {'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16...', 'stream': 0, 'mean_duration_us': np.float64(18.86)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 4.64}, {'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16...', 'stream': 0, 'mean_duration_us': 18.86}]</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
@@ -23246,12 +23290,12 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(308.848), 'mean_duration_us': np.float64(5.147466666666667), 'median_duration_us': np.float64(5.051), 'std_dev_duration_us': np.float64(0.35748615202394757), 'min_duration_us': np.float64(4.369), 'max_duration_us': np.float64(6.093)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': 308.848, 'mean_duration_us': 5.147466666666667, 'median_duration_us': 5.051, 'std_dev_duration_us': 0.35748615202394757, 'min_duration_us': 4.369, 'max_duration_us': 6.093}]</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': np.float64(5.15)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': 5.15}]</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
@@ -23373,12 +23417,12 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(294.65700000000004), 'mean_duration_us': np.float64(4.910950000000001), 'median_duration_us': np.float64(4.810499999999999), 'std_dev_duration_us': np.float64(0.34617815379753053), 'min_duration_us': np.float64(4.249), 'max_duration_us': np.float64(6.093)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)', 'stream': 0, 'count': 60, 'total_duration_us': 294.65700000000004, 'mean_duration_us': 4.910950000000001, 'median_duration_us': 4.810499999999999, 'std_dev_duration_us': 0.34617815379753053, 'min_duration_us': 4.249, 'max_duration_us': 6.093}]</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, ...', 'stream': 0, 'mean_duration_us': np.float64(4.91)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, ...', 'stream': 0, 'mean_duration_us': 4.91}]</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr"/>
@@ -23526,12 +23570,12 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(292.09), 'mean_duration_us': np.float64(4.868166666666666), 'median_duration_us': np.float64(4.77), 'std_dev_duration_us': np.float64(0.40604807460310527), 'min_duration_us': np.float64(4.128), 'max_duration_us': np.float64(5.852)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': 292.09, 'mean_duration_us': 4.868166666666666, 'median_duration_us': 4.77, 'std_dev_duration_us': 0.40604807460310527, 'min_duration_us': 4.128, 'max_duration_us': 5.852}]</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': np.float64(4.87)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': 4.87}]</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
@@ -23683,12 +23727,12 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(291.33199999999994), 'mean_duration_us': np.float64(4.855533333333332), 'median_duration_us': np.float64(4.73), 'std_dev_duration_us': np.float64(0.32905027309245954), 'min_duration_us': np.float64(4.289), 'max_duration_us': np.float64(5.532)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': 291.33199999999994, 'mean_duration_us': 4.855533333333332, 'median_duration_us': 4.73, 'std_dev_duration_us': 0.32905027309245954, 'min_duration_us': 4.289, 'max_duration_us': 5.532}]</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(4.86)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': 4.86}]</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
@@ -23840,12 +23884,12 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(291.32899999999995), 'mean_duration_us': np.float64(4.855483333333333), 'median_duration_us': np.float64(4.69), 'std_dev_duration_us': np.float64(0.34405471908145985), 'min_duration_us': np.float64(4.209), 'max_duration_us': np.float64(5.773)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': 291.32899999999995, 'mean_duration_us': 4.855483333333333, 'median_duration_us': 4.69, 'std_dev_duration_us': 0.34405471908145985, 'min_duration_us': 4.209, 'max_duration_us': 5.773}]</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(4.86)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': 4.86}]</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
@@ -23967,12 +24011,12 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 20, 'total_duration_us': np.float64(289.404), 'mean_duration_us': np.float64(14.4702), 'median_duration_us': np.float64(14.1715), 'std_dev_duration_us': np.float64(4.524248375144759), 'min_duration_us': np.float64(9.461), 'max_duration_us': np.float64(20.085)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 20, 'total_duration_us': 289.404, 'mean_duration_us': 14.4702, 'median_duration_us': 14.1715, 'std_dev_duration_us': 4.524248375144759, 'min_duration_us': 9.461, 'max_duration_us': 20.085}]</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Ge...', 'stream': 0, 'mean_duration_us': np.float64(14.47)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Ge...', 'stream': 0, 'mean_duration_us': 14.47}]</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr"/>
@@ -24090,12 +24134,12 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(149.136), 'mean_duration_us': np.float64(29.827199999999998), 'median_duration_us': np.float64(29.667), 'std_dev_duration_us': np.float64(0.5100754453999921), 'min_duration_us': np.float64(29.306), 'max_duration_us': np.float64(30.789)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'count': 5, 'total_duration_us': 149.136, 'mean_duration_us': 29.827199999999998, 'median_duration_us': 29.667, 'std_dev_duration_us': 0.5100754453999921, 'min_duration_us': 29.306, 'max_duration_us': 30.789}]</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 0, 'mean_duration_us': np.float64(29.83)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 0, 'mean_duration_us': 29.83}]</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr"/>
@@ -24243,12 +24287,12 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x64x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB4_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(136.148), 'mean_duration_us': np.float64(27.229599999999998), 'median_duration_us': np.float64(27.262), 'std_dev_duration_us': np.float64(0.7408710009171641), 'min_duration_us': np.float64(26.139), 'max_duration_us': np.float64(28.104)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x64x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB4_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 5, 'total_duration_us': 136.148, 'mean_duration_us': 27.229599999999998, 'median_duration_us': 27.262, 'std_dev_duration_us': 0.7408710009171641, 'min_duration_us': 26.139, 'max_duration_us': 28.104}]</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x64x64_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(27.23)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x64x64_MI16x1...', 'stream': 0, 'mean_duration_us': 27.23}]</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
@@ -24382,12 +24426,12 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 10, 'total_duration_us': np.float64(95.929), 'mean_duration_us': np.float64(9.5929), 'median_duration_us': np.float64(5.912), 'std_dev_duration_us': np.float64(9.921683712455259), 'min_duration_us': np.float64(4.049), 'max_duration_us': np.float64(38.407)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 10, 'total_duration_us': 95.929, 'mean_duration_us': 9.5929, 'median_duration_us': 5.912, 'std_dev_duration_us': 9.921683712455259, 'min_duration_us': 4.049, 'max_duration_us': 38.407}]</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(9.59)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': 9.59}]</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
@@ -24539,12 +24583,12 @@
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(90.724), 'mean_duration_us': np.float64(18.1448), 'median_duration_us': np.float64(18.241), 'std_dev_duration_us': np.float64(0.2411509071100502), 'min_duration_us': np.float64(17.72), 'max_duration_us': np.float64(18.441)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 5, 'total_duration_us': 90.724, 'mean_duration_us': 18.1448, 'median_duration_us': 18.241, 'std_dev_duration_us': 0.2411509071100502, 'min_duration_us': 17.72, 'max_duration_us': 18.441}]</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(18.14)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': 18.14}]</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
@@ -24666,12 +24710,12 @@
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(83.667), 'mean_duration_us': np.float64(16.7334), 'median_duration_us': np.float64(16.557), 'std_dev_duration_us': np.float64(0.8273663275720137), 'min_duration_us': np.float64(15.595), 'max_duration_us': np.float64(18.161)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 0, 'count': 5, 'total_duration_us': 83.667, 'mean_duration_us': 16.7334, 'median_duration_us': 16.557, 'std_dev_duration_us': 0.8273663275720137, 'min_duration_us': 15.595, 'max_duration_us': 18.161}]</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c1...', 'stream': 0, 'mean_duration_us': np.float64(16.73)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c1...', 'stream': 0, 'mean_duration_us': 16.73}]</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr"/>
@@ -24819,12 +24863,12 @@
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(75.429), 'mean_duration_us': np.float64(15.0858), 'median_duration_us': np.float64(14.823), 'std_dev_duration_us': np.float64(0.4742212142028235), 'min_duration_us': np.float64(14.603), 'max_duration_us': np.float64(15.755)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': 75.429, 'mean_duration_us': 15.0858, 'median_duration_us': 14.823, 'std_dev_duration_us': 0.4742212142028235, 'min_duration_us': 14.603, 'max_duration_us': 15.755}]</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(15.09)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': 15.09}]</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
@@ -24976,12 +25020,12 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA1_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB4_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS0_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_1', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(60.253), 'mean_duration_us': np.float64(12.0506), 'median_duration_us': np.float64(11.906), 'std_dev_duration_us': np.float64(0.49213477828741153), 'min_duration_us': np.float64(11.345), 'max_duration_us': np.float64(12.628)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA1_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB4_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS0_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_1', 'stream': 0, 'count': 5, 'total_duration_us': 60.253, 'mean_duration_us': 12.0506, 'median_duration_us': 11.906, 'std_dev_duration_us': 0.49213477828741153, 'min_duration_us': 11.345, 'max_duration_us': 12.628}]</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16...', 'stream': 0, 'mean_duration_us': np.float64(12.05)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16...', 'stream': 0, 'mean_duration_us': 12.05}]</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
@@ -25133,12 +25177,12 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(59.051), 'mean_duration_us': np.float64(11.8102), 'median_duration_us': np.float64(11.826), 'std_dev_duration_us': np.float64(0.3424951970466156), 'min_duration_us': np.float64(11.345), 'max_duration_us': np.float64(12.387)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 59.051, 'mean_duration_us': 11.8102, 'median_duration_us': 11.826, 'std_dev_duration_us': 0.3424951970466156, 'min_duration_us': 11.345, 'max_duration_us': 12.387}]</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(11.81)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 11.81}]</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
@@ -25290,12 +25334,12 @@
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(58.97), 'mean_duration_us': np.float64(11.794), 'median_duration_us': np.float64(5.772), 'std_dev_duration_us': np.float64(12.405547646113815), 'min_duration_us': np.float64(5.411), 'max_duration_us': np.float64(36.603)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': 58.97, 'mean_duration_us': 11.794, 'median_duration_us': 5.772, 'std_dev_duration_us': 12.405547646113815, 'min_duration_us': 5.411, 'max_duration_us': 36.603}]</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(11.79)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 11.79}]</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
@@ -25417,12 +25461,12 @@
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(55.763), 'mean_duration_us': np.float64(11.1526), 'median_duration_us': np.float64(5.171), 'std_dev_duration_us': np.float64(12.406593804908741), 'min_duration_us': np.float64(4.53), 'max_duration_us': np.float64(35.961)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::where_kernel_impl(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#3}::operator()() const::{lambda(bool, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 55.763, 'mean_duration_us': 11.1526, 'median_duration_us': 5.171, 'std_dev_duration_us': 12.406593804908741, 'min_duration_us': 4.53, 'max_duration_us': 35.961}]</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(11.15)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 11.15}]</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr"/>
@@ -25570,12 +25614,12 @@
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(49.509), 'mean_duration_us': np.float64(9.9018), 'median_duration_us': np.float64(9.662), 'std_dev_duration_us': np.float64(0.483819966516472), 'min_duration_us': np.float64(9.26), 'max_duration_us': np.float64(10.544)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 49.509, 'mean_duration_us': 9.9018, 'median_duration_us': 9.662, 'std_dev_duration_us': 0.483819966516472, 'min_duration_us': 9.26, 'max_duration_us': 10.544}]</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(9.9)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 9.9}]</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
@@ -25727,12 +25771,12 @@
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 10, 'total_duration_us': np.float64(49.504000000000005), 'mean_duration_us': np.float64(4.9504), 'median_duration_us': np.float64(5.091), 'std_dev_duration_us': np.float64(0.4543756595593562), 'min_duration_us': np.float64(4.088), 'max_duration_us': np.float64(5.491)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 10, 'total_duration_us': 49.504000000000005, 'mean_duration_us': 4.9504, 'median_duration_us': 5.091, 'std_dev_duration_us': 0.4543756595593562, 'min_duration_us': 4.088, 'max_duration_us': 5.491}]</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.95)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 4.95}]</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
@@ -25884,12 +25928,12 @@
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 10, 'total_duration_us': np.float64(48.14), 'mean_duration_us': np.float64(4.814), 'median_duration_us': np.float64(4.63), 'std_dev_duration_us': np.float64(0.7427319839619135), 'min_duration_us': np.float64(3.848), 'max_duration_us': np.float64(5.932)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 10, 'total_duration_us': 48.14, 'mean_duration_us': 4.814, 'median_duration_us': 4.63, 'std_dev_duration_us': 0.7427319839619135, 'min_duration_us': 3.848, 'max_duration_us': 5.932}]</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(4.81)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': 4.81}]</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
@@ -26041,12 +26085,12 @@
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bjlk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x16x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB1_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(47.143), 'mean_duration_us': np.float64(9.4286), 'median_duration_us': np.float64(9.14), 'std_dev_duration_us': np.float64(0.45920696858823895), 'min_duration_us': np.float64(8.94), 'max_duration_us': np.float64(10.062)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bjlk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x16x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB1_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 5, 'total_duration_us': 47.143, 'mean_duration_us': 9.4286, 'median_duration_us': 9.14, 'std_dev_duration_us': 0.45920696858823895, 'min_duration_us': 8.94, 'max_duration_us': 10.062}]</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bjlk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x16x128_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(9.43)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bjlk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x16x128_MI16x1...', 'stream': 0, 'mean_duration_us': 9.43}]</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
@@ -26194,12 +26238,12 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 10, 'total_duration_us': np.float64(42.248), 'mean_duration_us': np.float64(4.2248), 'median_duration_us': np.float64(4.148999999999999), 'std_dev_duration_us': np.float64(0.4044254690298325), 'min_duration_us': np.float64(3.808), 'max_duration_us': np.float64(5.292)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 10, 'total_duration_us': 42.248, 'mean_duration_us': 4.2248, 'median_duration_us': 4.148999999999999, 'std_dev_duration_us': 0.4044254690298325, 'min_duration_us': 3.808, 'max_duration_us': 5.292}]</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(4.22)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': 4.22}]</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
@@ -26321,12 +26365,12 @@
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4, 4&gt; &gt;(at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(37.763000000000005), 'mean_duration_us': np.float64(7.552600000000001), 'median_duration_us': np.float64(7.457), 'std_dev_duration_us': np.float64(0.2960490499900313), 'min_duration_us': np.float64(7.256), 'max_duration_us': np.float64(8.057)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4, 4&gt; &gt;(at::native::ReduceOp&lt;int, at::native::ArgMaxOps&lt;int&gt;, unsigned int, long, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 37.763000000000005, 'mean_duration_us': 7.552600000000001, 'median_duration_us': 7.457, 'std_dev_duration_us': 0.2960490499900313, 'min_duration_us': 7.256, 'max_duration_us': 8.057}]</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int,...', 'stream': 0, 'mean_duration_us': np.float64(7.55)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;int,...', 'stream': 0, 'mean_duration_us': 7.55}]</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr"/>
@@ -26444,12 +26488,12 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::index_elementwise_kernel&lt;128, 4, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1}&gt;(long, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(32.910000000000004), 'mean_duration_us': np.float64(6.582000000000001), 'median_duration_us': np.float64(6.655), 'std_dev_duration_us': np.float64(0.26174949856685475), 'min_duration_us': np.float64(6.253), 'max_duration_us': np.float64(6.975)}]</t>
+          <t>[{'name': 'void at::native::index_elementwise_kernel&lt;128, 4, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1}&gt;(long, at::native::gpu_index_kernel&lt;at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1}&gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;, at::native::index_kernel_impl&lt;at::native::OpaqueType&lt;2&gt; &gt;(at::TensorIteratorBase&amp;, c10::ArrayRef&lt;long&gt;, c10::ArrayRef&lt;long&gt;)::{lambda(char*, char const*, long)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 32.910000000000004, 'mean_duration_us': 6.582000000000001, 'median_duration_us': 6.655, 'std_dev_duration_us': 0.26174949856685475, 'min_duration_us': 6.253, 'max_duration_us': 6.975}]</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::index_elementwise_kernel&lt;128, 4, at::native::gp...', 'stream': 0, 'mean_duration_us': np.float64(6.58)}]</t>
+          <t>[{'name': 'void at::native::index_elementwise_kernel&lt;128, 4, at::native::gp...', 'stream': 0, 'mean_duration_us': 6.58}]</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr"/>
@@ -26597,12 +26641,12 @@
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(32.149), 'mean_duration_us': np.float64(6.4298), 'median_duration_us': np.float64(6.414), 'std_dev_duration_us': np.float64(0.32155770866206873), 'min_duration_us': np.float64(5.892), 'max_duration_us': np.float64(6.895)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 32.149, 'mean_duration_us': 6.4298, 'median_duration_us': 6.414, 'std_dev_duration_us': 0.32155770866206873, 'min_duration_us': 5.892, 'max_duration_us': 6.895}]</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(6.43)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': 6.43}]</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
@@ -26724,12 +26768,12 @@
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(31.827999999999996), 'mean_duration_us': np.float64(6.365599999999999), 'median_duration_us': np.float64(6.334), 'std_dev_duration_us': np.float64(0.16319877450520262), 'min_duration_us': np.float64(6.173), 'max_duration_us': np.float64(6.574)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)', 'stream': 0, 'count': 5, 'total_duration_us': 31.827999999999996, 'mean_duration_us': 6.365599999999999, 'median_duration_us': 6.334, 'std_dev_duration_us': 0.16319877450520262, 'min_duration_us': 6.173, 'max_duration_us': 6.574}]</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c1...', 'stream': 0, 'mean_duration_us': np.float64(6.37)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c1...', 'stream': 0, 'mean_duration_us': 6.37}]</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr"/>
@@ -26877,12 +26921,12 @@
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(31.067), 'mean_duration_us': np.float64(6.2134), 'median_duration_us': np.float64(6.093), 'std_dev_duration_us': np.float64(0.28699937282161453), 'min_duration_us': np.float64(6.013), 'max_duration_us': np.float64(6.775)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': 31.067, 'mean_duration_us': 6.2134, 'median_duration_us': 6.093, 'std_dev_duration_us': 0.28699937282161453, 'min_duration_us': 6.013, 'max_duration_us': 6.775}]</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(6.21)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 6.21}]</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
@@ -27034,12 +27078,12 @@
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(30.145000000000003), 'mean_duration_us': np.float64(6.029000000000001), 'median_duration_us': np.float64(6.093), 'std_dev_duration_us': np.float64(0.2632732420888988), 'min_duration_us': np.float64(5.652), 'max_duration_us': np.float64(6.374)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': 30.145000000000003, 'mean_duration_us': 6.029000000000001, 'median_duration_us': 6.093, 'std_dev_duration_us': 0.2632732420888988, 'min_duration_us': 5.652, 'max_duration_us': 6.374}]</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(6.03)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 6.03}]</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
@@ -27161,12 +27205,12 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(28.06), 'mean_duration_us': np.float64(5.612), 'median_duration_us': np.float64(5.572), 'std_dev_duration_us': np.float64(0.10158936952260311), 'min_duration_us': np.float64(5.492), 'max_duration_us': np.float64(5.733)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, long)', 'stream': 0, 'count': 5, 'total_duration_us': 28.06, 'mean_duration_us': 5.612, 'median_duration_us': 5.572, 'std_dev_duration_us': 0.10158936952260311, 'min_duration_us': 5.492, 'max_duration_us': 5.733}]</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c1...', 'stream': 0, 'mean_duration_us': np.float64(5.61)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectSmallIndex&lt;c1...', 'stream': 0, 'mean_duration_us': 5.61}]</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr"/>
@@ -27314,12 +27358,12 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(27.898), 'mean_duration_us': np.float64(5.5796), 'median_duration_us': np.float64(5.572), 'std_dev_duration_us': np.float64(0.0162061716639064), 'min_duration_us': np.float64(5.571), 'max_duration_us': np.float64(5.612)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 27.898, 'mean_duration_us': 5.5796, 'median_duration_us': 5.572, 'std_dev_duration_us': 0.0162061716639064, 'min_duration_us': 5.571, 'max_duration_us': 5.612}]</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(5.58)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 5.58}]</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
@@ -27453,12 +27497,12 @@
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(26.455), 'mean_duration_us': np.float64(5.2909999999999995), 'median_duration_us': np.float64(5.251), 'std_dev_duration_us': np.float64(0.30444835358398653), 'min_duration_us': np.float64(4.93), 'max_duration_us': np.float64(5.732)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 26.455, 'mean_duration_us': 5.2909999999999995, 'median_duration_us': 5.251, 'std_dev_duration_us': 0.30444835358398653, 'min_duration_us': 4.93, 'max_duration_us': 5.732}]</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(5.29)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 5.29}]</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
@@ -27592,12 +27636,12 @@
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(25.814), 'mean_duration_us': np.float64(5.1628), 'median_duration_us': np.float64(5.171), 'std_dev_duration_us': np.float64(0.1816726726835932), 'min_duration_us': np.float64(4.89), 'max_duration_us': np.float64(5.451)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 25.814, 'mean_duration_us': 5.1628, 'median_duration_us': 5.171, 'std_dev_duration_us': 0.1816726726835932, 'min_duration_us': 4.89, 'max_duration_us': 5.451}]</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(5.16)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 5.16}]</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
@@ -27719,12 +27763,12 @@
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(25.654999999999998), 'mean_duration_us': np.float64(5.130999999999999), 'median_duration_us': np.float64(5.371), 'std_dev_duration_us': np.float64(0.43609265070624603), 'min_duration_us': np.float64(4.61), 'max_duration_us': np.float64(5.652)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnOther_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 25.654999999999998, 'mean_duration_us': 5.130999999999999, 'median_duration_us': 5.371, 'std_dev_duration_us': 0.43609265070624603, 'min_duration_us': 4.61, 'max_duration_us': 5.652}]</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(5.13)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 5.13}]</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr"/>
@@ -27872,12 +27916,12 @@
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(25.655), 'mean_duration_us': np.float64(5.131), 'median_duration_us': np.float64(5.131), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(5.131), 'max_duration_us': np.float64(5.131)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 25.655, 'mean_duration_us': 5.131, 'median_duration_us': 5.131, 'std_dev_duration_us': 0.0, 'min_duration_us': 5.131, 'max_duration_us': 5.131}]</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(5.13)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 5.13}]</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
@@ -28029,12 +28073,12 @@
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(25.093000000000004), 'mean_duration_us': np.float64(5.018600000000001), 'median_duration_us': np.float64(5.051), 'std_dev_duration_us': np.float64(0.09307330444332598), 'min_duration_us': np.float64(4.89), 'max_duration_us': np.float64(5.131)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 0, 'count': 5, 'total_duration_us': 25.093000000000004, 'mean_duration_us': 5.018600000000001, 'median_duration_us': 5.051, 'std_dev_duration_us': 0.09307330444332598, 'min_duration_us': 4.89, 'max_duration_us': 5.131}]</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(5.02)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': 5.02}]</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
@@ -28156,12 +28200,12 @@
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(24.689999999999998), 'mean_duration_us': np.float64(4.938), 'median_duration_us': np.float64(5.05), 'std_dev_duration_us': np.float64(0.26999333325102687), 'min_duration_us': np.float64(4.449), 'max_duration_us': np.float64(5.251)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 24.689999999999998, 'mean_duration_us': 4.938, 'median_duration_us': 5.05, 'std_dev_duration_us': 0.26999333325102687, 'min_duration_us': 4.449, 'max_duration_us': 5.251}]</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 0, 'mean_duration_us': np.float64(4.94)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 0, 'mean_duration_us': 4.94}]</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr"/>
@@ -28309,12 +28353,12 @@
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(24.21), 'mean_duration_us': np.float64(4.8420000000000005), 'median_duration_us': np.float64(4.529), 'std_dev_duration_us': np.float64(0.4251691428125987), 'min_duration_us': np.float64(4.489), 'max_duration_us': np.float64(5.491)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 24.21, 'mean_duration_us': 4.8420000000000005, 'median_duration_us': 4.529, 'std_dev_duration_us': 0.4251691428125987, 'min_duration_us': 4.489, 'max_duration_us': 5.491}]</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 0, 'mean_duration_us': np.float64(4.84)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 0, 'mean_duration_us': 4.84}]</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
@@ -28462,12 +28506,12 @@
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(24.131), 'mean_duration_us': np.float64(4.8262), 'median_duration_us': np.float64(4.69), 'std_dev_duration_us': np.float64(0.2316759806281177), 'min_duration_us': np.float64(4.61), 'max_duration_us': np.float64(5.251)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 24.131, 'mean_duration_us': 4.8262, 'median_duration_us': 4.69, 'std_dev_duration_us': 0.2316759806281177, 'min_duration_us': 4.61, 'max_duration_us': 5.251}]</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.83)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.83}]</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
@@ -28589,12 +28633,12 @@
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(24.051000000000002), 'mean_duration_us': np.float64(4.8102), 'median_duration_us': np.float64(4.73), 'std_dev_duration_us': np.float64(0.2619926716532353), 'min_duration_us': np.float64(4.53), 'max_duration_us': np.float64(5.211)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::exp_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 24.051000000000002, 'mean_duration_us': 4.8102, 'median_duration_us': 4.73, 'std_dev_duration_us': 0.2619926716532353, 'min_duration_us': 4.53, 'max_duration_us': 5.211}]</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::ex...', 'stream': 0, 'mean_duration_us': np.float64(4.81)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::ex...', 'stream': 0, 'mean_duration_us': 4.81}]</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr"/>
@@ -28742,12 +28786,12 @@
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(24.011000000000003), 'mean_duration_us': np.float64(4.802200000000001), 'median_duration_us': np.float64(4.57), 'std_dev_duration_us': np.float64(0.5108465131524341), 'min_duration_us': np.float64(4.41), 'max_duration_us': np.float64(5.812)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 24.011000000000003, 'mean_duration_us': 4.802200000000001, 'median_duration_us': 4.57, 'std_dev_duration_us': 0.5108465131524341, 'min_duration_us': 4.41, 'max_duration_us': 5.812}]</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': np.float64(4.8)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': 4.8}]</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
@@ -28899,12 +28943,12 @@
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.931), 'mean_duration_us': np.float64(4.7862), 'median_duration_us': np.float64(4.61), 'std_dev_duration_us': np.float64(0.5367853947342459), 'min_duration_us': np.float64(4.249), 'max_duration_us': np.float64(5.812)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 23.931, 'mean_duration_us': 4.7862, 'median_duration_us': 4.61, 'std_dev_duration_us': 0.5367853947342459, 'min_duration_us': 4.249, 'max_duration_us': 5.812}]</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.79)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 4.79}]</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
@@ -29056,12 +29100,12 @@
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.85), 'mean_duration_us': np.float64(4.7700000000000005), 'median_duration_us': np.float64(4.61), 'std_dev_duration_us': np.float64(0.3218459258713711), 'min_duration_us': np.float64(4.449), 'max_duration_us': np.float64(5.251)}]</t>
+          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': 23.85, 'mean_duration_us': 4.7700000000000005, 'median_duration_us': 4.61, 'std_dev_duration_us': 0.3218459258713711, 'min_duration_us': 4.449, 'max_duration_us': 5.251}]</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(4.77)}]</t>
+          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'mean_duration_us': 4.77}]</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
@@ -29183,12 +29227,12 @@
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.769), 'mean_duration_us': np.float64(4.7538), 'median_duration_us': np.float64(4.931), 'std_dev_duration_us': np.float64(0.25055570238970815), 'min_duration_us': np.float64(4.409), 'max_duration_us': np.float64(4.97)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; &gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::CompareFunctor&lt;long&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 23.769, 'mean_duration_us': 4.7538, 'median_duration_us': 4.931, 'std_dev_duration_us': 0.25055570238970815, 'min_duration_us': 4.409, 'max_duration_us': 4.97}]</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.75)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 4.75}]</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr"/>
@@ -29336,12 +29380,12 @@
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.769), 'mean_duration_us': np.float64(4.7538), 'median_duration_us': np.float64(4.57), 'std_dev_duration_us': np.float64(0.2427059125773412), 'min_duration_us': np.float64(4.529), 'max_duration_us': np.float64(5.051)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2})', 'stream': 0, 'count': 5, 'total_duration_us': 23.769, 'mean_duration_us': 4.7538, 'median_duration_us': 4.57, 'std_dev_duration_us': 0.2427059125773412, 'min_duration_us': 4.529, 'max_duration_us': 5.051}]</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(4.75)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 4.75}]</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
@@ -29463,12 +29507,12 @@
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.568), 'mean_duration_us': np.float64(4.7136000000000005), 'median_duration_us': np.float64(4.489), 'std_dev_duration_us': np.float64(0.35368324811899154), 'min_duration_us': np.float64(4.329), 'max_duration_us': np.float64(5.251)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::compare_scalar_kernel&lt;long&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::OpType, long)::{lambda(long)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 23.568, 'mean_duration_us': 4.7136000000000005, 'median_duration_us': 4.489, 'std_dev_duration_us': 0.35368324811899154, 'min_duration_us': 4.329, 'max_duration_us': 5.251}]</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::co...', 'stream': 0, 'mean_duration_us': np.float64(4.71)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::co...', 'stream': 0, 'mean_duration_us': 4.71}]</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr"/>
@@ -29616,12 +29660,12 @@
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.368999999999996), 'mean_duration_us': np.float64(4.673799999999999), 'median_duration_us': np.float64(4.73), 'std_dev_duration_us': np.float64(0.19056169604618856), 'min_duration_us': np.float64(4.449), 'max_duration_us': np.float64(4.89)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 23.368999999999996, 'mean_duration_us': 4.673799999999999, 'median_duration_us': 4.73, 'std_dev_duration_us': 0.19056169604618856, 'min_duration_us': 4.449, 'max_duration_us': 4.89}]</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(4.67)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 4.67}]</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
@@ -29743,12 +29787,12 @@
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.25), 'mean_duration_us': np.float64(4.65), 'median_duration_us': np.float64(4.61), 'std_dev_duration_us': np.float64(0.13908414719154719), 'min_duration_us': np.float64(4.489), 'max_duration_us': np.float64(4.851)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#7}::operator()() const::{lambda(float, bool)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 23.25, 'mean_duration_us': 4.65, 'median_duration_us': 4.61, 'std_dev_duration_us': 0.13908414719154719, 'min_duration_us': 4.489, 'max_duration_us': 4.851}]</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 0, 'mean_duration_us': np.float64(4.65)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 0, 'mean_duration_us': 4.65}]</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr"/>
@@ -29896,12 +29940,12 @@
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.21), 'mean_duration_us': np.float64(4.642), 'median_duration_us': np.float64(4.57), 'std_dev_duration_us': np.float64(0.28190920524168783), 'min_duration_us': np.float64(4.329), 'max_duration_us': np.float64(5.011)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 23.21, 'mean_duration_us': 4.642, 'median_duration_us': 4.57, 'std_dev_duration_us': 0.28190920524168783, 'min_duration_us': 4.329, 'max_duration_us': 5.011}]</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.64)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.64}]</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
@@ -30053,12 +30097,12 @@
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.167), 'mean_duration_us': np.float64(4.6334), 'median_duration_us': np.float64(4.489), 'std_dev_duration_us': np.float64(0.36638482501326386), 'min_duration_us': np.float64(4.128), 'max_duration_us': np.float64(5.131)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 23.167, 'mean_duration_us': 4.6334, 'median_duration_us': 4.489, 'std_dev_duration_us': 0.36638482501326386, 'min_duration_us': 4.128, 'max_duration_us': 5.131}]</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.63)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.63}]</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
@@ -30180,12 +30224,12 @@
       </c>
       <c r="AL81" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.088), 'mean_duration_us': np.float64(4.6176), 'median_duration_us': np.float64(4.489), 'std_dev_duration_us': np.float64(0.2929693499327193), 'min_duration_us': np.float64(4.369), 'max_duration_us': np.float64(5.171)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 0, 'count': 5, 'total_duration_us': 23.088, 'mean_duration_us': 4.6176, 'median_duration_us': 4.489, 'std_dev_duration_us': 0.2929693499327193, 'min_duration_us': 4.369, 'max_duration_us': 5.171}]</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 0, 'mean_duration_us': np.float64(4.62)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 0, 'mean_duration_us': 4.62}]</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr"/>
@@ -30333,12 +30377,12 @@
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.087000000000003), 'mean_duration_us': np.float64(4.617400000000001), 'median_duration_us': np.float64(4.569), 'std_dev_duration_us': np.float64(0.2909203327373321), 'min_duration_us': np.float64(4.328), 'max_duration_us': np.float64(5.171)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 23.087000000000003, 'mean_duration_us': 4.617400000000001, 'median_duration_us': 4.569, 'std_dev_duration_us': 0.2909203327373321, 'min_duration_us': 4.328, 'max_duration_us': 5.171}]</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.62)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.62}]</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
@@ -30490,12 +30534,12 @@
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(22.929000000000002), 'mean_duration_us': np.float64(4.585800000000001), 'median_duration_us': np.float64(3.647), 'std_dev_duration_us': np.float64(2.16479425350309), 'min_duration_us': np.float64(2.525), 'max_duration_us': np.float64(8.739)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 22.929000000000002, 'mean_duration_us': 4.585800000000001, 'median_duration_us': 3.647, 'std_dev_duration_us': 2.16479425350309, 'min_duration_us': 2.525, 'max_duration_us': 8.739}]</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(4.59)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 4.59}]</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
@@ -30647,12 +30691,12 @@
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(22.928), 'mean_duration_us': np.float64(4.5856), 'median_duration_us': np.float64(4.329), 'std_dev_duration_us': np.float64(0.4130828488330158), 'min_duration_us': np.float64(4.169), 'max_duration_us': np.float64(5.291)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 22.928, 'mean_duration_us': 4.5856, 'median_duration_us': 4.329, 'std_dev_duration_us': 0.4130828488330158, 'min_duration_us': 4.169, 'max_duration_us': 5.291}]</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(4.59)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 4.59}]</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
@@ -30774,12 +30818,12 @@
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(22.646), 'mean_duration_us': np.float64(4.5292), 'median_duration_us': np.float64(4.649), 'std_dev_duration_us': np.float64(0.24465600340069316), 'min_duration_us': np.float64(4.088), 'max_duration_us': np.float64(4.77)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;c10::BFloat16&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 22.646, 'mean_duration_us': 4.5292, 'median_duration_us': 4.649, 'std_dev_duration_us': 0.24465600340069316, 'min_duration_us': 4.088, 'max_duration_us': 4.77}]</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Fi...', 'stream': 0, 'mean_duration_us': np.float64(4.53)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Fi...', 'stream': 0, 'mean_duration_us': 4.53}]</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr"/>
@@ -30927,12 +30971,12 @@
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(22.487000000000002), 'mean_duration_us': np.float64(4.497400000000001), 'median_duration_us': np.float64(4.369), 'std_dev_duration_us': np.float64(0.3635748066079388), 'min_duration_us': np.float64(4.048), 'max_duration_us': np.float64(5.131)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 22.487000000000002, 'mean_duration_us': 4.497400000000001, 'median_duration_us': 4.369, 'std_dev_duration_us': 0.3635748066079388, 'min_duration_us': 4.048, 'max_duration_us': 5.131}]</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.5)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.5}]</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
@@ -31054,12 +31098,12 @@
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(22.485999999999997), 'mean_duration_us': np.float64(4.497199999999999), 'median_duration_us': np.float64(4.449), 'std_dev_duration_us': np.float64(0.331947827225906), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(4.89)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 0, 'count': 5, 'total_duration_us': 22.485999999999997, 'mean_duration_us': 4.497199999999999, 'median_duration_us': 4.449, 'std_dev_duration_us': 0.331947827225906, 'min_duration_us': 3.968, 'max_duration_us': 4.89}]</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 0, 'mean_duration_us': np.float64(4.5)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 0, 'mean_duration_us': 4.5}]</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr"/>
@@ -31177,12 +31221,12 @@
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(22.366), 'mean_duration_us': np.float64(4.4732), 'median_duration_us': np.float64(4.369), 'std_dev_duration_us': np.float64(0.19400659782595026), 'min_duration_us': np.float64(4.289), 'max_duration_us': np.float64(4.81)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::(anonymous namespace)::masked_fill_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16, bool)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 22.366, 'mean_duration_us': 4.4732, 'median_duration_us': 4.369, 'std_dev_duration_us': 0.19400659782595026, 'min_duration_us': 4.289, 'max_duration_us': 4.81}]</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(a...', 'stream': 0, 'mean_duration_us': np.float64(4.47)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(a...', 'stream': 0, 'mean_duration_us': 4.47}]</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr"/>
@@ -31300,12 +31344,12 @@
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(21.964), 'mean_duration_us': np.float64(4.392799999999999), 'median_duration_us': np.float64(4.449), 'std_dev_duration_us': np.float64(0.24247424605512233), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(4.689)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::elu_kernel(at::TensorIteratorBase&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 21.964, 'mean_duration_us': 4.392799999999999, 'median_duration_us': 4.449, 'std_dev_duration_us': 0.24247424605512233, 'min_duration_us': 3.968, 'max_duration_us': 4.689}]</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(a...', 'stream': 0, 'mean_duration_us': np.float64(4.39)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(a...', 'stream': 0, 'mean_duration_us': 4.39}]</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr"/>
@@ -31453,12 +31497,12 @@
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(21.884999999999998), 'mean_duration_us': np.float64(4.377), 'median_duration_us': np.float64(4.329), 'std_dev_duration_us': np.float64(0.3979557764375334), 'min_duration_us': np.float64(3.848), 'max_duration_us': np.float64(4.97)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 21.884999999999998, 'mean_duration_us': 4.377, 'median_duration_us': 4.329, 'std_dev_duration_us': 0.3979557764375334, 'min_duration_us': 3.848, 'max_duration_us': 4.97}]</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': np.float64(4.38)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': 4.38}]</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
@@ -31580,12 +31624,12 @@
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(21.845), 'mean_duration_us': np.float64(4.369), 'median_duration_us': np.float64(4.288), 'std_dev_duration_us': np.float64(0.39618329091469784), 'min_duration_us': np.float64(3.888), 'max_duration_us': np.float64(5.091)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt; const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 21.845, 'mean_duration_us': 4.369, 'median_duration_us': 4.288, 'std_dev_duration_us': 0.39618329091469784, 'min_duration_us': 3.888, 'max_duration_us': 5.091}]</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(4.37)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 4.37}]</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr"/>
@@ -31733,12 +31777,12 @@
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(21.323), 'mean_duration_us': np.float64(4.2646), 'median_duration_us': np.float64(4.248), 'std_dev_duration_us': np.float64(0.1855506399881175), 'min_duration_us': np.float64(3.968), 'max_duration_us': np.float64(4.529)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::NormTwoOps&lt;c10::BFloat16, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 21.323, 'mean_duration_us': 4.2646, 'median_duration_us': 4.248, 'std_dev_duration_us': 0.1855506399881175, 'min_duration_us': 3.968, 'max_duration_us': 4.529}]</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(4.26)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': 4.26}]</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
@@ -31890,12 +31934,12 @@
       </c>
       <c r="AL93" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(17.916), 'mean_duration_us': np.float64(3.5832), 'median_duration_us': np.float64(3.407), 'std_dev_duration_us': np.float64(0.6221727734319463), 'min_duration_us': np.float64(2.886), 'max_duration_us': np.float64(4.609)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 17.916, 'mean_duration_us': 3.5832, 'median_duration_us': 3.407, 'std_dev_duration_us': 0.6221727734319463, 'min_duration_us': 2.886, 'max_duration_us': 4.609}]</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(3.58)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 3.58}]</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
@@ -32047,12 +32091,12 @@
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(15.99), 'mean_duration_us': np.float64(3.198), 'median_duration_us': np.float64(3.126), 'std_dev_duration_us': np.float64(0.3572125417731018), 'min_duration_us': np.float64(2.765), 'max_duration_us': np.float64(3.687)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 15.99, 'mean_duration_us': 3.198, 'median_duration_us': 3.126, 'std_dev_duration_us': 0.3572125417731018, 'min_duration_us': 2.765, 'max_duration_us': 3.687}]</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': np.float64(3.2)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': 3.2}]</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
@@ -32204,12 +32248,12 @@
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(15.951), 'mean_duration_us': np.float64(3.1902), 'median_duration_us': np.float64(3.006), 'std_dev_duration_us': np.float64(0.5261100265153668), 'min_duration_us': np.float64(2.605), 'max_duration_us': np.float64(3.928)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 15.951, 'mean_duration_us': 3.1902, 'median_duration_us': 3.006, 'std_dev_duration_us': 0.5261100265153668, 'min_duration_us': 2.605, 'max_duration_us': 3.928}]</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(3.19)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 3.19}]</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
@@ -32361,12 +32405,12 @@
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(15.391), 'mean_duration_us': np.float64(3.0782), 'median_duration_us': np.float64(2.926), 'std_dev_duration_us': np.float64(0.3955605642629204), 'min_duration_us': np.float64(2.726), 'max_duration_us': np.float64(3.848)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 15.391, 'mean_duration_us': 3.0782, 'median_duration_us': 2.926, 'std_dev_duration_us': 0.3955605642629204, 'min_duration_us': 2.726, 'max_duration_us': 3.848}]</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(3.08)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 3.08}]</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
@@ -32518,12 +32562,12 @@
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(15.030000000000001), 'mean_duration_us': np.float64(3.0060000000000002), 'median_duration_us': np.float64(2.926), 'std_dev_duration_us': np.float64(0.3119506371206829), 'min_duration_us': np.float64(2.725), 'max_duration_us': np.float64(3.568)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 15.030000000000001, 'mean_duration_us': 3.0060000000000002, 'median_duration_us': 2.926, 'std_dev_duration_us': 0.3119506371206829, 'min_duration_us': 2.725, 'max_duration_us': 3.568}]</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(3.01)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 3.01}]</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
@@ -32556,207 +32600,207 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>param: M</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>param: N</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>param: K</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>param: bias</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>param: stride_A</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>param: stride_B</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>param: dtype_A_B</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>param: B</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>param: transpose</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>process_name_first</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>process_label_first</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>thread_name_first</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -32874,12 +32918,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x288x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA32_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_9_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(55056.329), 'mean_duration_us': np.float64(458.80274166666663), 'median_duration_us': np.float64(459.394), 'std_dev_duration_us': np.float64(39.331859811628505), 'min_duration_us': np.float64(399.316), 'max_duration_us': np.float64(559.804)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x288x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB128_LBSPPM0_LPA32_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT2_9_MO40_NTn1_NTA0_NTB4_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW2_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA2_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': 55056.329, 'mean_duration_us': 458.80274166666663, 'median_duration_us': 459.394, 'std_dev_duration_us': 39.331859811628505, 'min_duration_us': 399.316, 'max_duration_us': 559.804}]</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x288x64_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(458.8)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x288x64_MI16x1...', 'stream': 0, 'mean_duration_us': 458.8}]</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -33039,12 +33083,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB256_LBSPPM0_LPA4_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(40460.247), 'mean_duration_us': np.float64(337.16872500000005), 'median_duration_us': np.float64(331.821), 'std_dev_duration_us': np.float64(11.541609001032239), 'min_duration_us': np.float64(322.5), 'max_duration_us': np.float64(377.545)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x32_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB256_LBSPPM0_LPA4_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': 40460.247, 'mean_duration_us': 337.16872500000005, 'median_duration_us': 331.821, 'std_dev_duration_us': 11.541609001032239, 'min_duration_us': 322.5, 'max_duration_us': 377.545}]</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x32_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(337.17)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x32_MI16x...', 'stream': 0, 'mean_duration_us': 337.17}]</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -33204,12 +33248,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_5_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 480, 'total_duration_us': np.float64(15205.791000000001), 'mean_duration_us': np.float64(31.678731250000002), 'median_duration_us': np.float64(31.2305), 'std_dev_duration_us': np.float64(1.291014259160901), 'min_duration_us': np.float64(29.667), 'max_duration_us': np.float64(38.488)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_5_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 480, 'total_duration_us': 15205.791000000001, 'mean_duration_us': 31.678731250000002, 'median_duration_us': 31.2305, 'std_dev_duration_us': 1.291014259160901, 'min_duration_us': 29.667, 'max_duration_us': 38.488}]</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(31.68)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x...', 'stream': 0, 'mean_duration_us': 31.68}]</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -33369,12 +33413,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT160x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT5_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(12190.582999999999), 'mean_duration_us': np.float64(101.58819166666666), 'median_duration_us': np.float64(101.071), 'std_dev_duration_us': np.float64(2.68756934575908), 'min_duration_us': np.float64(96.981), 'max_duration_us': np.float64(110.813)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT160x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT5_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': 12190.582999999999, 'mean_duration_us': 101.58819166666666, 'median_duration_us': 101.071, 'std_dev_duration_us': 2.68756934575908, 'min_duration_us': 96.981, 'max_duration_us': 110.813}]</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT160x128x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(101.59)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT160x128x64_MI16x...', 'stream': 0, 'mean_duration_us': 101.59}]</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -33534,12 +33578,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x288x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_9_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(11587.363), 'mean_duration_us': np.float64(96.56135833333333), 'median_duration_us': np.float64(95.899), 'std_dev_duration_us': np.float64(2.207858184590643), 'min_duration_us': np.float64(93.814), 'max_duration_us': np.float64(105.121)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x288x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_9_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 120, 'total_duration_us': 11587.363, 'mean_duration_us': 96.56135833333333, 'median_duration_us': 95.899, 'std_dev_duration_us': 2.207858184590643, 'min_duration_us': 93.814, 'max_duration_us': 105.121}]</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x288x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(96.56)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x288x64_MI16x...', 'stream': 0, 'mean_duration_us': 96.56}]</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -33699,12 +33743,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 240, 'total_duration_us': np.float64(1649.788), 'mean_duration_us': np.float64(6.874116666666667), 'median_duration_us': np.float64(6.895), 'std_dev_duration_us': np.float64(0.40092175428075183), 'min_duration_us': np.float64(5.812), 'max_duration_us': np.float64(8.979)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 240, 'total_duration_us': 1649.788, 'mean_duration_us': 6.874116666666667, 'median_duration_us': 6.895, 'std_dev_duration_us': 0.40092175428075183, 'min_duration_us': 5.812, 'max_duration_us': 8.979}]</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(6.87)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 6.87}]</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -33864,12 +33908,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_5_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 20, 'total_duration_us': np.float64(622.568), 'mean_duration_us': np.float64(31.1284), 'median_duration_us': np.float64(30.448999999999998), 'std_dev_duration_us': np.float64(1.3790227119231941), 'min_duration_us': np.float64(28.705), 'max_duration_us': np.float64(33.516)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_5_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 20, 'total_duration_us': 622.568, 'mean_duration_us': 31.1284, 'median_duration_us': 30.448999999999998, 'std_dev_duration_us': 1.3790227119231941, 'min_duration_us': 28.705, 'max_duration_us': 33.516}]</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(31.13)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x160x64_MI16x...', 'stream': 0, 'mean_duration_us': 31.13}]</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -34029,12 +34073,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(514.482), 'mean_duration_us': np.float64(8.5747), 'median_duration_us': np.float64(8.6385), 'std_dev_duration_us': np.float64(0.3650420660691038), 'min_duration_us': np.float64(7.657), 'max_duration_us': np.float64(9.18)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': 514.482, 'mean_duration_us': 8.5747, 'median_duration_us': 8.6385, 'std_dev_duration_us': 0.3650420660691038, 'min_duration_us': 7.657, 'max_duration_us': 9.18}]</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(8.57)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 8.57}]</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -34194,12 +34238,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(419.266), 'mean_duration_us': np.float64(6.987766666666667), 'median_duration_us': np.float64(6.895), 'std_dev_duration_us': np.float64(0.5233797654561062), 'min_duration_us': np.float64(5.973), 'max_duration_us': np.float64(8.658)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': 419.266, 'mean_duration_us': 6.987766666666667, 'median_duration_us': 6.895, 'std_dev_duration_us': 0.5233797654561062, 'min_duration_us': 5.973, 'max_duration_us': 8.658}]</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(6.99)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 6.99}]</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -34359,12 +34403,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(384.538), 'mean_duration_us': np.float64(6.408966666666667), 'median_duration_us': np.float64(6.273), 'std_dev_duration_us': np.float64(0.7107715049312417), 'min_duration_us': np.float64(5.091), 'max_duration_us': np.float64(8.659)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': 384.538, 'mean_duration_us': 6.408966666666667, 'median_duration_us': 6.273, 'std_dev_duration_us': 0.7107715049312417, 'min_duration_us': 5.091, 'max_duration_us': 8.659}]</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(6.41)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 6.41}]</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -34524,12 +34568,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(355.711), 'mean_duration_us': np.float64(5.928516666666667), 'median_duration_us': np.float64(5.812), 'std_dev_duration_us': np.float64(0.600517262912196), 'min_duration_us': np.float64(4.609), 'max_duration_us': np.float64(7.857)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 60, 'total_duration_us': 355.711, 'mean_duration_us': 5.928516666666667, 'median_duration_us': 5.812, 'std_dev_duration_us': 0.600517262912196, 'min_duration_us': 4.609, 'max_duration_us': 7.857}]</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(5.93)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 5.93}]</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -34689,12 +34733,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 15, 'total_duration_us': np.float64(69.66600000000001), 'mean_duration_us': np.float64(4.644400000000001), 'median_duration_us': np.float64(4.689), 'std_dev_duration_us': np.float64(0.2239195688932374), 'min_duration_us': np.float64(4.248), 'max_duration_us': np.float64(5.01)}, {'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA1_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB4_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS0_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_1', 'stream': 0, 'count': 15, 'total_duration_us': np.float64(282.956), 'mean_duration_us': np.float64(18.863733333333336), 'median_duration_us': np.float64(17.158), 'std_dev_duration_us': np.float64(7.847680162244695), 'min_duration_us': np.float64(15.234), 'max_duration_us': np.float64(47.99)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 15, 'total_duration_us': 69.66600000000001, 'mean_duration_us': 4.644400000000001, 'median_duration_us': 4.689, 'std_dev_duration_us': 0.2239195688932374, 'min_duration_us': 4.248, 'max_duration_us': 5.01}, {'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA1_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB4_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS0_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_1', 'stream': 0, 'count': 15, 'total_duration_us': 282.956, 'mean_duration_us': 18.863733333333336, 'median_duration_us': 17.158, 'std_dev_duration_us': 7.847680162244695, 'min_duration_us': 15.234, 'max_duration_us': 47.99}]</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.64)}, {'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16...', 'stream': 0, 'mean_duration_us': np.float64(18.86)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 4.64}, {'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16...', 'stream': 0, 'mean_duration_us': 18.86}]</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -34854,12 +34898,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x64x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB4_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(136.148), 'mean_duration_us': np.float64(27.229599999999998), 'median_duration_us': np.float64(27.262), 'std_dev_duration_us': np.float64(0.7408710009171641), 'min_duration_us': np.float64(26.139), 'max_duration_us': np.float64(28.104)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x64x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB4_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 5, 'total_duration_us': 136.148, 'mean_duration_us': 27.229599999999998, 'median_duration_us': 27.262, 'std_dev_duration_us': 0.7408710009171641, 'min_duration_us': 26.139, 'max_duration_us': 28.104}]</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x64x64_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(27.23)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x64x64_MI16x1...', 'stream': 0, 'mean_duration_us': 27.23}]</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -35019,12 +35063,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA1_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB4_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS0_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_1', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(60.253), 'mean_duration_us': np.float64(12.0506), 'median_duration_us': np.float64(11.906), 'std_dev_duration_us': np.float64(0.49213477828741153), 'min_duration_us': np.float64(11.345), 'max_duration_us': np.float64(12.628)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16x1_SN_LDSB0_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA1_GRVWB4_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA128_LBSPPB128_LBSPPM0_LPA16_LPB4_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB4_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS0_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_1', 'stream': 0, 'count': 5, 'total_duration_us': 60.253, 'mean_duration_us': 12.0506, 'median_duration_us': 11.906, 'std_dev_duration_us': 0.49213477828741153, 'min_duration_us': 11.345, 'max_duration_us': 12.628}]</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16...', 'stream': 0, 'mean_duration_us': np.float64(12.05)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x32_MI16x16...', 'stream': 0, 'mean_duration_us': 12.05}]</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -35184,12 +35228,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(58.97), 'mean_duration_us': np.float64(11.794), 'median_duration_us': np.float64(5.772), 'std_dev_duration_us': np.float64(12.405547646113815), 'min_duration_us': np.float64(5.411), 'max_duration_us': np.float64(36.603)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': 58.97, 'mean_duration_us': 11.794, 'median_duration_us': 5.772, 'std_dev_duration_us': 12.405547646113815, 'min_duration_us': 5.411, 'max_duration_us': 36.603}]</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(11.79)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 11.79}]</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -35349,12 +35393,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bjlk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x16x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB1_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(47.143), 'mean_duration_us': np.float64(9.4286), 'median_duration_us': np.float64(9.14), 'std_dev_duration_us': np.float64(0.45920696858823895), 'min_duration_us': np.float64(8.94), 'max_duration_us': np.float64(10.062)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bjlk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x16x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB1_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB256_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG64_4_1', 'stream': 0, 'count': 5, 'total_duration_us': 47.143, 'mean_duration_us': 9.4286, 'median_duration_us': 9.14, 'std_dev_duration_us': 0.45920696858823895, 'min_duration_us': 8.94, 'max_duration_us': 10.062}]</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bjlk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x16x128_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(9.43)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bjlk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT64x16x128_MI16x1...', 'stream': 0, 'mean_duration_us': 9.43}]</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -35514,12 +35558,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(31.067), 'mean_duration_us': np.float64(6.2134), 'median_duration_us': np.float64(6.093), 'std_dev_duration_us': np.float64(0.28699937282161453), 'min_duration_us': np.float64(6.013), 'max_duration_us': np.float64(6.775)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA0_NTB4_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': 31.067, 'mean_duration_us': 6.2134, 'median_duration_us': 6.093, 'std_dev_duration_us': 0.28699937282161453, 'min_duration_us': 6.013, 'max_duration_us': 6.775}]</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(6.21)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 6.21}]</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -35679,12 +35723,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(30.145000000000003), 'mean_duration_us': np.float64(6.029000000000001), 'median_duration_us': np.float64(6.093), 'std_dev_duration_us': np.float64(0.2632732420888988), 'min_duration_us': np.float64(5.652), 'max_duration_us': np.float64(6.374)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 5, 'total_duration_us': 30.145000000000003, 'mean_duration_us': 6.029000000000001, 'median_duration_us': 6.093, 'std_dev_duration_us': 0.2632732420888988, 'min_duration_us': 5.652, 'max_duration_us': 6.374}]</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': np.float64(6.03)}]</t>
+          <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT16x16x256_MI16x1...', 'stream': 0, 'mean_duration_us': 6.03}]</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -35747,227 +35791,227 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>param: convNd</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>param: input_shape</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>param: filter_shape</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>param: dtype_input_weight</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>param: input_stride</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>param: weight_stride</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>param: bias</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>param: stride</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>param: padding</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>param: dilation</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>param: transposed_conv</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>param: output_padding</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>param: groups</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>process_name_first</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>process_label_first</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>thread_name_first</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -36105,12 +36149,12 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[{'name': 'Im2d2Col_v2', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(219.258), 'mean_duration_us': np.float64(43.851600000000005), 'median_duration_us': np.float64(44.621), 'std_dev_duration_us': np.float64(1.7498733211292758), 'min_duration_us': np.float64(40.372), 'max_duration_us': np.float64(45.063)}, {'name': 'Cijk_Ailk_Bljk_BBS_BH_MT64x64x64_MI16x16x16x1_SN_1LDSB0_APM1_ABV0_ACED0_AF0EM1_AF1EM1_AMAS0_ASE_ASGT_ASLT_ASM_ASAE01_ASCE01_ASEM1_AAC0_BL1_BS1_CLR1_DTLA0_DTLB0_DTVA0_DTVB0_DVO0_ETSP_EPS1_ELFLR0_EMLL0_FSSC10_FL0_GLVWA2_GLVWB8_GRCGA1_GRCGB1_GRPM1_GRVWn1_GSU1_GSUASB_GLS0_ISA942_IU1_K1_KLA_LBSPPA1024_LBSPPB128_LPA16_LPB16_LDL1_LRVW8_LWPMn1_LDW0_FMA_MIAV0_MDA2_MO40_MMFSC_MKFGSU256_NTA0_NTB0_NTC0_NTD0_NEPBS0_NLCA1_NLCB1_ONLL1_OPLV0_PK0_PAP0_PGR1_PLR5_PKA0_SIA3_SLW1_SS0_SU16_SUM0_SUS512_SCIUI1_SPO0_SRVW0_SSO0_SVW4_SNLL0_TSGRA0_TSGRB0_TT1_64_TLDS1_UMLDSA0_UMLDSB1_U64SL1_USFGROn1_VAW1_VSn1_VW1_VWB1_VFLRP1_WSGRA0_WSGRB0_WS64_WG64_4_1_WGMn16', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(298.64099999999996), 'mean_duration_us': np.float64(59.728199999999994), 'median_duration_us': np.float64(60.458), 'std_dev_duration_us': np.float64(1.7082119774782034), 'min_duration_us': np.float64(56.328), 'max_duration_us': np.float64(60.899)}]</t>
+          <t>[{'name': 'Im2d2Col_v2', 'stream': 0, 'count': 5, 'total_duration_us': 219.258, 'mean_duration_us': 43.851600000000005, 'median_duration_us': 44.621, 'std_dev_duration_us': 1.7498733211292758, 'min_duration_us': 40.372, 'max_duration_us': 45.063}, {'name': 'Cijk_Ailk_Bljk_BBS_BH_MT64x64x64_MI16x16x16x1_SN_1LDSB0_APM1_ABV0_ACED0_AF0EM1_AF1EM1_AMAS0_ASE_ASGT_ASLT_ASM_ASAE01_ASCE01_ASEM1_AAC0_BL1_BS1_CLR1_DTLA0_DTLB0_DTVA0_DTVB0_DVO0_ETSP_EPS1_ELFLR0_EMLL0_FSSC10_FL0_GLVWA2_GLVWB8_GRCGA1_GRCGB1_GRPM1_GRVWn1_GSU1_GSUASB_GLS0_ISA942_IU1_K1_KLA_LBSPPA1024_LBSPPB128_LPA16_LPB16_LDL1_LRVW8_LWPMn1_LDW0_FMA_MIAV0_MDA2_MO40_MMFSC_MKFGSU256_NTA0_NTB0_NTC0_NTD0_NEPBS0_NLCA1_NLCB1_ONLL1_OPLV0_PK0_PAP0_PGR1_PLR5_PKA0_SIA3_SLW1_SS0_SU16_SUM0_SUS512_SCIUI1_SPO0_SRVW0_SSO0_SVW4_SNLL0_TSGRA0_TSGRB0_TT1_64_TLDS1_UMLDSA0_UMLDSB1_U64SL1_USFGROn1_VAW1_VSn1_VW1_VWB1_VFLRP1_WSGRA0_WSGRB0_WS64_WG64_4_1_WGMn16', 'stream': 0, 'count': 5, 'total_duration_us': 298.64099999999996, 'mean_duration_us': 59.728199999999994, 'median_duration_us': 60.458, 'std_dev_duration_us': 1.7082119774782034, 'min_duration_us': 56.328, 'max_duration_us': 60.899}]</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>[{'name': 'Im2d2Col_v2', 'stream': 0, 'mean_duration_us': np.float64(43.85)}, {'name': 'Cijk_Ailk_Bljk_BBS_BH_MT64x64x64_MI16x16x16x1_SN_1LDSB0_APM1_ABV...', 'stream': 0, 'mean_duration_us': np.float64(59.73)}]</t>
+          <t>[{'name': 'Im2d2Col_v2', 'stream': 0, 'mean_duration_us': 43.85}, {'name': 'Cijk_Ailk_Bljk_BBS_BH_MT64x64x64_MI16x16x16x1_SN_1LDSB0_APM1_ABV...', 'stream': 0, 'mean_duration_us': 59.73}]</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -36173,192 +36217,192 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>param: shape_in1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>param: shape_in2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>param: dtype_in1_in2_out</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>param: stride_input1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>param: stride_input2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>param: stride_output</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>process_name_first</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>process_label_first</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>thread_name_first</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -36395,7 +36439,11 @@
           <t>(21237760, 4096, 1)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>0.02123776</v>
       </c>
@@ -36457,12 +36505,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(4463.737999999999), 'mean_duration_us': np.float64(37.19781666666666), 'median_duration_us': np.float64(37.084), 'std_dev_duration_us': np.float64(4.0768960782751815), 'min_duration_us': np.float64(28.985), 'max_duration_us': np.float64(50.435)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': 4463.737999999999, 'mean_duration_us': 37.19781666666666, 'median_duration_us': 37.084, 'std_dev_duration_us': 4.0768960782751815, 'min_duration_us': 28.985, 'max_duration_us': 50.435}]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': np.float64(37.2)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': 37.2}]</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -36541,7 +36589,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>0.02123776</v>
       </c>
@@ -36603,12 +36655,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(3008.275), 'mean_duration_us': np.float64(25.068958333333335), 'median_duration_us': np.float64(24.8965), 'std_dev_duration_us': np.float64(2.5754997003683036), 'min_duration_us': np.float64(19.765), 'max_duration_us': np.float64(33.957)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': 3008.275, 'mean_duration_us': 25.068958333333335, 'median_duration_us': 24.8965, 'std_dev_duration_us': 2.5754997003683036, 'min_duration_us': 19.765, 'max_duration_us': 33.957}]</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(25.07)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': 25.07}]</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -36687,7 +36739,11 @@
           <t>(5309440, 1024, 1)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>0.00530944</v>
       </c>
@@ -36749,12 +36805,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 245, 'total_duration_us': np.float64(2450.014), 'mean_duration_us': np.float64(10.000057142857143), 'median_duration_us': np.float64(9.942), 'std_dev_duration_us': np.float64(0.8502293788941274), 'min_duration_us': np.float64(8.218), 'max_duration_us': np.float64(13.429)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 245, 'total_duration_us': 2450.014, 'mean_duration_us': 10.000057142857143, 'median_duration_us': 9.942, 'std_dev_duration_us': 0.8502293788941274, 'min_duration_us': 8.218, 'max_duration_us': 13.429}]</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(10.0)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 10.0}]</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -36833,7 +36889,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>0.00530944</v>
       </c>
@@ -36895,12 +36955,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(868.479), 'mean_duration_us': np.float64(7.237325), 'median_duration_us': np.float64(7.175), 'std_dev_duration_us': np.float64(0.5774263757181518), 'min_duration_us': np.float64(6.414), 'max_duration_us': np.float64(10.503)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': 868.479, 'mean_duration_us': 7.237325, 'median_duration_us': 7.175, 'std_dev_duration_us': 0.5774263757181518, 'min_duration_us': 6.414, 'max_duration_us': 10.503}]</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(7.24)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': 7.24}]</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -36979,7 +37039,11 @@
           <t>(3840, 768, 1)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>3.84e-06</v>
       </c>
@@ -37041,12 +37105,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 125, 'total_duration_us': np.float64(572.1489999999999), 'mean_duration_us': np.float64(4.577191999999999), 'median_duration_us': np.float64(4.489), 'std_dev_duration_us': np.float64(0.3315058659149187), 'min_duration_us': np.float64(4.048), 'max_duration_us': np.float64(5.452)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 125, 'total_duration_us': 572.1489999999999, 'mean_duration_us': 4.577191999999999, 'median_duration_us': 4.489, 'std_dev_duration_us': 0.3315058659149187, 'min_duration_us': 4.048, 'max_duration_us': 5.452}]</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.58)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.58}]</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -37125,7 +37189,11 @@
           <t>(25, 25, 5, 1)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>3e-07</v>
       </c>
@@ -37187,12 +37255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(555.2339999999999), 'mean_duration_us': np.float64(4.626949999999999), 'median_duration_us': np.float64(4.569), 'std_dev_duration_us': np.float64(0.3686557755323161), 'min_duration_us': np.float64(4.008), 'max_duration_us': np.float64(5.612)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 120, 'total_duration_us': 555.2339999999999, 'mean_duration_us': 4.626949999999999, 'median_duration_us': 4.569, 'std_dev_duration_us': 0.3686557755323161, 'min_duration_us': 4.008, 'max_duration_us': 5.612}]</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.63)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 4.63}]</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -37271,7 +37339,11 @@
           <t>(15360, 3072, 1)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>1.536e-05</v>
       </c>
@@ -37333,12 +37405,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(308.848), 'mean_duration_us': np.float64(5.147466666666667), 'median_duration_us': np.float64(5.051), 'std_dev_duration_us': np.float64(0.35748615202394757), 'min_duration_us': np.float64(4.369), 'max_duration_us': np.float64(6.093)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': 308.848, 'mean_duration_us': 5.147466666666667, 'median_duration_us': 5.051, 'std_dev_duration_us': 0.35748615202394757, 'min_duration_us': 4.369, 'max_duration_us': 6.093}]</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': np.float64(5.15)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': 5.15}]</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -37417,7 +37489,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>3.84e-06</v>
       </c>
@@ -37479,12 +37555,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(291.33199999999994), 'mean_duration_us': np.float64(4.855533333333332), 'median_duration_us': np.float64(4.73), 'std_dev_duration_us': np.float64(0.32905027309245954), 'min_duration_us': np.float64(4.289), 'max_duration_us': np.float64(5.532)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': 291.33199999999994, 'mean_duration_us': 4.855533333333332, 'median_duration_us': 4.73, 'std_dev_duration_us': 0.32905027309245954, 'min_duration_us': 4.289, 'max_duration_us': 5.532}]</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(4.86)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': 4.86}]</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -37563,7 +37639,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>1.536e-05</v>
       </c>
@@ -37625,12 +37705,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(291.32899999999995), 'mean_duration_us': np.float64(4.855483333333333), 'median_duration_us': np.float64(4.69), 'std_dev_duration_us': np.float64(0.34405471908145985), 'min_duration_us': np.float64(4.209), 'max_duration_us': np.float64(5.773)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': 291.32899999999995, 'mean_duration_us': 4.855483333333333, 'median_duration_us': 4.69, 'std_dev_duration_us': 0.34405471908145985, 'min_duration_us': 4.209, 'max_duration_us': 5.773}]</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(4.86)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': 4.86}]</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -37709,7 +37789,11 @@
           <t>(5309440, 0, 1)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>0.005308416</v>
       </c>
@@ -37771,12 +37855,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(59.051), 'mean_duration_us': np.float64(11.8102), 'median_duration_us': np.float64(11.826), 'std_dev_duration_us': np.float64(0.3424951970466156), 'min_duration_us': np.float64(11.345), 'max_duration_us': np.float64(12.387)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 59.051, 'mean_duration_us': 11.8102, 'median_duration_us': 11.826, 'std_dev_duration_us': 0.3424951970466156, 'min_duration_us': 11.345, 'max_duration_us': 12.387}]</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(11.81)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 11.81}]</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -37855,7 +37939,11 @@
           <t>(5184, 1, 1)</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>0.003981312</v>
       </c>
@@ -37917,12 +38005,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(49.509), 'mean_duration_us': np.float64(9.9018), 'median_duration_us': np.float64(9.662), 'std_dev_duration_us': np.float64(0.483819966516472), 'min_duration_us': np.float64(9.26), 'max_duration_us': np.float64(10.544)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 49.509, 'mean_duration_us': 9.9018, 'median_duration_us': 9.662, 'std_dev_duration_us': 0.483819966516472, 'min_duration_us': 9.26, 'max_duration_us': 10.544}]</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(9.9)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 9.9}]</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -38001,7 +38089,11 @@
           <t>(1, 1)</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>7.68e-07</v>
       </c>
@@ -38063,12 +38155,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 10, 'total_duration_us': np.float64(49.504000000000005), 'mean_duration_us': np.float64(4.9504), 'median_duration_us': np.float64(5.091), 'std_dev_duration_us': np.float64(0.4543756595593562), 'min_duration_us': np.float64(4.088), 'max_duration_us': np.float64(5.491)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 10, 'total_duration_us': 49.504000000000005, 'mean_duration_us': 4.9504, 'median_duration_us': 5.091, 'std_dev_duration_us': 0.4543756595593562, 'min_duration_us': 4.088, 'max_duration_us': 5.491}]</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.95)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 4.95}]</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -38147,7 +38239,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>5e-09</v>
       </c>
@@ -38205,12 +38301,12 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(24.131), 'mean_duration_us': np.float64(4.8262), 'median_duration_us': np.float64(4.69), 'std_dev_duration_us': np.float64(0.2316759806281177), 'min_duration_us': np.float64(4.61), 'max_duration_us': np.float64(5.251)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 24.131, 'mean_duration_us': 4.8262, 'median_duration_us': 4.69, 'std_dev_duration_us': 0.2316759806281177, 'min_duration_us': 4.61, 'max_duration_us': 5.251}]</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.83)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.83}]</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -38289,7 +38385,11 @@
           <t>(5184, 1, 1)</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>5.184e-06</v>
       </c>
@@ -38351,12 +38451,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(24.011000000000003), 'mean_duration_us': np.float64(4.802200000000001), 'median_duration_us': np.float64(4.57), 'std_dev_duration_us': np.float64(0.5108465131524341), 'min_duration_us': np.float64(4.41), 'max_duration_us': np.float64(5.812)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 24.011000000000003, 'mean_duration_us': 4.802200000000001, 'median_duration_us': 4.57, 'std_dev_duration_us': 0.5108465131524341, 'min_duration_us': 4.41, 'max_duration_us': 5.812}]</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': np.float64(4.8)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': 4.8}]</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -38435,7 +38535,11 @@
           <t>(1, 1, 1)</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>7.68e-07</v>
       </c>
@@ -38497,12 +38601,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.931), 'mean_duration_us': np.float64(4.7862), 'median_duration_us': np.float64(4.61), 'std_dev_duration_us': np.float64(0.5367853947342459), 'min_duration_us': np.float64(4.249), 'max_duration_us': np.float64(5.812)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::DivFunctor&lt;c10::BFloat16&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 23.931, 'mean_duration_us': 4.7862, 'median_duration_us': 4.61, 'std_dev_duration_us': 0.5367853947342459, 'min_duration_us': 4.249, 'max_duration_us': 5.812}]</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.79)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 4.79}]</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -38581,7 +38685,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>5.184e-06</v>
       </c>
@@ -38643,12 +38751,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.21), 'mean_duration_us': np.float64(4.642), 'median_duration_us': np.float64(4.57), 'std_dev_duration_us': np.float64(0.28190920524168783), 'min_duration_us': np.float64(4.329), 'max_duration_us': np.float64(5.011)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 23.21, 'mean_duration_us': 4.642, 'median_duration_us': 4.57, 'std_dev_duration_us': 0.28190920524168783, 'min_duration_us': 4.329, 'max_duration_us': 5.011}]</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.64)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.64}]</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -38727,7 +38835,11 @@
           <t>(5184, 1, 1)</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>5.184e-06</v>
       </c>
@@ -38789,12 +38901,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.167), 'mean_duration_us': np.float64(4.6334), 'median_duration_us': np.float64(4.489), 'std_dev_duration_us': np.float64(0.36638482501326386), 'min_duration_us': np.float64(4.128), 'max_duration_us': np.float64(5.131)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 23.167, 'mean_duration_us': 4.6334, 'median_duration_us': 4.489, 'std_dev_duration_us': 0.36638482501326386, 'min_duration_us': 4.128, 'max_duration_us': 5.131}]</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.63)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.63}]</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -38873,7 +38985,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>5.184e-06</v>
       </c>
@@ -38935,12 +39051,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.087000000000003), 'mean_duration_us': np.float64(4.617400000000001), 'median_duration_us': np.float64(4.569), 'std_dev_duration_us': np.float64(0.2909203327373321), 'min_duration_us': np.float64(4.328), 'max_duration_us': np.float64(5.171)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 23.087000000000003, 'mean_duration_us': 4.617400000000001, 'median_duration_us': 4.569, 'std_dev_duration_us': 0.2909203327373321, 'min_duration_us': 4.328, 'max_duration_us': 5.171}]</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.62)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.62}]</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -39019,7 +39135,11 @@
           <t>(4, 1)</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>2.0736e-05</v>
       </c>
@@ -39081,12 +39201,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(22.928), 'mean_duration_us': np.float64(4.5856), 'median_duration_us': np.float64(4.329), 'std_dev_duration_us': np.float64(0.4130828488330158), 'min_duration_us': np.float64(4.169), 'max_duration_us': np.float64(5.291)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::CUDAFunctor_add&lt;float&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;float&gt; const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 22.928, 'mean_duration_us': 4.5856, 'median_duration_us': 4.329, 'std_dev_duration_us': 0.4130828488330158, 'min_duration_us': 4.169, 'max_duration_us': 5.291}]</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(4.59)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 4.59}]</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -39165,7 +39285,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>1e-09</v>
       </c>
@@ -39227,12 +39351,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(22.487000000000002), 'mean_duration_us': np.float64(4.497400000000001), 'median_duration_us': np.float64(4.369), 'std_dev_duration_us': np.float64(0.3635748066079388), 'min_duration_us': np.float64(4.048), 'max_duration_us': np.float64(5.131)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 22.487000000000002, 'mean_duration_us': 4.497400000000001, 'median_duration_us': 4.369, 'std_dev_duration_us': 0.3635748066079388, 'min_duration_us': 4.048, 'max_duration_us': 5.131}]</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.5)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': 4.5}]</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -39311,7 +39435,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>1e-09</v>
       </c>
@@ -39373,12 +39501,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(21.884999999999998), 'mean_duration_us': np.float64(4.377), 'median_duration_us': np.float64(4.329), 'std_dev_duration_us': np.float64(0.3979557764375334), 'min_duration_us': np.float64(3.848), 'max_duration_us': np.float64(4.97)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 21.884999999999998, 'mean_duration_us': 4.377, 'median_duration_us': 4.329, 'std_dev_duration_us': 0.3979557764375334, 'min_duration_us': 3.848, 'max_duration_us': 4.97}]</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': np.float64(4.38)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': 4.38}]</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -39457,7 +39585,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>5.184e-06</v>
       </c>
@@ -39579,7 +39711,11 @@
           <t>(5184, 1)</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>5.184e-06</v>
       </c>
@@ -39701,7 +39837,11 @@
           <t>(4, 4, 1)</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>2.0736e-05</v>
       </c>
@@ -39803,182 +39943,182 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>param: op_shape</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>param: dtype_in_out</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>param: stride_input</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>param: stride_output</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>process_name_first</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>process_label_first</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>thread_name_first</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -40071,12 +40211,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 360, 'total_duration_us': np.float64(6226.331), 'mean_duration_us': np.float64(17.29536388888889), 'median_duration_us': np.float64(15.795), 'std_dev_duration_us': np.float64(2.8259221431687647), 'min_duration_us': np.float64(12.067), 'max_duration_us': np.float64(23.693)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 360, 'total_duration_us': 6226.331, 'mean_duration_us': 17.29536388888889, 'median_duration_us': 15.795, 'std_dev_duration_us': 2.8259221431687647, 'min_duration_us': 12.067, 'max_duration_us': 23.693}]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(17.3)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 17.3}]</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -40145,7 +40285,11 @@
           <t>(21237760, 4096, 1)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F3" t="n">
         <v>0.02123776</v>
       </c>
@@ -40207,12 +40351,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(3529.13), 'mean_duration_us': np.float64(29.40941666666667), 'median_duration_us': np.float64(29.1055), 'std_dev_duration_us': np.float64(1.2255553202754885), 'min_duration_us': np.float64(27.703), 'max_duration_us': np.float64(33.035)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 120, 'total_duration_us': 3529.13, 'mean_duration_us': 29.40941666666667, 'median_duration_us': 29.1055, 'std_dev_duration_us': 1.2255553202754885, 'min_duration_us': 27.703, 'max_duration_us': 33.035}]</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': np.float64(29.41)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': 29.41}]</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -40347,12 +40491,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 120, 'total_duration_us': np.float64(1979.3850000000002), 'mean_duration_us': np.float64(16.494875), 'median_duration_us': np.float64(16.216), 'std_dev_duration_us': np.float64(0.889071627809031), 'min_duration_us': np.float64(14.673), 'max_duration_us': np.float64(18.802)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 120, 'total_duration_us': 1979.3850000000002, 'mean_duration_us': 16.494875, 'median_duration_us': 16.216, 'std_dev_duration_us': 0.889071627809031, 'min_duration_us': 14.673, 'max_duration_us': 18.802}]</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(16.49)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 16.49}]</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -40487,12 +40631,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(1138.047), 'mean_duration_us': np.float64(227.6094), 'median_duration_us': np.float64(225.036), 'std_dev_duration_us': np.float64(4.802322254909601), 'min_duration_us': np.float64(224.634), 'max_duration_us': np.float64(237.144)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 1138.047, 'mean_duration_us': 227.6094, 'median_duration_us': 225.036, 'std_dev_duration_us': 4.802322254909601, 'min_duration_us': 224.634, 'max_duration_us': 237.144}]</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(227.61)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 227.61}]</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -40627,12 +40771,12 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(1136.443), 'mean_duration_us': np.float64(227.2886), 'median_duration_us': np.float64(226.238), 'std_dev_duration_us': np.float64(2.4922390415046425), 'min_duration_us': np.float64(224.715), 'max_duration_us': np.float64(230.528)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 1136.443, 'mean_duration_us': 227.2886, 'median_duration_us': 226.238, 'std_dev_duration_us': 2.4922390415046425, 'min_duration_us': 224.715, 'max_duration_us': 230.528}]</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(227.29)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 227.29}]</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -40767,12 +40911,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 180, 'total_duration_us': np.float64(1058.8980000000001), 'mean_duration_us': np.float64(5.882766666666668), 'median_duration_us': np.float64(5.893), 'std_dev_duration_us': np.float64(0.3655466545691078), 'min_duration_us': np.float64(4.81), 'max_duration_us': np.float64(6.775)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 180, 'total_duration_us': 1058.8980000000001, 'mean_duration_us': 5.882766666666668, 'median_duration_us': 5.893, 'std_dev_duration_us': 0.3655466545691078, 'min_duration_us': 4.81, 'max_duration_us': 6.775}]</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(5.88)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 5.88}]</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -40907,12 +41051,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(898.455), 'mean_duration_us': np.float64(179.691), 'median_duration_us': np.float64(189.314), 'std_dev_duration_us': np.float64(29.36311296167353), 'min_duration_us': np.float64(122.118), 'max_duration_us': np.float64(204.147)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': 898.455, 'mean_duration_us': 179.691, 'median_duration_us': 189.314, 'std_dev_duration_us': 29.36311296167353, 'min_duration_us': 122.118, 'max_duration_us': 204.147}]</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(179.69)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': 179.69}]</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -41047,12 +41191,12 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(848.183), 'mean_duration_us': np.float64(169.6366), 'median_duration_us': np.float64(169.549), 'std_dev_duration_us': np.float64(0.12531017516545753), 'min_duration_us': np.float64(169.508), 'max_duration_us': np.float64(169.789)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 848.183, 'mean_duration_us': 169.6366, 'median_duration_us': 169.549, 'std_dev_duration_us': 0.12531017516545753, 'min_duration_us': 169.508, 'max_duration_us': 169.789}]</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(169.64)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 169.64}]</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -41187,12 +41331,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(401.82699999999994), 'mean_duration_us': np.float64(6.697116666666665), 'median_duration_us': np.float64(6.775), 'std_dev_duration_us': np.float64(0.31499709478378085), 'min_duration_us': np.float64(5.973), 'max_duration_us': np.float64(7.296)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 60, 'total_duration_us': 401.82699999999994, 'mean_duration_us': 6.697116666666665, 'median_duration_us': 6.775, 'std_dev_duration_us': 0.31499709478378085, 'min_duration_us': 5.973, 'max_duration_us': 7.296}]</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(6.7)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': 6.7}]</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -41261,7 +41405,11 @@
           <t>(15360, 3072, 1)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F11" t="n">
         <v>1.536e-05</v>
       </c>
@@ -41323,12 +41471,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': np.float64(292.09), 'mean_duration_us': np.float64(4.868166666666666), 'median_duration_us': np.float64(4.77), 'std_dev_duration_us': np.float64(0.40604807460310527), 'min_duration_us': np.float64(4.128), 'max_duration_us': np.float64(5.852)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 60, 'total_duration_us': 292.09, 'mean_duration_us': 4.868166666666666, 'median_duration_us': 4.77, 'std_dev_duration_us': 0.40604807460310527, 'min_duration_us': 4.128, 'max_duration_us': 5.852}]</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': np.float64(4.87)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': 4.87}]</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -41445,12 +41593,12 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 10, 'total_duration_us': np.float64(95.929), 'mean_duration_us': np.float64(9.5929), 'median_duration_us': np.float64(5.912), 'std_dev_duration_us': np.float64(9.921683712455259), 'min_duration_us': np.float64(4.049), 'max_duration_us': np.float64(38.407)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 10, 'total_duration_us': 95.929, 'mean_duration_us': 9.5929, 'median_duration_us': 5.912, 'std_dev_duration_us': 9.921683712455259, 'min_duration_us': 4.049, 'max_duration_us': 38.407}]</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(9.59)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': 9.59}]</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -41585,12 +41733,12 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(75.429), 'mean_duration_us': np.float64(15.0858), 'median_duration_us': np.float64(14.823), 'std_dev_duration_us': np.float64(0.4742212142028235), 'min_duration_us': np.float64(14.603), 'max_duration_us': np.float64(15.755)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': 75.429, 'mean_duration_us': 15.0858, 'median_duration_us': 14.823, 'std_dev_duration_us': 0.4742212142028235, 'min_duration_us': 14.603, 'max_duration_us': 15.755}]</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(15.09)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': 15.09}]</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -41721,12 +41869,12 @@
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 10, 'total_duration_us': np.float64(42.248), 'mean_duration_us': np.float64(4.2248), 'median_duration_us': np.float64(4.148999999999999), 'std_dev_duration_us': np.float64(0.4044254690298325), 'min_duration_us': np.float64(3.808), 'max_duration_us': np.float64(5.292)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'count': 10, 'total_duration_us': 42.248, 'mean_duration_us': 4.2248, 'median_duration_us': 4.148999999999999, 'std_dev_duration_us': 0.4044254690298325, 'min_duration_us': 3.808, 'max_duration_us': 5.292}]</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(4.22)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Host -&gt; Device)', 'stream': 0, 'mean_duration_us': 4.22}]</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -41861,12 +42009,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(27.898), 'mean_duration_us': np.float64(5.5796), 'median_duration_us': np.float64(5.572), 'std_dev_duration_us': np.float64(0.0162061716639064), 'min_duration_us': np.float64(5.571), 'max_duration_us': np.float64(5.612)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 27.898, 'mean_duration_us': 5.5796, 'median_duration_us': 5.572, 'std_dev_duration_us': 0.0162061716639064, 'min_duration_us': 5.571, 'max_duration_us': 5.612}]</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(5.58)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 5.58}]</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -41983,12 +42131,12 @@
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(26.455), 'mean_duration_us': np.float64(5.2909999999999995), 'median_duration_us': np.float64(5.251), 'std_dev_duration_us': np.float64(0.30444835358398653), 'min_duration_us': np.float64(4.93), 'max_duration_us': np.float64(5.732)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#11}::operator()() const::{lambda(bool)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 26.455, 'mean_duration_us': 5.2909999999999995, 'median_duration_us': 5.251, 'std_dev_duration_us': 0.30444835358398653, 'min_duration_us': 4.93, 'max_duration_us': 5.732}]</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(5.29)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 5.29}]</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -42105,12 +42253,12 @@
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(25.814), 'mean_duration_us': np.float64(5.1628), 'median_duration_us': np.float64(5.171), 'std_dev_duration_us': np.float64(0.1816726726835932), 'min_duration_us': np.float64(4.89), 'max_duration_us': np.float64(5.451)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#3}::operator()() const::{lambda(int)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 25.814, 'mean_duration_us': 5.1628, 'median_duration_us': 5.171, 'std_dev_duration_us': 0.1816726726835932, 'min_duration_us': 4.89, 'max_duration_us': 5.451}]</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(5.16)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 5.16}]</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -42245,12 +42393,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(25.655), 'mean_duration_us': np.float64(5.131), 'median_duration_us': np.float64(5.131), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(5.131), 'max_duration_us': np.float64(5.131)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 25.655, 'mean_duration_us': 5.131, 'median_duration_us': 5.131, 'std_dev_duration_us': 0.0, 'min_duration_us': 5.131, 'max_duration_us': 5.131}]</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(5.13)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 5.13}]</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -42385,12 +42533,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(24.21), 'mean_duration_us': np.float64(4.8420000000000005), 'median_duration_us': np.float64(4.529), 'std_dev_duration_us': np.float64(0.4251691428125987), 'min_duration_us': np.float64(4.489), 'max_duration_us': np.float64(5.491)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 24.21, 'mean_duration_us': 4.8420000000000005, 'median_duration_us': 4.529, 'std_dev_duration_us': 0.4251691428125987, 'min_duration_us': 4.489, 'max_duration_us': 5.491}]</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 0, 'mean_duration_us': np.float64(4.84)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 0, 'mean_duration_us': 4.84}]</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -42525,12 +42673,12 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.85), 'mean_duration_us': np.float64(4.7700000000000005), 'median_duration_us': np.float64(4.61), 'std_dev_duration_us': np.float64(0.3218459258713711), 'min_duration_us': np.float64(4.449), 'max_duration_us': np.float64(5.251)}]</t>
+          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'count': 5, 'total_duration_us': 23.85, 'mean_duration_us': 4.7700000000000005, 'median_duration_us': 4.61, 'std_dev_duration_us': 0.3218459258713711, 'min_duration_us': 4.449, 'max_duration_us': 5.251}]</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(4.77)}]</t>
+          <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'mean_duration_us': 4.77}]</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -42665,12 +42813,12 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.769), 'mean_duration_us': np.float64(4.7538), 'median_duration_us': np.float64(4.57), 'std_dev_duration_us': np.float64(0.2427059125773412), 'min_duration_us': np.float64(4.529), 'max_duration_us': np.float64(5.051)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#2})', 'stream': 0, 'count': 5, 'total_duration_us': 23.769, 'mean_duration_us': 4.7538, 'median_duration_us': 4.57, 'std_dev_duration_us': 0.2427059125773412, 'min_duration_us': 4.529, 'max_duration_us': 5.051}]</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(4.75)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 4.75}]</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -42805,12 +42953,12 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(23.368999999999996), 'mean_duration_us': np.float64(4.673799999999999), 'median_duration_us': np.float64(4.73), 'std_dev_duration_us': np.float64(0.19056169604618856), 'min_duration_us': np.float64(4.449), 'max_duration_us': np.float64(4.89)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 5, 'total_duration_us': 23.368999999999996, 'mean_duration_us': 4.673799999999999, 'median_duration_us': 4.73, 'std_dev_duration_us': 0.19056169604618856, 'min_duration_us': 4.449, 'max_duration_us': 4.89}]</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(4.67)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': 4.67}]</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -42945,12 +43093,12 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(22.929000000000002), 'mean_duration_us': np.float64(4.585800000000001), 'median_duration_us': np.float64(3.647), 'std_dev_duration_us': np.float64(2.16479425350309), 'min_duration_us': np.float64(2.525), 'max_duration_us': np.float64(8.739)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 22.929000000000002, 'mean_duration_us': 4.585800000000001, 'median_duration_us': 3.647, 'std_dev_duration_us': 2.16479425350309, 'min_duration_us': 2.525, 'max_duration_us': 8.739}]</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(4.59)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 4.59}]</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -43085,12 +43233,12 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(17.916), 'mean_duration_us': np.float64(3.5832), 'median_duration_us': np.float64(3.407), 'std_dev_duration_us': np.float64(0.6221727734319463), 'min_duration_us': np.float64(2.886), 'max_duration_us': np.float64(4.609)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 17.916, 'mean_duration_us': 3.5832, 'median_duration_us': 3.407, 'std_dev_duration_us': 0.6221727734319463, 'min_duration_us': 2.886, 'max_duration_us': 4.609}]</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(3.58)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 3.58}]</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -43159,7 +43307,11 @@
           <t>(20736, 4, 1)</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F25" t="n">
         <v>2.0736e-05</v>
       </c>
@@ -43221,12 +43373,12 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(15.99), 'mean_duration_us': np.float64(3.198), 'median_duration_us': np.float64(3.126), 'std_dev_duration_us': np.float64(0.3572125417731018), 'min_duration_us': np.float64(2.765), 'max_duration_us': np.float64(3.687)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sigmoid_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 5, 'total_duration_us': 15.99, 'mean_duration_us': 3.198, 'median_duration_us': 3.126, 'std_dev_duration_us': 0.3572125417731018, 'min_duration_us': 2.765, 'max_duration_us': 3.687}]</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': np.float64(3.2)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::si...', 'stream': 0, 'mean_duration_us': 3.2}]</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -43361,12 +43513,12 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(15.951), 'mean_duration_us': np.float64(3.1902), 'median_duration_us': np.float64(3.006), 'std_dev_duration_us': np.float64(0.5261100265153668), 'min_duration_us': np.float64(2.605), 'max_duration_us': np.float64(3.928)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 15.951, 'mean_duration_us': 3.1902, 'median_duration_us': 3.006, 'std_dev_duration_us': 0.5261100265153668, 'min_duration_us': 2.605, 'max_duration_us': 3.928}]</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(3.19)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 3.19}]</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -43501,12 +43653,12 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(15.391), 'mean_duration_us': np.float64(3.0782), 'median_duration_us': np.float64(2.926), 'std_dev_duration_us': np.float64(0.3955605642629204), 'min_duration_us': np.float64(2.726), 'max_duration_us': np.float64(3.848)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 15.391, 'mean_duration_us': 3.0782, 'median_duration_us': 2.926, 'std_dev_duration_us': 0.3955605642629204, 'min_duration_us': 2.726, 'max_duration_us': 3.848}]</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(3.08)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 3.08}]</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -43641,12 +43793,12 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': np.float64(15.030000000000001), 'mean_duration_us': np.float64(3.0060000000000002), 'median_duration_us': np.float64(2.926), 'std_dev_duration_us': np.float64(0.3119506371206829), 'min_duration_us': np.float64(2.725), 'max_duration_us': np.float64(3.568)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'count': 5, 'total_duration_us': 15.030000000000001, 'mean_duration_us': 3.0060000000000002, 'median_duration_us': 2.926, 'std_dev_duration_us': 0.3119506371206829, 'min_duration_us': 2.725, 'max_duration_us': 3.568}]</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': np.float64(3.01)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Host)', 'stream': 0, 'mean_duration_us': 3.01}]</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -43831,7 +43983,11 @@
           <t>(5184, 1)</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F30" t="n">
         <v>5.184e-06</v>
       </c>
@@ -43943,7 +44099,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F31" t="n">
         <v>1e-09</v>
       </c>
@@ -44167,7 +44327,11 @@
           <t>()</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="F33" t="n">
         <v>1e-09</v>
       </c>
